--- a/output/elod_progresivos.xlsx
+++ b/output/elod_progresivos.xlsx
@@ -51,7 +51,7 @@
       <color rgb="00FF0000"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -68,6 +68,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E6E6FA"/>
         <bgColor rgb="00E6E6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -89,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -109,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -191,6 +200,36 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1143000" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1003,7 +1042,7 @@
           <t>Nueva Zelanda</t>
         </is>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="9" t="n">
         <v>2745</v>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -1017,22 +1056,22 @@
       <c r="H6" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="I6" s="9" t="n">
+      <c r="I6" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="K6" s="9" t="n">
+      <c r="K6" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="M6" s="9" t="n">
+      <c r="M6" s="10" t="n">
         <v>44</v>
       </c>
-      <c r="U6" s="9" t="n">
+      <c r="U6" s="10" t="n">
         <v>109</v>
       </c>
-      <c r="W6" s="9" t="n">
+      <c r="W6" s="10" t="n">
         <v>229</v>
       </c>
-      <c r="Y6" s="9" t="n">
+      <c r="Y6" s="10" t="n">
         <v>220</v>
       </c>
     </row>
@@ -1055,7 +1094,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="9" t="n">
         <v>2705</v>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -1069,46 +1108,46 @@
       <c r="H7" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="I7" s="9" t="n">
+      <c r="I7" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="K7" s="9" t="n">
+      <c r="K7" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="M7" s="9" t="n">
+      <c r="M7" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="U7" s="9" t="n">
+      <c r="U7" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="W7" s="10" t="n">
+      <c r="W7" s="11" t="n">
         <v>-23</v>
       </c>
-      <c r="Y7" s="9" t="n">
+      <c r="Y7" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="AC7" s="10" t="n">
+      <c r="AC7" s="11" t="n">
         <v>-20</v>
       </c>
-      <c r="AF7" s="9" t="n">
+      <c r="AF7" s="10" t="n">
         <v>53</v>
       </c>
-      <c r="AH7" s="9" t="n">
+      <c r="AH7" s="10" t="n">
         <v>71</v>
       </c>
-      <c r="AJ7" s="9" t="n">
+      <c r="AJ7" s="10" t="n">
         <v>56</v>
       </c>
-      <c r="AO7" s="9" t="n">
+      <c r="AO7" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="AR7" s="10" t="n">
+      <c r="AR7" s="11" t="n">
         <v>-52</v>
       </c>
-      <c r="AT7" s="9" t="n">
+      <c r="AT7" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="AV7" s="9" t="n">
+      <c r="AV7" s="10" t="n">
         <v>210</v>
       </c>
     </row>
@@ -1131,7 +1170,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="9" t="n">
         <v>2689</v>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -1145,43 +1184,43 @@
       <c r="H8" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="I8" s="9" t="n">
+      <c r="I8" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="K8" s="10" t="n">
+      <c r="K8" s="11" t="n">
         <v>-17</v>
       </c>
-      <c r="M8" s="9" t="n">
+      <c r="M8" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="U8" s="9" t="n">
+      <c r="U8" s="10" t="n">
         <v>29</v>
       </c>
-      <c r="W8" s="9" t="n">
+      <c r="W8" s="10" t="n">
         <v>55</v>
       </c>
-      <c r="Y8" s="9" t="n">
+      <c r="Y8" s="10" t="n">
         <v>65</v>
       </c>
-      <c r="AC8" s="9" t="n">
+      <c r="AC8" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="AF8" s="9" t="n">
+      <c r="AF8" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="AH8" s="9" t="n">
+      <c r="AH8" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="AJ8" s="9" t="n">
+      <c r="AJ8" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="AR8" s="9" t="n">
+      <c r="AR8" s="10" t="n">
         <v>53</v>
       </c>
-      <c r="AT8" s="9" t="n">
+      <c r="AT8" s="10" t="n">
         <v>94</v>
       </c>
-      <c r="AV8" s="9" t="n">
+      <c r="AV8" s="10" t="n">
         <v>200</v>
       </c>
     </row>
@@ -1204,7 +1243,7 @@
           <t>Francia</t>
         </is>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="E9" s="9" t="n">
         <v>2672</v>
       </c>
       <c r="F9" s="8" t="inlineStr">
@@ -1218,49 +1257,49 @@
       <c r="H9" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="I9" s="10" t="n">
+      <c r="I9" s="11" t="n">
         <v>-15</v>
       </c>
-      <c r="K9" s="9" t="n">
+      <c r="K9" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="M9" s="10" t="n">
+      <c r="M9" s="11" t="n">
         <v>-13</v>
       </c>
-      <c r="N9" s="9" t="n">
+      <c r="N9" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="U9" s="9" t="n">
+      <c r="U9" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="W9" s="9" t="n">
+      <c r="W9" s="10" t="n">
         <v>47</v>
       </c>
-      <c r="Y9" s="9" t="n">
+      <c r="Y9" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="AF9" s="9" t="n">
+      <c r="AF9" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="AH9" s="9" t="n">
+      <c r="AH9" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="AJ9" s="9" t="n">
+      <c r="AJ9" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="AK9" s="9" t="n">
+      <c r="AK9" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="AR9" s="9" t="n">
+      <c r="AR9" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="AT9" s="9" t="n">
+      <c r="AT9" s="10" t="n">
         <v>98</v>
       </c>
-      <c r="AV9" s="9" t="n">
+      <c r="AV9" s="10" t="n">
         <v>194</v>
       </c>
-      <c r="AW9" s="9" t="n">
+      <c r="AW9" s="10" t="n">
         <v>41</v>
       </c>
     </row>
@@ -1283,7 +1322,7 @@
           <t>España</t>
         </is>
       </c>
-      <c r="E10" s="8" t="n">
+      <c r="E10" s="9" t="n">
         <v>2520</v>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -1297,25 +1336,25 @@
       <c r="H10" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="N10" s="10" t="n">
+      <c r="N10" s="11" t="n">
         <v>-5</v>
       </c>
-      <c r="U10" s="10" t="n">
+      <c r="U10" s="11" t="n">
         <v>-2</v>
       </c>
-      <c r="W10" s="9" t="n">
+      <c r="W10" s="10" t="n">
         <v>111</v>
       </c>
-      <c r="Y10" s="9" t="n">
+      <c r="Y10" s="10" t="n">
         <v>206</v>
       </c>
-      <c r="AF10" s="10" t="n">
+      <c r="AF10" s="11" t="n">
         <v>-47</v>
       </c>
-      <c r="AH10" s="9" t="n">
+      <c r="AH10" s="10" t="n">
         <v>123</v>
       </c>
-      <c r="AJ10" s="9" t="n">
+      <c r="AJ10" s="10" t="n">
         <v>58</v>
       </c>
     </row>
@@ -1338,7 +1377,7 @@
           <t>España</t>
         </is>
       </c>
-      <c r="E11" s="8" t="n">
+      <c r="E11" s="9" t="n">
         <v>2489</v>
       </c>
       <c r="F11" s="8" t="inlineStr">
@@ -1352,19 +1391,19 @@
       <c r="H11" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N11" s="9" t="n">
+      <c r="N11" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="U11" s="9" t="n">
+      <c r="U11" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="W11" s="9" t="n">
+      <c r="W11" s="10" t="n">
         <v>114</v>
       </c>
-      <c r="Y11" s="9" t="n">
+      <c r="Y11" s="10" t="n">
         <v>190</v>
       </c>
-      <c r="AK11" s="9" t="n">
+      <c r="AK11" s="10" t="n">
         <v>96</v>
       </c>
     </row>
@@ -1387,7 +1426,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E12" s="8" t="n">
+      <c r="E12" s="9" t="n">
         <v>2486</v>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -1401,25 +1440,25 @@
       <c r="H12" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="U12" s="9" t="n">
+      <c r="U12" s="10" t="n">
         <v>54</v>
       </c>
-      <c r="W12" s="9" t="n">
+      <c r="W12" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Y12" s="9" t="n">
+      <c r="Y12" s="10" t="n">
         <v>97</v>
       </c>
-      <c r="AN12" s="9" t="n">
+      <c r="AN12" s="10" t="n">
         <v>59</v>
       </c>
-      <c r="AR12" s="10" t="n">
+      <c r="AR12" s="11" t="n">
         <v>-81</v>
       </c>
-      <c r="AT12" s="9" t="n">
+      <c r="AT12" s="10" t="n">
         <v>88</v>
       </c>
-      <c r="AV12" s="9" t="n">
+      <c r="AV12" s="10" t="n">
         <v>190</v>
       </c>
     </row>
@@ -1442,7 +1481,7 @@
           <t>España</t>
         </is>
       </c>
-      <c r="E13" s="8" t="n">
+      <c r="E13" s="9" t="n">
         <v>2474</v>
       </c>
       <c r="F13" s="8" t="inlineStr">
@@ -1456,22 +1495,22 @@
       <c r="H13" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="U13" s="10" t="n">
+      <c r="U13" s="11" t="n">
         <v>-69</v>
       </c>
-      <c r="W13" s="9" t="n">
+      <c r="W13" s="10" t="n">
         <v>113</v>
       </c>
-      <c r="Y13" s="9" t="n">
+      <c r="Y13" s="10" t="n">
         <v>273</v>
       </c>
-      <c r="Z13" s="9" t="n">
+      <c r="Z13" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="AK13" s="10" t="n">
+      <c r="AK13" s="11" t="n">
         <v>-3</v>
       </c>
-      <c r="AW13" s="9" t="n">
+      <c r="AW13" s="10" t="n">
         <v>71</v>
       </c>
     </row>
@@ -1494,7 +1533,7 @@
           <t>Costa Rica</t>
         </is>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="E14" s="9" t="n">
         <v>2469</v>
       </c>
       <c r="F14" s="8" t="inlineStr">
@@ -1508,52 +1547,52 @@
       <c r="H14" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="I14" s="9" t="n">
+      <c r="I14" s="10" t="n">
         <v>95</v>
       </c>
-      <c r="K14" s="9" t="n">
+      <c r="K14" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="M14" s="10" t="n">
+      <c r="M14" s="11" t="n">
         <v>-62</v>
       </c>
-      <c r="P14" s="9" t="n">
+      <c r="P14" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="Q14" s="10" t="n">
+      <c r="Q14" s="11" t="n">
         <v>-5</v>
       </c>
-      <c r="S14" s="9" t="n">
+      <c r="S14" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="U14" s="9" t="n">
+      <c r="U14" s="10" t="n">
         <v>361</v>
       </c>
-      <c r="W14" s="10" t="n">
+      <c r="W14" s="11" t="n">
         <v>-74</v>
       </c>
-      <c r="Y14" s="10" t="n">
+      <c r="Y14" s="11" t="n">
         <v>-100</v>
       </c>
-      <c r="AF14" s="9" t="n">
+      <c r="AF14" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="AH14" s="10" t="n">
+      <c r="AH14" s="11" t="n">
         <v>-102</v>
       </c>
-      <c r="AJ14" s="9" t="n">
+      <c r="AJ14" s="10" t="n">
         <v>161</v>
       </c>
-      <c r="AP14" s="9" t="n">
+      <c r="AP14" s="10" t="n">
         <v>57</v>
       </c>
-      <c r="AQ14" s="10" t="n">
+      <c r="AQ14" s="11" t="n">
         <v>-60</v>
       </c>
-      <c r="AX14" s="10" t="n">
+      <c r="AX14" s="11" t="n">
         <v>-16</v>
       </c>
-      <c r="AY14" s="9" t="n">
+      <c r="AY14" s="10" t="n">
         <v>105</v>
       </c>
     </row>
@@ -1576,7 +1615,7 @@
           <t>Panamá</t>
         </is>
       </c>
-      <c r="E15" s="8" t="n">
+      <c r="E15" s="9" t="n">
         <v>2465</v>
       </c>
       <c r="F15" s="8" t="inlineStr">
@@ -1590,28 +1629,28 @@
       <c r="H15" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="U15" s="9" t="n">
+      <c r="U15" s="10" t="n">
         <v>186</v>
       </c>
-      <c r="W15" s="9" t="n">
+      <c r="W15" s="10" t="n">
         <v>170</v>
       </c>
-      <c r="Y15" s="10" t="n">
+      <c r="Y15" s="11" t="n">
         <v>-32</v>
       </c>
-      <c r="AL15" s="9" t="n">
+      <c r="AL15" s="10" t="n">
         <v>75</v>
       </c>
-      <c r="AM15" s="9" t="n">
+      <c r="AM15" s="10" t="n">
         <v>113</v>
       </c>
-      <c r="AR15" s="10" t="n">
+      <c r="AR15" s="11" t="n">
         <v>-173</v>
       </c>
-      <c r="AT15" s="10" t="n">
+      <c r="AT15" s="11" t="n">
         <v>-19</v>
       </c>
-      <c r="AV15" s="9" t="n">
+      <c r="AV15" s="10" t="n">
         <v>70</v>
       </c>
     </row>
@@ -1634,7 +1673,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E16" s="8" t="n">
+      <c r="E16" s="9" t="n">
         <v>2463</v>
       </c>
       <c r="F16" s="8" t="inlineStr">
@@ -1648,37 +1687,37 @@
       <c r="H16" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="I16" s="10" t="n">
+      <c r="I16" s="11" t="n">
         <v>-59</v>
       </c>
-      <c r="K16" s="10" t="n">
+      <c r="K16" s="11" t="n">
         <v>-103</v>
       </c>
-      <c r="M16" s="9" t="n">
+      <c r="M16" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="U16" s="9" t="n">
+      <c r="U16" s="10" t="n">
         <v>96</v>
       </c>
-      <c r="W16" s="9" t="n">
+      <c r="W16" s="10" t="n">
         <v>114</v>
       </c>
-      <c r="Y16" s="9" t="n">
+      <c r="Y16" s="10" t="n">
         <v>192</v>
       </c>
-      <c r="AC16" s="9" t="n">
+      <c r="AC16" s="10" t="n">
         <v>53</v>
       </c>
-      <c r="AO16" s="9" t="n">
+      <c r="AO16" s="10" t="n">
         <v>120</v>
       </c>
-      <c r="AR16" s="10" t="n">
+      <c r="AR16" s="11" t="n">
         <v>-132</v>
       </c>
-      <c r="AT16" s="9" t="n">
+      <c r="AT16" s="10" t="n">
         <v>117</v>
       </c>
-      <c r="AV16" s="10" t="n">
+      <c r="AV16" s="11" t="n">
         <v>-30</v>
       </c>
     </row>
@@ -1701,7 +1740,7 @@
           <t>España</t>
         </is>
       </c>
-      <c r="E17" s="8" t="n">
+      <c r="E17" s="9" t="n">
         <v>2462</v>
       </c>
       <c r="F17" s="8" t="inlineStr">
@@ -1715,22 +1754,22 @@
       <c r="H17" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="I17" s="9" t="n">
+      <c r="I17" s="10" t="n">
         <v>68</v>
       </c>
-      <c r="K17" s="9" t="n">
+      <c r="K17" s="10" t="n">
         <v>75</v>
       </c>
-      <c r="M17" s="9" t="n">
+      <c r="M17" s="10" t="n">
         <v>71</v>
       </c>
-      <c r="U17" s="10" t="n">
+      <c r="U17" s="11" t="n">
         <v>-142</v>
       </c>
-      <c r="W17" s="10" t="n">
+      <c r="W17" s="11" t="n">
         <v>-55</v>
       </c>
-      <c r="Y17" s="9" t="n">
+      <c r="Y17" s="10" t="n">
         <v>370</v>
       </c>
     </row>
@@ -1753,7 +1792,7 @@
           <t>Chile</t>
         </is>
       </c>
-      <c r="E18" s="8" t="n">
+      <c r="E18" s="9" t="n">
         <v>2462</v>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -1767,22 +1806,22 @@
       <c r="H18" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="I18" s="9" t="n">
+      <c r="I18" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="K18" s="9" t="n">
+      <c r="K18" s="10" t="n">
         <v>98</v>
       </c>
-      <c r="M18" s="9" t="n">
+      <c r="M18" s="10" t="n">
         <v>138</v>
       </c>
-      <c r="AR18" s="9" t="n">
+      <c r="AR18" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="AT18" s="9" t="n">
+      <c r="AT18" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="AV18" s="9" t="n">
+      <c r="AV18" s="10" t="n">
         <v>90</v>
       </c>
     </row>
@@ -1805,7 +1844,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E19" s="8" t="n">
+      <c r="E19" s="9" t="n">
         <v>2448</v>
       </c>
       <c r="F19" s="8" t="inlineStr">
@@ -1819,70 +1858,70 @@
       <c r="H19" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="I19" s="9" t="n">
+      <c r="I19" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="K19" s="9" t="n">
+      <c r="K19" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="M19" s="10" t="n">
+      <c r="M19" s="11" t="n">
         <v>-16</v>
       </c>
-      <c r="R19" s="9" t="n">
+      <c r="R19" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="S19" s="9" t="n">
+      <c r="S19" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="T19" s="9" t="n">
+      <c r="T19" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="U19" s="10" t="n">
+      <c r="U19" s="11" t="n">
         <v>-89</v>
       </c>
-      <c r="W19" s="10" t="n">
+      <c r="W19" s="11" t="n">
         <v>-24</v>
       </c>
-      <c r="Y19" s="10" t="n">
+      <c r="Y19" s="11" t="n">
         <v>-29</v>
       </c>
-      <c r="AA19" s="9" t="n">
+      <c r="AA19" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="AC19" s="9" t="n">
+      <c r="AC19" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="AF19" s="9" t="n">
+      <c r="AF19" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="AH19" s="9" t="n">
+      <c r="AH19" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="AJ19" s="10" t="n">
+      <c r="AJ19" s="11" t="n">
         <v>-111</v>
       </c>
-      <c r="AO19" s="9" t="n">
+      <c r="AO19" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="AP19" s="9" t="n">
+      <c r="AP19" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="AQ19" s="10" t="n">
+      <c r="AQ19" s="11" t="n">
         <v>-19</v>
       </c>
-      <c r="AR19" s="9" t="n">
+      <c r="AR19" s="10" t="n">
         <v>73</v>
       </c>
-      <c r="AT19" s="9" t="n">
+      <c r="AT19" s="10" t="n">
         <v>29</v>
       </c>
-      <c r="AV19" s="9" t="n">
+      <c r="AV19" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="AW19" s="9" t="n">
+      <c r="AW19" s="10" t="n">
         <v>52</v>
       </c>
-      <c r="AZ19" s="9" t="n">
+      <c r="AZ19" s="10" t="n">
         <v>45</v>
       </c>
     </row>
@@ -1905,7 +1944,7 @@
           <t>México</t>
         </is>
       </c>
-      <c r="E20" s="8" t="n">
+      <c r="E20" s="9" t="n">
         <v>2431</v>
       </c>
       <c r="F20" s="8" t="inlineStr">
@@ -1919,28 +1958,28 @@
       <c r="H20" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="J20" s="9" t="n">
+      <c r="J20" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="L20" s="9" t="n">
+      <c r="L20" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="U20" s="9" t="n">
+      <c r="U20" s="10" t="n">
         <v>485</v>
       </c>
-      <c r="W20" s="10" t="n">
+      <c r="W20" s="11" t="n">
         <v>-25</v>
       </c>
-      <c r="Y20" s="10" t="n">
+      <c r="Y20" s="11" t="n">
         <v>-20</v>
       </c>
-      <c r="AF20" s="10" t="n">
+      <c r="AF20" s="11" t="n">
         <v>-67</v>
       </c>
-      <c r="AH20" s="10" t="n">
+      <c r="AH20" s="11" t="n">
         <v>-90</v>
       </c>
-      <c r="AJ20" s="9" t="n">
+      <c r="AJ20" s="10" t="n">
         <v>18</v>
       </c>
     </row>
@@ -1963,7 +2002,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E21" s="8" t="n">
+      <c r="E21" s="9" t="n">
         <v>2430</v>
       </c>
       <c r="F21" s="8" t="inlineStr">
@@ -1977,16 +2016,16 @@
       <c r="H21" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="U21" s="9" t="n">
+      <c r="U21" s="10" t="n">
         <v>196</v>
       </c>
-      <c r="W21" s="10" t="n">
+      <c r="W21" s="11" t="n">
         <v>-93</v>
       </c>
-      <c r="Y21" s="9" t="n">
+      <c r="Y21" s="10" t="n">
         <v>105</v>
       </c>
-      <c r="AN21" s="9" t="n">
+      <c r="AN21" s="10" t="n">
         <v>147</v>
       </c>
     </row>
@@ -2009,7 +2048,7 @@
           <t>México</t>
         </is>
       </c>
-      <c r="E22" s="8" t="n">
+      <c r="E22" s="9" t="n">
         <v>2412</v>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -2023,25 +2062,25 @@
       <c r="H22" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="I22" s="9" t="n">
+      <c r="I22" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="K22" s="10" t="n">
+      <c r="K22" s="11" t="n">
         <v>-23</v>
       </c>
-      <c r="M22" s="9" t="n">
+      <c r="M22" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="O22" s="9" t="n">
+      <c r="O22" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="AF22" s="9" t="n">
+      <c r="AF22" s="10" t="n">
         <v>95</v>
       </c>
-      <c r="AH22" s="9" t="n">
+      <c r="AH22" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="AJ22" s="9" t="n">
+      <c r="AJ22" s="10" t="n">
         <v>178</v>
       </c>
     </row>
@@ -2064,7 +2103,7 @@
           <t>México</t>
         </is>
       </c>
-      <c r="E23" s="8" t="n">
+      <c r="E23" s="9" t="n">
         <v>2372</v>
       </c>
       <c r="F23" s="8" t="inlineStr">
@@ -2078,13 +2117,13 @@
       <c r="H23" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="U23" s="9" t="n">
+      <c r="U23" s="10" t="n">
         <v>74</v>
       </c>
-      <c r="W23" s="9" t="n">
+      <c r="W23" s="10" t="n">
         <v>63</v>
       </c>
-      <c r="Y23" s="9" t="n">
+      <c r="Y23" s="10" t="n">
         <v>160</v>
       </c>
     </row>
@@ -2107,7 +2146,7 @@
           <t>España</t>
         </is>
       </c>
-      <c r="E24" s="8" t="n">
+      <c r="E24" s="9" t="n">
         <v>2370</v>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -2121,13 +2160,13 @@
       <c r="H24" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="U24" s="10" t="n">
+      <c r="U24" s="11" t="n">
         <v>-130</v>
       </c>
-      <c r="W24" s="9" t="n">
+      <c r="W24" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="Y24" s="9" t="n">
+      <c r="Y24" s="10" t="n">
         <v>390</v>
       </c>
     </row>
@@ -2150,7 +2189,7 @@
           <t>España</t>
         </is>
       </c>
-      <c r="E25" s="8" t="n">
+      <c r="E25" s="9" t="n">
         <v>2356</v>
       </c>
       <c r="F25" s="8" t="inlineStr">
@@ -2164,46 +2203,46 @@
       <c r="H25" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="I25" s="10" t="n">
+      <c r="I25" s="11" t="n">
         <v>-58</v>
       </c>
-      <c r="K25" s="10" t="n">
+      <c r="K25" s="11" t="n">
         <v>-53</v>
       </c>
-      <c r="M25" s="9" t="n">
+      <c r="M25" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="N25" s="9" t="n">
+      <c r="N25" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="U25" s="9" t="n">
+      <c r="U25" s="10" t="n">
         <v>164</v>
       </c>
-      <c r="W25" s="10" t="n">
+      <c r="W25" s="11" t="n">
         <v>-173</v>
       </c>
-      <c r="Y25" s="9" t="n">
+      <c r="Y25" s="10" t="n">
         <v>141</v>
       </c>
-      <c r="AF25" s="9" t="n">
+      <c r="AF25" s="10" t="n">
         <v>59</v>
       </c>
-      <c r="AH25" s="10" t="n">
+      <c r="AH25" s="11" t="n">
         <v>-127</v>
       </c>
-      <c r="AJ25" s="9" t="n">
+      <c r="AJ25" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="AR25" s="9" t="n">
+      <c r="AR25" s="10" t="n">
         <v>74</v>
       </c>
-      <c r="AT25" s="9" t="n">
+      <c r="AT25" s="10" t="n">
         <v>47</v>
       </c>
-      <c r="AV25" s="9" t="n">
+      <c r="AV25" s="10" t="n">
         <v>140</v>
       </c>
-      <c r="AW25" s="9" t="n">
+      <c r="AW25" s="10" t="n">
         <v>31</v>
       </c>
     </row>
@@ -2226,7 +2265,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E26" s="8" t="n">
+      <c r="E26" s="9" t="n">
         <v>2340</v>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -2240,34 +2279,34 @@
       <c r="H26" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="I26" s="10" t="n">
+      <c r="I26" s="11" t="n">
         <v>-36</v>
       </c>
-      <c r="K26" s="9" t="n">
+      <c r="K26" s="10" t="n">
         <v>116</v>
       </c>
-      <c r="M26" s="9" t="n">
+      <c r="M26" s="10" t="n">
         <v>58</v>
       </c>
-      <c r="AF26" s="10" t="n">
+      <c r="AF26" s="11" t="n">
         <v>-10</v>
       </c>
-      <c r="AH26" s="10" t="n">
+      <c r="AH26" s="11" t="n">
         <v>-31</v>
       </c>
-      <c r="AJ26" s="10" t="n">
+      <c r="AJ26" s="11" t="n">
         <v>-54</v>
       </c>
-      <c r="AR26" s="9" t="n">
+      <c r="AR26" s="10" t="n">
         <v>80</v>
       </c>
-      <c r="AT26" s="9" t="n">
+      <c r="AT26" s="10" t="n">
         <v>93</v>
       </c>
-      <c r="AV26" s="9" t="n">
+      <c r="AV26" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="AW26" s="9" t="n">
+      <c r="AW26" s="10" t="n">
         <v>21</v>
       </c>
     </row>
@@ -2290,7 +2329,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E27" s="8" t="n">
+      <c r="E27" s="9" t="n">
         <v>2324</v>
       </c>
       <c r="F27" s="8" t="inlineStr">
@@ -2304,16 +2343,16 @@
       <c r="H27" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="AC27" s="10" t="n">
+      <c r="AC27" s="11" t="n">
         <v>-25</v>
       </c>
-      <c r="AR27" s="9" t="n">
+      <c r="AR27" s="10" t="n">
         <v>70</v>
       </c>
-      <c r="AT27" s="9" t="n">
+      <c r="AT27" s="10" t="n">
         <v>83</v>
       </c>
-      <c r="AV27" s="9" t="n">
+      <c r="AV27" s="10" t="n">
         <v>120</v>
       </c>
     </row>
@@ -2336,7 +2375,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E28" s="8" t="n">
+      <c r="E28" s="9" t="n">
         <v>2323</v>
       </c>
       <c r="F28" s="8" t="inlineStr">
@@ -2350,16 +2389,16 @@
       <c r="H28" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="U28" s="9" t="n">
+      <c r="U28" s="10" t="n">
         <v>110</v>
       </c>
-      <c r="W28" s="9" t="n">
+      <c r="W28" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="Y28" s="10" t="n">
+      <c r="Y28" s="11" t="n">
         <v>-72</v>
       </c>
-      <c r="AN28" s="9" t="n">
+      <c r="AN28" s="10" t="n">
         <v>167</v>
       </c>
     </row>
@@ -2382,7 +2421,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E29" s="8" t="n">
+      <c r="E29" s="9" t="n">
         <v>2311</v>
       </c>
       <c r="F29" s="8" t="inlineStr">
@@ -2396,16 +2435,16 @@
       <c r="H29" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="U29" s="9" t="n">
+      <c r="U29" s="10" t="n">
         <v>466</v>
       </c>
-      <c r="W29" s="10" t="n">
+      <c r="W29" s="11" t="n">
         <v>-337</v>
       </c>
-      <c r="Y29" s="9" t="n">
+      <c r="Y29" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AN29" s="9" t="n">
+      <c r="AN29" s="10" t="n">
         <v>107</v>
       </c>
     </row>
@@ -2428,7 +2467,7 @@
           <t>Uruguay</t>
         </is>
       </c>
-      <c r="E30" s="8" t="n">
+      <c r="E30" s="9" t="n">
         <v>2310</v>
       </c>
       <c r="F30" s="8" t="inlineStr">
@@ -2442,43 +2481,43 @@
       <c r="H30" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="I30" s="9" t="n">
+      <c r="I30" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="K30" s="9" t="n">
+      <c r="K30" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="M30" s="10" t="n">
+      <c r="M30" s="11" t="n">
         <v>-86</v>
       </c>
-      <c r="U30" s="9" t="n">
+      <c r="U30" s="10" t="n">
         <v>86</v>
       </c>
-      <c r="W30" s="10" t="n">
+      <c r="W30" s="11" t="n">
         <v>-61</v>
       </c>
-      <c r="Y30" s="9" t="n">
+      <c r="Y30" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="AF30" s="10" t="n">
+      <c r="AF30" s="11" t="n">
         <v>-6</v>
       </c>
-      <c r="AH30" s="10" t="n">
+      <c r="AH30" s="11" t="n">
         <v>-57</v>
       </c>
-      <c r="AJ30" s="9" t="n">
+      <c r="AJ30" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="AO30" s="10" t="n">
+      <c r="AO30" s="11" t="n">
         <v>-58</v>
       </c>
-      <c r="AR30" s="9" t="n">
+      <c r="AR30" s="10" t="n">
         <v>134</v>
       </c>
-      <c r="AT30" s="9" t="n">
+      <c r="AT30" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="AV30" s="9" t="n">
+      <c r="AV30" s="10" t="n">
         <v>140</v>
       </c>
     </row>
@@ -2501,7 +2540,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E31" s="8" t="n">
+      <c r="E31" s="9" t="n">
         <v>2309</v>
       </c>
       <c r="F31" s="8" t="inlineStr">
@@ -2515,34 +2554,34 @@
       <c r="H31" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="I31" s="10" t="n">
+      <c r="I31" s="11" t="n">
         <v>-6</v>
       </c>
-      <c r="K31" s="9" t="n">
+      <c r="K31" s="10" t="n">
         <v>72</v>
       </c>
-      <c r="M31" s="9" t="n">
+      <c r="M31" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="U31" s="10" t="n">
+      <c r="U31" s="11" t="n">
         <v>-226</v>
       </c>
-      <c r="W31" s="9" t="n">
+      <c r="W31" s="10" t="n">
         <v>52</v>
       </c>
-      <c r="Y31" s="9" t="n">
+      <c r="Y31" s="10" t="n">
         <v>131</v>
       </c>
-      <c r="AC31" s="9" t="n">
+      <c r="AC31" s="10" t="n">
         <v>64</v>
       </c>
-      <c r="AR31" s="9" t="n">
+      <c r="AR31" s="10" t="n">
         <v>139</v>
       </c>
-      <c r="AT31" s="9" t="n">
+      <c r="AT31" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="AV31" s="10" t="n">
+      <c r="AV31" s="11" t="n">
         <v>-40</v>
       </c>
     </row>
@@ -2565,7 +2604,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E32" s="8" t="n">
+      <c r="E32" s="9" t="n">
         <v>2304</v>
       </c>
       <c r="F32" s="8" t="inlineStr">
@@ -2579,40 +2618,40 @@
       <c r="H32" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="J32" s="9" t="n">
+      <c r="J32" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="L32" s="9" t="n">
+      <c r="L32" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="U32" s="10" t="n">
+      <c r="U32" s="11" t="n">
         <v>-113</v>
       </c>
-      <c r="V32" s="9" t="n">
+      <c r="V32" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="X32" s="9" t="n">
+      <c r="X32" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="AC32" s="10" t="n">
+      <c r="AC32" s="11" t="n">
         <v>-58</v>
       </c>
-      <c r="AF32" s="9" t="n">
+      <c r="AF32" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="AG32" s="9" t="n">
+      <c r="AG32" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="AI32" s="10" t="n">
+      <c r="AI32" s="11" t="n">
         <v>-11</v>
       </c>
-      <c r="AR32" s="9" t="n">
+      <c r="AR32" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="AT32" s="9" t="n">
+      <c r="AT32" s="10" t="n">
         <v>63</v>
       </c>
-      <c r="AV32" s="9" t="n">
+      <c r="AV32" s="10" t="n">
         <v>180</v>
       </c>
     </row>
@@ -2635,7 +2674,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="E33" s="8" t="n">
+      <c r="E33" s="9" t="n">
         <v>2282</v>
       </c>
       <c r="F33" s="8" t="inlineStr">
@@ -2649,34 +2688,34 @@
       <c r="H33" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="AF33" s="9" t="n">
+      <c r="AF33" s="10" t="n">
         <v>135</v>
       </c>
-      <c r="AH33" s="9" t="n">
+      <c r="AH33" s="10" t="n">
         <v>98</v>
       </c>
-      <c r="AJ33" s="10" t="n">
+      <c r="AJ33" s="11" t="n">
         <v>-36</v>
       </c>
-      <c r="AL33" s="9" t="n">
+      <c r="AL33" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="AM33" s="9" t="n">
+      <c r="AM33" s="10" t="n">
         <v>67</v>
       </c>
-      <c r="AR33" s="9" t="n">
+      <c r="AR33" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="AT33" s="10" t="n">
+      <c r="AT33" s="11" t="n">
         <v>-130</v>
       </c>
-      <c r="AV33" s="10" t="n">
+      <c r="AV33" s="11" t="n">
         <v>-32</v>
       </c>
-      <c r="AX33" s="9" t="n">
+      <c r="AX33" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="AY33" s="10" t="n">
+      <c r="AY33" s="11" t="n">
         <v>-15</v>
       </c>
     </row>
@@ -2699,7 +2738,7 @@
           <t>Perú</t>
         </is>
       </c>
-      <c r="E34" s="8" t="n">
+      <c r="E34" s="9" t="n">
         <v>2274</v>
       </c>
       <c r="F34" s="8" t="inlineStr">
@@ -2713,19 +2752,19 @@
       <c r="H34" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="P34" s="10" t="n">
+      <c r="P34" s="11" t="n">
         <v>-24</v>
       </c>
-      <c r="Q34" s="9" t="n">
+      <c r="Q34" s="10" t="n">
         <v>29</v>
       </c>
-      <c r="AF34" s="9" t="n">
+      <c r="AF34" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="AH34" s="9" t="n">
+      <c r="AH34" s="10" t="n">
         <v>73</v>
       </c>
-      <c r="AJ34" s="9" t="n">
+      <c r="AJ34" s="10" t="n">
         <v>108</v>
       </c>
     </row>
@@ -2748,7 +2787,7 @@
           <t>Cuba</t>
         </is>
       </c>
-      <c r="E35" s="8" t="n">
+      <c r="E35" s="9" t="n">
         <v>2269</v>
       </c>
       <c r="F35" s="8" t="inlineStr">
@@ -2762,25 +2801,25 @@
       <c r="H35" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="S35" s="9" t="n">
+      <c r="S35" s="10" t="n">
         <v>58</v>
       </c>
-      <c r="AD35" s="10" t="n">
+      <c r="AD35" s="11" t="n">
         <v>-29</v>
       </c>
-      <c r="AE35" s="10" t="n">
+      <c r="AE35" s="11" t="n">
         <v>-69</v>
       </c>
-      <c r="AP35" s="9" t="n">
+      <c r="AP35" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="AQ35" s="9" t="n">
+      <c r="AQ35" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="BA35" s="9" t="n">
+      <c r="BA35" s="10" t="n">
         <v>66</v>
       </c>
-      <c r="BB35" s="9" t="n">
+      <c r="BB35" s="10" t="n">
         <v>75</v>
       </c>
     </row>
@@ -2803,7 +2842,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E36" s="8" t="n">
+      <c r="E36" s="9" t="n">
         <v>2262</v>
       </c>
       <c r="F36" s="8" t="inlineStr">
@@ -2817,49 +2856,49 @@
       <c r="H36" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="I36" s="9" t="n">
+      <c r="I36" s="10" t="n">
         <v>51</v>
       </c>
-      <c r="K36" s="10" t="n">
+      <c r="K36" s="11" t="n">
         <v>-195</v>
       </c>
-      <c r="M36" s="10" t="n">
+      <c r="M36" s="11" t="n">
         <v>-8</v>
       </c>
-      <c r="R36" s="9" t="n">
+      <c r="R36" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="U36" s="10" t="n">
+      <c r="U36" s="11" t="n">
         <v>-73</v>
       </c>
-      <c r="W36" s="9" t="n">
+      <c r="W36" s="10" t="n">
         <v>104</v>
       </c>
-      <c r="Y36" s="9" t="n">
+      <c r="Y36" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="AC36" s="10" t="n">
+      <c r="AC36" s="11" t="n">
         <v>-17</v>
       </c>
-      <c r="AF36" s="9" t="n">
+      <c r="AF36" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="AH36" s="9" t="n">
+      <c r="AH36" s="10" t="n">
         <v>77</v>
       </c>
-      <c r="AJ36" s="10" t="n">
+      <c r="AJ36" s="11" t="n">
         <v>-9</v>
       </c>
-      <c r="AO36" s="9" t="n">
+      <c r="AO36" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="AR36" s="9" t="n">
+      <c r="AR36" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="AT36" s="9" t="n">
+      <c r="AT36" s="10" t="n">
         <v>204</v>
       </c>
-      <c r="AV36" s="10" t="n">
+      <c r="AV36" s="11" t="n">
         <v>-60</v>
       </c>
     </row>
@@ -2882,7 +2921,7 @@
           <t>Estados Unidos</t>
         </is>
       </c>
-      <c r="E37" s="8" t="n">
+      <c r="E37" s="9" t="n">
         <v>2257</v>
       </c>
       <c r="F37" s="8" t="inlineStr">
@@ -2896,64 +2935,64 @@
       <c r="H37" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="J37" s="9" t="n">
+      <c r="J37" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="L37" s="10" t="n">
+      <c r="L37" s="11" t="n">
         <v>-80</v>
       </c>
-      <c r="O37" s="10" t="n">
+      <c r="O37" s="11" t="n">
         <v>-5</v>
       </c>
-      <c r="P37" s="9" t="n">
+      <c r="P37" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="Q37" s="10" t="n">
+      <c r="Q37" s="11" t="n">
         <v>-29</v>
       </c>
-      <c r="U37" s="9" t="n">
+      <c r="U37" s="10" t="n">
         <v>150</v>
       </c>
-      <c r="W37" s="9" t="n">
+      <c r="W37" s="10" t="n">
         <v>142</v>
       </c>
-      <c r="Y37" s="10" t="n">
+      <c r="Y37" s="11" t="n">
         <v>-32</v>
       </c>
-      <c r="AA37" s="9" t="n">
+      <c r="AA37" s="10" t="n">
         <v>64</v>
       </c>
-      <c r="AF37" s="10" t="n">
+      <c r="AF37" s="11" t="n">
         <v>-76</v>
       </c>
-      <c r="AH37" s="9" t="n">
+      <c r="AH37" s="10" t="n">
         <v>29</v>
       </c>
-      <c r="AJ37" s="10" t="n">
+      <c r="AJ37" s="11" t="n">
         <v>-17</v>
       </c>
-      <c r="AL37" s="10" t="n">
+      <c r="AL37" s="11" t="n">
         <v>-91</v>
       </c>
-      <c r="AM37" s="9" t="n">
+      <c r="AM37" s="10" t="n">
         <v>117</v>
       </c>
-      <c r="AN37" s="9" t="n">
+      <c r="AN37" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="AR37" s="10" t="n">
+      <c r="AR37" s="11" t="n">
         <v>-26</v>
       </c>
-      <c r="AT37" s="10" t="n">
+      <c r="AT37" s="11" t="n">
         <v>-217</v>
       </c>
-      <c r="AV37" s="9" t="n">
+      <c r="AV37" s="10" t="n">
         <v>52</v>
       </c>
-      <c r="AX37" s="9" t="n">
+      <c r="AX37" s="10" t="n">
         <v>53</v>
       </c>
-      <c r="AY37" s="9" t="n">
+      <c r="AY37" s="10" t="n">
         <v>75</v>
       </c>
     </row>
@@ -2976,7 +3015,7 @@
           <t>España</t>
         </is>
       </c>
-      <c r="E38" s="8" t="n">
+      <c r="E38" s="9" t="n">
         <v>2252</v>
       </c>
       <c r="F38" s="8" t="inlineStr">
@@ -2990,16 +3029,16 @@
       <c r="H38" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="U38" s="10" t="n">
+      <c r="U38" s="11" t="n">
         <v>-74</v>
       </c>
-      <c r="W38" s="9" t="n">
+      <c r="W38" s="10" t="n">
         <v>97</v>
       </c>
-      <c r="Y38" s="9" t="n">
+      <c r="Y38" s="10" t="n">
         <v>88</v>
       </c>
-      <c r="AK38" s="9" t="n">
+      <c r="AK38" s="10" t="n">
         <v>66</v>
       </c>
     </row>
@@ -3022,7 +3061,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E39" s="8" t="n">
+      <c r="E39" s="9" t="n">
         <v>2252</v>
       </c>
       <c r="F39" s="8" t="inlineStr">
@@ -3036,7 +3075,7 @@
       <c r="H39" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AN39" s="9" t="n">
+      <c r="AN39" s="10" t="n">
         <v>177</v>
       </c>
     </row>
@@ -3059,7 +3098,7 @@
           <t>Cuba</t>
         </is>
       </c>
-      <c r="E40" s="8" t="n">
+      <c r="E40" s="9" t="n">
         <v>2247</v>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -3073,19 +3112,19 @@
       <c r="H40" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="T40" s="9" t="n">
+      <c r="T40" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="AD40" s="9" t="n">
+      <c r="AD40" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="AE40" s="9" t="n">
+      <c r="AE40" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="BA40" s="9" t="n">
+      <c r="BA40" s="10" t="n">
         <v>69</v>
       </c>
-      <c r="BB40" s="9" t="n">
+      <c r="BB40" s="10" t="n">
         <v>25</v>
       </c>
     </row>
@@ -3108,7 +3147,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E41" s="8" t="n">
+      <c r="E41" s="9" t="n">
         <v>2246</v>
       </c>
       <c r="F41" s="8" t="inlineStr">
@@ -3122,22 +3161,22 @@
       <c r="H41" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="U41" s="9" t="n">
+      <c r="U41" s="10" t="n">
         <v>87</v>
       </c>
-      <c r="W41" s="10" t="n">
+      <c r="W41" s="11" t="n">
         <v>-120</v>
       </c>
-      <c r="Y41" s="10" t="n">
+      <c r="Y41" s="11" t="n">
         <v>-15</v>
       </c>
-      <c r="AL41" s="9" t="n">
+      <c r="AL41" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="AM41" s="10" t="n">
+      <c r="AM41" s="11" t="n">
         <v>-5</v>
       </c>
-      <c r="AN41" s="9" t="n">
+      <c r="AN41" s="10" t="n">
         <v>187</v>
       </c>
     </row>
@@ -3160,7 +3199,7 @@
           <t>Cuba</t>
         </is>
       </c>
-      <c r="E42" s="8" t="n">
+      <c r="E42" s="9" t="n">
         <v>2246</v>
       </c>
       <c r="F42" s="8" t="inlineStr">
@@ -3174,40 +3213,40 @@
       <c r="H42" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="J42" s="9" t="n">
+      <c r="J42" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="L42" s="9" t="n">
+      <c r="L42" s="10" t="n">
         <v>67</v>
       </c>
-      <c r="S42" s="9" t="n">
+      <c r="S42" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="U42" s="9" t="n">
+      <c r="U42" s="10" t="n">
         <v>131</v>
       </c>
-      <c r="W42" s="9" t="n">
+      <c r="W42" s="10" t="n">
         <v>61</v>
       </c>
-      <c r="Y42" s="10" t="n">
+      <c r="Y42" s="11" t="n">
         <v>-302</v>
       </c>
-      <c r="AD42" s="9" t="n">
+      <c r="AD42" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="AE42" s="9" t="n">
+      <c r="AE42" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="AP42" s="9" t="n">
+      <c r="AP42" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="AQ42" s="9" t="n">
+      <c r="AQ42" s="10" t="n">
         <v>52</v>
       </c>
-      <c r="BA42" s="9" t="n">
+      <c r="BA42" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="BB42" s="9" t="n">
+      <c r="BB42" s="10" t="n">
         <v>45</v>
       </c>
     </row>
@@ -3230,7 +3269,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E43" s="8" t="n">
+      <c r="E43" s="9" t="n">
         <v>2239</v>
       </c>
       <c r="F43" s="8" t="inlineStr">
@@ -3244,19 +3283,19 @@
       <c r="H43" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="U43" s="9" t="n">
+      <c r="U43" s="10" t="n">
         <v>138</v>
       </c>
-      <c r="W43" s="9" t="n">
+      <c r="W43" s="10" t="n">
         <v>120</v>
       </c>
-      <c r="Y43" s="10" t="n">
+      <c r="Y43" s="11" t="n">
         <v>-187</v>
       </c>
-      <c r="AC43" s="9" t="n">
+      <c r="AC43" s="10" t="n">
         <v>102</v>
       </c>
-      <c r="AW43" s="10" t="n">
+      <c r="AW43" s="11" t="n">
         <v>-9</v>
       </c>
     </row>
@@ -3279,7 +3318,7 @@
           <t>Cuba</t>
         </is>
       </c>
-      <c r="E44" s="8" t="n">
+      <c r="E44" s="9" t="n">
         <v>2237</v>
       </c>
       <c r="F44" s="8" t="inlineStr">
@@ -3293,19 +3332,19 @@
       <c r="H44" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="S44" s="9" t="n">
+      <c r="S44" s="10" t="n">
         <v>29</v>
       </c>
-      <c r="AP44" s="9" t="n">
+      <c r="AP44" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="AQ44" s="9" t="n">
+      <c r="AQ44" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="BA44" s="9" t="n">
+      <c r="BA44" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="BB44" s="9" t="n">
+      <c r="BB44" s="10" t="n">
         <v>35</v>
       </c>
     </row>
@@ -3328,7 +3367,7 @@
           <t>España</t>
         </is>
       </c>
-      <c r="E45" s="8" t="n">
+      <c r="E45" s="9" t="n">
         <v>2230</v>
       </c>
       <c r="F45" s="8" t="inlineStr">
@@ -3342,34 +3381,34 @@
       <c r="H45" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="I45" s="9" t="n">
+      <c r="I45" s="10" t="n">
         <v>114</v>
       </c>
-      <c r="K45" s="9" t="n">
+      <c r="K45" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="M45" s="9" t="n">
+      <c r="M45" s="10" t="n">
         <v>101</v>
       </c>
-      <c r="N45" s="9" t="n">
+      <c r="N45" s="10" t="n">
         <v>70</v>
       </c>
-      <c r="U45" s="10" t="n">
+      <c r="U45" s="11" t="n">
         <v>-78</v>
       </c>
-      <c r="W45" s="10" t="n">
+      <c r="W45" s="11" t="n">
         <v>-186</v>
       </c>
-      <c r="Y45" s="9" t="n">
+      <c r="Y45" s="10" t="n">
         <v>137</v>
       </c>
-      <c r="Z45" s="10" t="n">
+      <c r="Z45" s="11" t="n">
         <v>-12</v>
       </c>
-      <c r="AK45" s="10" t="n">
+      <c r="AK45" s="11" t="n">
         <v>-57</v>
       </c>
-      <c r="AW45" s="9" t="n">
+      <c r="AW45" s="10" t="n">
         <v>51</v>
       </c>
     </row>
@@ -3392,7 +3431,7 @@
           <t>España</t>
         </is>
       </c>
-      <c r="E46" s="8" t="n">
+      <c r="E46" s="9" t="n">
         <v>2230</v>
       </c>
       <c r="F46" s="8" t="inlineStr">
@@ -3406,37 +3445,37 @@
       <c r="H46" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="N46" s="9" t="n">
+      <c r="N46" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="U46" s="10" t="n">
+      <c r="U46" s="11" t="n">
         <v>-101</v>
       </c>
-      <c r="W46" s="10" t="n">
+      <c r="W46" s="11" t="n">
         <v>-55</v>
       </c>
-      <c r="Y46" s="9" t="n">
+      <c r="Y46" s="10" t="n">
         <v>142</v>
       </c>
-      <c r="AF46" s="9" t="n">
+      <c r="AF46" s="10" t="n">
         <v>88</v>
       </c>
-      <c r="AH46" s="10" t="n">
+      <c r="AH46" s="11" t="n">
         <v>-100</v>
       </c>
-      <c r="AJ46" s="10" t="n">
+      <c r="AJ46" s="11" t="n">
         <v>-20</v>
       </c>
-      <c r="AK46" s="9" t="n">
+      <c r="AK46" s="10" t="n">
         <v>47</v>
       </c>
-      <c r="AR46" s="9" t="n">
+      <c r="AR46" s="10" t="n">
         <v>52</v>
       </c>
-      <c r="AT46" s="9" t="n">
+      <c r="AT46" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="AV46" s="10" t="n">
+      <c r="AV46" s="11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3459,7 +3498,7 @@
           <t>España</t>
         </is>
       </c>
-      <c r="E47" s="8" t="n">
+      <c r="E47" s="9" t="n">
         <v>2219</v>
       </c>
       <c r="F47" s="8" t="inlineStr">
@@ -3473,19 +3512,19 @@
       <c r="H47" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N47" s="10" t="n">
+      <c r="N47" s="11" t="n">
         <v>-6</v>
       </c>
-      <c r="U47" s="10" t="n">
+      <c r="U47" s="11" t="n">
         <v>-226</v>
       </c>
-      <c r="W47" s="9" t="n">
+      <c r="W47" s="10" t="n">
         <v>73</v>
       </c>
-      <c r="Y47" s="9" t="n">
+      <c r="Y47" s="10" t="n">
         <v>248</v>
       </c>
-      <c r="AK47" s="9" t="n">
+      <c r="AK47" s="10" t="n">
         <v>56</v>
       </c>
     </row>
@@ -3508,7 +3547,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E48" s="8" t="n">
+      <c r="E48" s="9" t="n">
         <v>2218</v>
       </c>
       <c r="F48" s="8" t="inlineStr">
@@ -3522,19 +3561,19 @@
       <c r="H48" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="J48" s="9" t="n">
+      <c r="J48" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="L48" s="10" t="n">
+      <c r="L48" s="11" t="n">
         <v>-23</v>
       </c>
-      <c r="AF48" s="9" t="n">
+      <c r="AF48" s="10" t="n">
         <v>74</v>
       </c>
-      <c r="AG48" s="9" t="n">
+      <c r="AG48" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="AI48" s="9" t="n">
+      <c r="AI48" s="10" t="n">
         <v>23</v>
       </c>
     </row>
@@ -3557,7 +3596,7 @@
           <t>España</t>
         </is>
       </c>
-      <c r="E49" s="8" t="n">
+      <c r="E49" s="9" t="n">
         <v>2217</v>
       </c>
       <c r="F49" s="8" t="inlineStr">
@@ -3571,19 +3610,19 @@
       <c r="H49" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N49" s="9" t="n">
+      <c r="N49" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="U49" s="10" t="n">
+      <c r="U49" s="11" t="n">
         <v>-123</v>
       </c>
-      <c r="W49" s="10" t="n">
+      <c r="W49" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Y49" s="9" t="n">
+      <c r="Y49" s="10" t="n">
         <v>187</v>
       </c>
-      <c r="AK49" s="9" t="n">
+      <c r="AK49" s="10" t="n">
         <v>46</v>
       </c>
     </row>
@@ -3606,7 +3645,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="E50" s="8" t="n">
+      <c r="E50" s="9" t="n">
         <v>2217</v>
       </c>
       <c r="F50" s="8" t="inlineStr">
@@ -3620,22 +3659,22 @@
       <c r="H50" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="I50" s="9" t="n">
+      <c r="I50" s="10" t="n">
         <v>136</v>
       </c>
-      <c r="K50" s="9" t="n">
+      <c r="K50" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="M50" s="9" t="n">
+      <c r="M50" s="10" t="n">
         <v>104</v>
       </c>
-      <c r="U50" s="10" t="n">
+      <c r="U50" s="11" t="n">
         <v>-136</v>
       </c>
-      <c r="W50" s="10" t="n">
+      <c r="W50" s="11" t="n">
         <v>-152</v>
       </c>
-      <c r="Y50" s="9" t="n">
+      <c r="Y50" s="10" t="n">
         <v>140</v>
       </c>
     </row>
@@ -3658,7 +3697,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="E51" s="8" t="n">
+      <c r="E51" s="9" t="n">
         <v>2216</v>
       </c>
       <c r="F51" s="8" t="inlineStr">
@@ -3672,16 +3711,16 @@
       <c r="H51" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="AL51" s="9" t="n">
+      <c r="AL51" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="AM51" s="10" t="n">
+      <c r="AM51" s="11" t="n">
         <v>-35</v>
       </c>
-      <c r="AX51" s="9" t="n">
+      <c r="AX51" s="10" t="n">
         <v>85</v>
       </c>
-      <c r="AY51" s="9" t="n">
+      <c r="AY51" s="10" t="n">
         <v>65</v>
       </c>
     </row>
@@ -3704,7 +3743,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E52" s="8" t="n">
+      <c r="E52" s="9" t="n">
         <v>2215</v>
       </c>
       <c r="F52" s="8" t="inlineStr">
@@ -3718,22 +3757,22 @@
       <c r="H52" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="R52" s="10" t="n">
+      <c r="R52" s="11" t="n">
         <v>-4</v>
       </c>
-      <c r="AC52" s="10" t="n">
+      <c r="AC52" s="11" t="n">
         <v>-18</v>
       </c>
-      <c r="AO52" s="10" t="n">
+      <c r="AO52" s="11" t="n">
         <v>-28</v>
       </c>
-      <c r="AR52" s="9" t="n">
+      <c r="AR52" s="10" t="n">
         <v>72</v>
       </c>
-      <c r="AT52" s="10" t="n">
+      <c r="AT52" s="11" t="n">
         <v>-52</v>
       </c>
-      <c r="AV52" s="9" t="n">
+      <c r="AV52" s="10" t="n">
         <v>170</v>
       </c>
     </row>
@@ -3756,7 +3795,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="E53" s="8" t="n">
+      <c r="E53" s="9" t="n">
         <v>2212</v>
       </c>
       <c r="F53" s="8" t="inlineStr">
@@ -3770,19 +3809,19 @@
       <c r="H53" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="AL53" s="9" t="n">
+      <c r="AL53" s="10" t="n">
         <v>85</v>
       </c>
-      <c r="AM53" s="10" t="n">
+      <c r="AM53" s="11" t="n">
         <v>-22</v>
       </c>
-      <c r="AW53" s="10" t="n">
+      <c r="AW53" s="11" t="n">
         <v>-42</v>
       </c>
-      <c r="AX53" s="9" t="n">
+      <c r="AX53" s="10" t="n">
         <v>71</v>
       </c>
-      <c r="AY53" s="9" t="n">
+      <c r="AY53" s="10" t="n">
         <v>45</v>
       </c>
     </row>
@@ -3805,7 +3844,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E54" s="8" t="n">
+      <c r="E54" s="9" t="n">
         <v>2207</v>
       </c>
       <c r="F54" s="8" t="inlineStr">
@@ -3819,10 +3858,10 @@
       <c r="H54" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="R54" s="9" t="n">
+      <c r="R54" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="AC54" s="9" t="n">
+      <c r="AC54" s="10" t="n">
         <v>110</v>
       </c>
     </row>
@@ -3845,7 +3884,7 @@
           <t>España</t>
         </is>
       </c>
-      <c r="E55" s="8" t="n">
+      <c r="E55" s="9" t="n">
         <v>2202</v>
       </c>
       <c r="F55" s="8" t="inlineStr">
@@ -3859,16 +3898,16 @@
       <c r="H55" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="N55" s="10" t="n">
+      <c r="N55" s="11" t="n">
         <v>-40</v>
       </c>
-      <c r="U55" s="9" t="n">
+      <c r="U55" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="W55" s="9" t="n">
+      <c r="W55" s="10" t="n">
         <v>175</v>
       </c>
-      <c r="Y55" s="10" t="n">
+      <c r="Y55" s="11" t="n">
         <v>-10</v>
       </c>
     </row>
@@ -3891,7 +3930,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E56" s="8" t="n">
+      <c r="E56" s="9" t="n">
         <v>2201</v>
       </c>
       <c r="F56" s="8" t="inlineStr">
@@ -3905,25 +3944,25 @@
       <c r="H56" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="I56" s="10" t="n">
+      <c r="I56" s="11" t="n">
         <v>-101</v>
       </c>
-      <c r="K56" s="9" t="n">
+      <c r="K56" s="10" t="n">
         <v>112</v>
       </c>
-      <c r="M56" s="10" t="n">
+      <c r="M56" s="11" t="n">
         <v>-28</v>
       </c>
-      <c r="AC56" s="10" t="n">
+      <c r="AC56" s="11" t="n">
         <v>-58</v>
       </c>
-      <c r="AR56" s="9" t="n">
+      <c r="AR56" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="AT56" s="9" t="n">
+      <c r="AT56" s="10" t="n">
         <v>48</v>
       </c>
-      <c r="AV56" s="9" t="n">
+      <c r="AV56" s="10" t="n">
         <v>150</v>
       </c>
     </row>
@@ -3946,7 +3985,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E57" s="8" t="n">
+      <c r="E57" s="9" t="n">
         <v>2200</v>
       </c>
       <c r="F57" s="8" t="inlineStr">
@@ -3960,37 +3999,37 @@
       <c r="H57" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="U57" s="9" t="n">
+      <c r="U57" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="V57" s="10" t="n">
+      <c r="V57" s="11" t="n">
         <v>-38</v>
       </c>
-      <c r="X57" s="10" t="n">
+      <c r="X57" s="11" t="n">
         <v>-47</v>
       </c>
-      <c r="AF57" s="10" t="n">
+      <c r="AF57" s="11" t="n">
         <v>-21</v>
       </c>
-      <c r="AH57" s="9" t="n">
+      <c r="AH57" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="AJ57" s="10" t="n">
+      <c r="AJ57" s="11" t="n">
         <v>-30</v>
       </c>
-      <c r="AN57" s="9" t="n">
+      <c r="AN57" s="10" t="n">
         <v>116</v>
       </c>
-      <c r="AO57" s="10" t="n">
+      <c r="AO57" s="11" t="n">
         <v>-35</v>
       </c>
-      <c r="AR57" s="9" t="n">
+      <c r="AR57" s="10" t="n">
         <v>74</v>
       </c>
-      <c r="AT57" s="9" t="n">
+      <c r="AT57" s="10" t="n">
         <v>132</v>
       </c>
-      <c r="AV57" s="10" t="n">
+      <c r="AV57" s="11" t="n">
         <v>-150</v>
       </c>
     </row>
@@ -4013,7 +4052,7 @@
           <t>Cuba</t>
         </is>
       </c>
-      <c r="E58" s="8" t="n">
+      <c r="E58" s="9" t="n">
         <v>2198</v>
       </c>
       <c r="F58" s="8" t="inlineStr">
@@ -4027,22 +4066,22 @@
       <c r="H58" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="S58" s="9" t="n">
+      <c r="S58" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="T58" s="9" t="n">
+      <c r="T58" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="AP58" s="9" t="n">
+      <c r="AP58" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="AQ58" s="10" t="n">
+      <c r="AQ58" s="11" t="n">
         <v>-25</v>
       </c>
-      <c r="BA58" s="9" t="n">
+      <c r="BA58" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="BB58" s="9" t="n">
+      <c r="BB58" s="10" t="n">
         <v>65</v>
       </c>
     </row>
@@ -4065,7 +4104,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="E59" s="8" t="n">
+      <c r="E59" s="9" t="n">
         <v>2198</v>
       </c>
       <c r="F59" s="8" t="inlineStr">
@@ -4079,58 +4118,58 @@
       <c r="H59" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="I59" s="9" t="n">
+      <c r="I59" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="K59" s="10" t="n">
+      <c r="K59" s="11" t="n">
         <v>-45</v>
       </c>
-      <c r="M59" s="9" t="n">
+      <c r="M59" s="10" t="n">
         <v>168</v>
       </c>
-      <c r="P59" s="10" t="n">
+      <c r="P59" s="11" t="n">
         <v>-10</v>
       </c>
-      <c r="Q59" s="9" t="n">
+      <c r="Q59" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="U59" s="10" t="n">
+      <c r="U59" s="11" t="n">
         <v>-122</v>
       </c>
-      <c r="W59" s="9" t="n">
+      <c r="W59" s="10" t="n">
         <v>221</v>
       </c>
-      <c r="Y59" s="10" t="n">
+      <c r="Y59" s="11" t="n">
         <v>-132</v>
       </c>
-      <c r="AF59" s="10" t="n">
+      <c r="AF59" s="11" t="n">
         <v>-108</v>
       </c>
-      <c r="AH59" s="9" t="n">
+      <c r="AH59" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="AJ59" s="9" t="n">
+      <c r="AJ59" s="10" t="n">
         <v>58</v>
       </c>
-      <c r="AL59" s="9" t="n">
+      <c r="AL59" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="AM59" s="9" t="n">
+      <c r="AM59" s="10" t="n">
         <v>111</v>
       </c>
-      <c r="AR59" s="9" t="n">
+      <c r="AR59" s="10" t="n">
         <v>72</v>
       </c>
-      <c r="AT59" s="9" t="n">
+      <c r="AT59" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="AV59" s="10" t="n">
+      <c r="AV59" s="11" t="n">
         <v>-142</v>
       </c>
-      <c r="AX59" s="9" t="n">
+      <c r="AX59" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="AY59" s="10" t="n">
+      <c r="AY59" s="11" t="n">
         <v>-35</v>
       </c>
     </row>
@@ -4153,7 +4192,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E60" s="8" t="n">
+      <c r="E60" s="9" t="n">
         <v>2194</v>
       </c>
       <c r="F60" s="8" t="inlineStr">
@@ -4167,46 +4206,46 @@
       <c r="H60" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="I60" s="10" t="n">
+      <c r="I60" s="11" t="n">
         <v>-52</v>
       </c>
-      <c r="K60" s="10" t="n">
+      <c r="K60" s="11" t="n">
         <v>-152</v>
       </c>
-      <c r="M60" s="9" t="n">
+      <c r="M60" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="U60" s="9" t="n">
+      <c r="U60" s="10" t="n">
         <v>104</v>
       </c>
-      <c r="W60" s="10" t="n">
+      <c r="W60" s="11" t="n">
         <v>-6</v>
       </c>
-      <c r="Y60" s="9" t="n">
+      <c r="Y60" s="10" t="n">
         <v>176</v>
       </c>
-      <c r="AC60" s="10" t="n">
+      <c r="AC60" s="11" t="n">
         <v>-50</v>
       </c>
-      <c r="AF60" s="10" t="n">
+      <c r="AF60" s="11" t="n">
         <v>-206</v>
       </c>
-      <c r="AH60" s="10" t="n">
+      <c r="AH60" s="11" t="n">
         <v>-68</v>
       </c>
-      <c r="AJ60" s="9" t="n">
+      <c r="AJ60" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="AO60" s="9" t="n">
+      <c r="AO60" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="AR60" s="9" t="n">
+      <c r="AR60" s="10" t="n">
         <v>111</v>
       </c>
-      <c r="AT60" s="9" t="n">
+      <c r="AT60" s="10" t="n">
         <v>124</v>
       </c>
-      <c r="AV60" s="9" t="n">
+      <c r="AV60" s="10" t="n">
         <v>100</v>
       </c>
     </row>
@@ -4229,7 +4268,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="E61" s="8" t="n">
+      <c r="E61" s="9" t="n">
         <v>2192</v>
       </c>
       <c r="F61" s="8" t="inlineStr">
@@ -4243,7 +4282,7 @@
       <c r="H61" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AN61" s="9" t="n">
+      <c r="AN61" s="10" t="n">
         <v>117</v>
       </c>
     </row>
@@ -4266,7 +4305,7 @@
           <t>Cuba</t>
         </is>
       </c>
-      <c r="E62" s="8" t="n">
+      <c r="E62" s="9" t="n">
         <v>2188</v>
       </c>
       <c r="F62" s="8" t="inlineStr">
@@ -4280,28 +4319,28 @@
       <c r="H62" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="S62" s="9" t="n">
+      <c r="S62" s="10" t="n">
         <v>29</v>
       </c>
-      <c r="T62" s="10" t="n">
+      <c r="T62" s="11" t="n">
         <v>-11</v>
       </c>
-      <c r="AD62" s="9" t="n">
+      <c r="AD62" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="AE62" s="10" t="n">
+      <c r="AE62" s="11" t="n">
         <v>-7</v>
       </c>
-      <c r="AP62" s="9" t="n">
+      <c r="AP62" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="AQ62" s="9" t="n">
+      <c r="AQ62" s="10" t="n">
         <v>55</v>
       </c>
-      <c r="BA62" s="10" t="n">
+      <c r="BA62" s="11" t="n">
         <v>-39</v>
       </c>
-      <c r="BB62" s="9" t="n">
+      <c r="BB62" s="10" t="n">
         <v>55</v>
       </c>
     </row>
@@ -4324,7 +4363,7 @@
           <t>Chile</t>
         </is>
       </c>
-      <c r="E63" s="8" t="n">
+      <c r="E63" s="9" t="n">
         <v>2185</v>
       </c>
       <c r="F63" s="8" t="inlineStr">
@@ -4338,49 +4377,49 @@
       <c r="H63" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="K63" s="9" t="n">
+      <c r="K63" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="M63" s="10" t="n">
+      <c r="M63" s="11" t="n">
         <v>-108</v>
       </c>
-      <c r="P63" s="10" t="n">
+      <c r="P63" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="Q63" s="9" t="n">
+      <c r="Q63" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="U63" s="10" t="n">
+      <c r="U63" s="11" t="n">
         <v>-99</v>
       </c>
-      <c r="W63" s="9" t="n">
+      <c r="W63" s="10" t="n">
         <v>240</v>
       </c>
-      <c r="Y63" s="10" t="n">
+      <c r="Y63" s="11" t="n">
         <v>-131</v>
       </c>
-      <c r="AC63" s="10" t="n">
+      <c r="AC63" s="11" t="n">
         <v>-104</v>
       </c>
-      <c r="AF63" s="9" t="n">
+      <c r="AF63" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="AH63" s="9" t="n">
+      <c r="AH63" s="10" t="n">
         <v>79</v>
       </c>
-      <c r="AJ63" s="9" t="n">
+      <c r="AJ63" s="10" t="n">
         <v>136</v>
       </c>
-      <c r="AO63" s="9" t="n">
+      <c r="AO63" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="AR63" s="10" t="n">
+      <c r="AR63" s="11" t="n">
         <v>-70</v>
       </c>
-      <c r="AT63" s="9" t="n">
+      <c r="AT63" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="AV63" s="10" t="n">
+      <c r="AV63" s="11" t="n">
         <v>-10</v>
       </c>
     </row>
@@ -4403,7 +4442,7 @@
           <t>Rep. Dominicana</t>
         </is>
       </c>
-      <c r="E64" s="8" t="n">
+      <c r="E64" s="9" t="n">
         <v>2182</v>
       </c>
       <c r="F64" s="8" t="inlineStr">
@@ -4417,10 +4456,10 @@
       <c r="H64" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="AL64" s="9" t="n">
+      <c r="AL64" s="10" t="n">
         <v>115</v>
       </c>
-      <c r="AM64" s="10" t="n">
+      <c r="AM64" s="11" t="n">
         <v>-8</v>
       </c>
     </row>
@@ -4443,7 +4482,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="E65" s="8" t="n">
+      <c r="E65" s="9" t="n">
         <v>2176</v>
       </c>
       <c r="F65" s="8" t="inlineStr">
@@ -4457,13 +4496,13 @@
       <c r="H65" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="AA65" s="10" t="n">
+      <c r="AA65" s="11" t="n">
         <v>-31</v>
       </c>
-      <c r="AX65" s="9" t="n">
+      <c r="AX65" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="AY65" s="9" t="n">
+      <c r="AY65" s="10" t="n">
         <v>95</v>
       </c>
     </row>
@@ -4486,7 +4525,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E66" s="8" t="n">
+      <c r="E66" s="9" t="n">
         <v>2172</v>
       </c>
       <c r="F66" s="8" t="inlineStr">
@@ -4500,7 +4539,7 @@
       <c r="H66" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AN66" s="9" t="n">
+      <c r="AN66" s="10" t="n">
         <v>97</v>
       </c>
     </row>
@@ -4523,7 +4562,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E67" s="8" t="n">
+      <c r="E67" s="9" t="n">
         <v>2164</v>
       </c>
       <c r="F67" s="8" t="inlineStr">
@@ -4537,10 +4576,10 @@
       <c r="H67" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="BA67" s="9" t="n">
+      <c r="BA67" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="BB67" s="9" t="n">
+      <c r="BB67" s="10" t="n">
         <v>85</v>
       </c>
     </row>
@@ -4563,7 +4602,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E68" s="8" t="n">
+      <c r="E68" s="9" t="n">
         <v>2162</v>
       </c>
       <c r="F68" s="8" t="inlineStr">
@@ -4577,7 +4616,7 @@
       <c r="H68" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AN68" s="9" t="n">
+      <c r="AN68" s="10" t="n">
         <v>87</v>
       </c>
     </row>
@@ -4600,7 +4639,7 @@
           <t>Estados Unidos</t>
         </is>
       </c>
-      <c r="E69" s="8" t="n">
+      <c r="E69" s="9" t="n">
         <v>2156</v>
       </c>
       <c r="F69" s="8" t="inlineStr">
@@ -4614,7 +4653,7 @@
       <c r="H69" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AA69" s="9" t="n">
+      <c r="AA69" s="10" t="n">
         <v>81</v>
       </c>
     </row>
@@ -4637,7 +4676,7 @@
           <t>España</t>
         </is>
       </c>
-      <c r="E70" s="8" t="n">
+      <c r="E70" s="9" t="n">
         <v>2144</v>
       </c>
       <c r="F70" s="8" t="inlineStr">
@@ -4651,16 +4690,16 @@
       <c r="H70" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="N70" s="10" t="n">
+      <c r="N70" s="11" t="n">
         <v>-38</v>
       </c>
-      <c r="U70" s="9" t="n">
+      <c r="U70" s="10" t="n">
         <v>29</v>
       </c>
-      <c r="V70" s="9" t="n">
+      <c r="V70" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="X70" s="9" t="n">
+      <c r="X70" s="10" t="n">
         <v>37</v>
       </c>
     </row>
@@ -4683,7 +4722,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E71" s="8" t="n">
+      <c r="E71" s="9" t="n">
         <v>2143</v>
       </c>
       <c r="F71" s="8" t="inlineStr">
@@ -4697,40 +4736,40 @@
       <c r="H71" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="J71" s="10" t="n">
+      <c r="J71" s="11" t="n">
         <v>-76</v>
       </c>
-      <c r="L71" s="9" t="n">
+      <c r="L71" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="U71" s="10" t="n">
+      <c r="U71" s="11" t="n">
         <v>-66</v>
       </c>
-      <c r="V71" s="9" t="n">
+      <c r="V71" s="10" t="n">
         <v>63</v>
       </c>
-      <c r="X71" s="10" t="n">
+      <c r="X71" s="11" t="n">
         <v>-5</v>
       </c>
-      <c r="AC71" s="10" t="n">
+      <c r="AC71" s="11" t="n">
         <v>-34</v>
       </c>
-      <c r="AF71" s="10" t="n">
+      <c r="AF71" s="11" t="n">
         <v>-20</v>
       </c>
-      <c r="AG71" s="9" t="n">
+      <c r="AG71" s="10" t="n">
         <v>47</v>
       </c>
-      <c r="AI71" s="9" t="n">
+      <c r="AI71" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="AO71" s="9" t="n">
+      <c r="AO71" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="AS71" s="9" t="n">
+      <c r="AS71" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="AU71" s="9" t="n">
+      <c r="AU71" s="10" t="n">
         <v>15</v>
       </c>
     </row>
@@ -4753,7 +4792,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="E72" s="8" t="n">
+      <c r="E72" s="9" t="n">
         <v>2140</v>
       </c>
       <c r="F72" s="8" t="inlineStr">
@@ -4767,10 +4806,10 @@
       <c r="H72" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="AX72" s="10" t="n">
+      <c r="AX72" s="11" t="n">
         <v>-20</v>
       </c>
-      <c r="AY72" s="9" t="n">
+      <c r="AY72" s="10" t="n">
         <v>85</v>
       </c>
     </row>
@@ -4793,7 +4832,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E73" s="8" t="n">
+      <c r="E73" s="9" t="n">
         <v>2139</v>
       </c>
       <c r="F73" s="8" t="inlineStr">
@@ -4807,40 +4846,40 @@
       <c r="H73" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="R73" s="9" t="n">
+      <c r="R73" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="U73" s="10" t="n">
+      <c r="U73" s="11" t="n">
         <v>-292</v>
       </c>
-      <c r="W73" s="9" t="n">
+      <c r="W73" s="10" t="n">
         <v>185</v>
       </c>
-      <c r="Y73" s="10" t="n">
+      <c r="Y73" s="11" t="n">
         <v>-9</v>
       </c>
-      <c r="AC73" s="9" t="n">
+      <c r="AC73" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="AF73" s="9" t="n">
+      <c r="AF73" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="AG73" s="9" t="n">
+      <c r="AG73" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="AI73" s="9" t="n">
+      <c r="AI73" s="10" t="n">
         <v>75</v>
       </c>
-      <c r="AO73" s="9" t="n">
+      <c r="AO73" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AR73" s="9" t="n">
+      <c r="AR73" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="AT73" s="10" t="n">
+      <c r="AT73" s="11" t="n">
         <v>-77</v>
       </c>
-      <c r="AV73" s="9" t="n">
+      <c r="AV73" s="10" t="n">
         <v>30</v>
       </c>
     </row>
@@ -4863,7 +4902,7 @@
           <t>Estados Unidos</t>
         </is>
       </c>
-      <c r="E74" s="8" t="n">
+      <c r="E74" s="9" t="n">
         <v>2136</v>
       </c>
       <c r="F74" s="8" t="inlineStr">
@@ -4877,7 +4916,7 @@
       <c r="H74" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AA74" s="9" t="n">
+      <c r="AA74" s="10" t="n">
         <v>61</v>
       </c>
     </row>
@@ -4900,7 +4939,7 @@
           <t>México</t>
         </is>
       </c>
-      <c r="E75" s="8" t="n">
+      <c r="E75" s="9" t="n">
         <v>2135</v>
       </c>
       <c r="F75" s="8" t="inlineStr">
@@ -4914,7 +4953,7 @@
       <c r="H75" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="O75" s="9" t="n">
+      <c r="O75" s="10" t="n">
         <v>60</v>
       </c>
     </row>
@@ -4937,7 +4976,7 @@
           <t>Cuba</t>
         </is>
       </c>
-      <c r="E76" s="8" t="n">
+      <c r="E76" s="9" t="n">
         <v>2133</v>
       </c>
       <c r="F76" s="8" t="inlineStr">
@@ -4951,28 +4990,28 @@
       <c r="H76" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="S76" s="10" t="n">
+      <c r="S76" s="11" t="n">
         <v>-7</v>
       </c>
-      <c r="T76" s="9" t="n">
+      <c r="T76" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="AD76" s="10" t="n">
+      <c r="AD76" s="11" t="n">
         <v>-23</v>
       </c>
-      <c r="AE76" s="9" t="n">
+      <c r="AE76" s="10" t="n">
         <v>59</v>
       </c>
-      <c r="AP76" s="9" t="n">
+      <c r="AP76" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AQ76" s="9" t="n">
+      <c r="AQ76" s="10" t="n">
         <v>58</v>
       </c>
-      <c r="BA76" s="10" t="n">
+      <c r="BA76" s="11" t="n">
         <v>-44</v>
       </c>
-      <c r="BB76" s="10" t="n">
+      <c r="BB76" s="11" t="n">
         <v>-5</v>
       </c>
     </row>
@@ -4995,7 +5034,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E77" s="8" t="n">
+      <c r="E77" s="9" t="n">
         <v>2132</v>
       </c>
       <c r="F77" s="8" t="inlineStr">
@@ -5009,7 +5048,7 @@
       <c r="H77" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AN77" s="9" t="n">
+      <c r="AN77" s="10" t="n">
         <v>57</v>
       </c>
     </row>
@@ -5032,7 +5071,7 @@
           <t>Costa Rica</t>
         </is>
       </c>
-      <c r="E78" s="8" t="n">
+      <c r="E78" s="9" t="n">
         <v>2126</v>
       </c>
       <c r="F78" s="8" t="inlineStr">
@@ -5046,13 +5085,13 @@
       <c r="H78" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="AF78" s="9" t="n">
+      <c r="AF78" s="10" t="n">
         <v>118</v>
       </c>
-      <c r="AH78" s="9" t="n">
+      <c r="AH78" s="10" t="n">
         <v>55</v>
       </c>
-      <c r="AJ78" s="10" t="n">
+      <c r="AJ78" s="11" t="n">
         <v>-122</v>
       </c>
     </row>
@@ -5075,7 +5114,7 @@
           <t>México</t>
         </is>
       </c>
-      <c r="E79" s="8" t="n">
+      <c r="E79" s="9" t="n">
         <v>2125</v>
       </c>
       <c r="F79" s="8" t="inlineStr">
@@ -5089,7 +5128,7 @@
       <c r="H79" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="O79" s="9" t="n">
+      <c r="O79" s="10" t="n">
         <v>50</v>
       </c>
     </row>
@@ -5112,7 +5151,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="E80" s="8" t="n">
+      <c r="E80" s="9" t="n">
         <v>2124</v>
       </c>
       <c r="F80" s="8" t="inlineStr">
@@ -5126,10 +5165,10 @@
       <c r="H80" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="AX80" s="9" t="n">
+      <c r="AX80" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="AY80" s="9" t="n">
+      <c r="AY80" s="10" t="n">
         <v>35</v>
       </c>
     </row>
@@ -5152,7 +5191,7 @@
           <t>Estados Unidos</t>
         </is>
       </c>
-      <c r="E81" s="8" t="n">
+      <c r="E81" s="9" t="n">
         <v>2124</v>
       </c>
       <c r="F81" s="8" t="inlineStr">
@@ -5166,16 +5205,16 @@
       <c r="H81" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="AA81" s="10" t="n">
+      <c r="AA81" s="11" t="n">
         <v>-2</v>
       </c>
-      <c r="AF81" s="10" t="n">
+      <c r="AF81" s="11" t="n">
         <v>-44</v>
       </c>
-      <c r="AH81" s="9" t="n">
+      <c r="AH81" s="10" t="n">
         <v>116</v>
       </c>
-      <c r="AJ81" s="10" t="n">
+      <c r="AJ81" s="11" t="n">
         <v>-22</v>
       </c>
     </row>
@@ -5198,7 +5237,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E82" s="8" t="n">
+      <c r="E82" s="9" t="n">
         <v>2122</v>
       </c>
       <c r="F82" s="8" t="inlineStr">
@@ -5212,7 +5251,7 @@
       <c r="H82" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AN82" s="9" t="n">
+      <c r="AN82" s="10" t="n">
         <v>47</v>
       </c>
     </row>
@@ -5235,7 +5274,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E83" s="8" t="n">
+      <c r="E83" s="9" t="n">
         <v>2119</v>
       </c>
       <c r="F83" s="8" t="inlineStr">
@@ -5249,16 +5288,16 @@
       <c r="H83" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="L83" s="10" t="n">
+      <c r="L83" s="11" t="n">
         <v>-96</v>
       </c>
-      <c r="AF83" s="10" t="n">
+      <c r="AF83" s="11" t="n">
         <v>-7</v>
       </c>
-      <c r="AG83" s="9" t="n">
+      <c r="AG83" s="10" t="n">
         <v>64</v>
       </c>
-      <c r="AI83" s="9" t="n">
+      <c r="AI83" s="10" t="n">
         <v>83</v>
       </c>
     </row>
@@ -5281,7 +5320,7 @@
           <t>Cuba</t>
         </is>
       </c>
-      <c r="E84" s="8" t="n">
+      <c r="E84" s="9" t="n">
         <v>2119</v>
       </c>
       <c r="F84" s="8" t="inlineStr">
@@ -5295,10 +5334,10 @@
       <c r="H84" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="AD84" s="9" t="n">
+      <c r="AD84" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="AE84" s="9" t="n">
+      <c r="AE84" s="10" t="n">
         <v>41</v>
       </c>
     </row>
@@ -5321,7 +5360,7 @@
           <t>Reino Unido</t>
         </is>
       </c>
-      <c r="E85" s="8" t="n">
+      <c r="E85" s="9" t="n">
         <v>2118</v>
       </c>
       <c r="F85" s="8" t="inlineStr">
@@ -5335,19 +5374,19 @@
       <c r="H85" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N85" s="10" t="n">
+      <c r="N85" s="11" t="n">
         <v>-81</v>
       </c>
-      <c r="U85" s="9" t="n">
+      <c r="U85" s="10" t="n">
         <v>254</v>
       </c>
-      <c r="W85" s="9" t="n">
+      <c r="W85" s="10" t="n">
         <v>110</v>
       </c>
-      <c r="Y85" s="10" t="n">
+      <c r="Y85" s="11" t="n">
         <v>-241</v>
       </c>
-      <c r="AW85" s="9" t="n">
+      <c r="AW85" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5370,7 +5409,7 @@
           <t>Chile</t>
         </is>
       </c>
-      <c r="E86" s="8" t="n">
+      <c r="E86" s="9" t="n">
         <v>2117</v>
       </c>
       <c r="F86" s="8" t="inlineStr">
@@ -5384,16 +5423,16 @@
       <c r="H86" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="I86" s="10" t="n">
+      <c r="I86" s="11" t="n">
         <v>-25</v>
       </c>
-      <c r="K86" s="10" t="n">
+      <c r="K86" s="11" t="n">
         <v>-64</v>
       </c>
-      <c r="M86" s="10" t="n">
+      <c r="M86" s="11" t="n">
         <v>-6</v>
       </c>
-      <c r="AN86" s="9" t="n">
+      <c r="AN86" s="10" t="n">
         <v>137</v>
       </c>
     </row>
@@ -5416,7 +5455,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="E87" s="8" t="n">
+      <c r="E87" s="9" t="n">
         <v>2113</v>
       </c>
       <c r="F87" s="8" t="inlineStr">
@@ -5430,10 +5469,10 @@
       <c r="H87" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="AX87" s="9" t="n">
+      <c r="AX87" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="AY87" s="9" t="n">
+      <c r="AY87" s="10" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5456,7 +5495,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E88" s="8" t="n">
+      <c r="E88" s="9" t="n">
         <v>2112</v>
       </c>
       <c r="F88" s="8" t="inlineStr">
@@ -5470,7 +5509,7 @@
       <c r="H88" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AN88" s="9" t="n">
+      <c r="AN88" s="10" t="n">
         <v>37</v>
       </c>
     </row>
@@ -5493,7 +5532,7 @@
           <t>España</t>
         </is>
       </c>
-      <c r="E89" s="8" t="n">
+      <c r="E89" s="9" t="n">
         <v>2112</v>
       </c>
       <c r="F89" s="8" t="inlineStr">
@@ -5507,16 +5546,16 @@
       <c r="H89" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="U89" s="10" t="n">
+      <c r="U89" s="11" t="n">
         <v>-239</v>
       </c>
-      <c r="W89" s="9" t="n">
+      <c r="W89" s="10" t="n">
         <v>144</v>
       </c>
-      <c r="Y89" s="9" t="n">
+      <c r="Y89" s="10" t="n">
         <v>106</v>
       </c>
-      <c r="AK89" s="9" t="n">
+      <c r="AK89" s="10" t="n">
         <v>26</v>
       </c>
     </row>
@@ -5539,7 +5578,7 @@
           <t>Panamá</t>
         </is>
       </c>
-      <c r="E90" s="8" t="n">
+      <c r="E90" s="9" t="n">
         <v>2112</v>
       </c>
       <c r="F90" s="8" t="inlineStr">
@@ -5553,28 +5592,28 @@
       <c r="H90" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="I90" s="10" t="n">
+      <c r="I90" s="11" t="n">
         <v>-130</v>
       </c>
-      <c r="K90" s="9" t="n">
+      <c r="K90" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="M90" s="10" t="n">
+      <c r="M90" s="11" t="n">
         <v>-112</v>
       </c>
-      <c r="U90" s="9" t="n">
+      <c r="U90" s="10" t="n">
         <v>201</v>
       </c>
-      <c r="W90" s="9" t="n">
+      <c r="W90" s="10" t="n">
         <v>65</v>
       </c>
-      <c r="Y90" s="10" t="n">
+      <c r="Y90" s="11" t="n">
         <v>-131</v>
       </c>
-      <c r="AL90" s="10" t="n">
+      <c r="AL90" s="11" t="n">
         <v>-18</v>
       </c>
-      <c r="AM90" s="9" t="n">
+      <c r="AM90" s="10" t="n">
         <v>62</v>
       </c>
     </row>
@@ -5597,7 +5636,7 @@
           <t>Chile</t>
         </is>
       </c>
-      <c r="E91" s="8" t="n">
+      <c r="E91" s="9" t="n">
         <v>2111</v>
       </c>
       <c r="F91" s="8" t="inlineStr">
@@ -5611,28 +5650,28 @@
       <c r="H91" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="J91" s="10" t="n">
+      <c r="J91" s="11" t="n">
         <v>-20</v>
       </c>
-      <c r="L91" s="9" t="n">
+      <c r="L91" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="S91" s="10" t="n">
+      <c r="S91" s="11" t="n">
         <v>-21</v>
       </c>
-      <c r="AF91" s="9" t="n">
+      <c r="AF91" s="10" t="n">
         <v>63</v>
       </c>
-      <c r="AG91" s="9" t="n">
+      <c r="AG91" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="AI91" s="9" t="n">
+      <c r="AI91" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="AP91" s="10" t="n">
+      <c r="AP91" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="AQ91" s="10" t="n">
+      <c r="AQ91" s="11" t="n">
         <v>-72</v>
       </c>
     </row>
@@ -5655,7 +5694,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E92" s="8" t="n">
+      <c r="E92" s="9" t="n">
         <v>2109</v>
       </c>
       <c r="F92" s="8" t="inlineStr">
@@ -5669,22 +5708,22 @@
       <c r="H92" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="P92" s="9" t="n">
+      <c r="P92" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="Q92" s="9" t="n">
+      <c r="Q92" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="U92" s="9" t="n">
+      <c r="U92" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="V92" s="10" t="n">
+      <c r="V92" s="11" t="n">
         <v>-29</v>
       </c>
-      <c r="X92" s="10" t="n">
+      <c r="X92" s="11" t="n">
         <v>-34</v>
       </c>
-      <c r="AO92" s="10" t="n">
+      <c r="AO92" s="11" t="n">
         <v>-31</v>
       </c>
     </row>
@@ -5707,7 +5746,7 @@
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="E93" s="8" t="n">
+      <c r="E93" s="9" t="n">
         <v>2100</v>
       </c>
       <c r="F93" s="8" t="inlineStr">
@@ -5721,7 +5760,7 @@
       <c r="H93" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AZ93" s="9" t="n">
+      <c r="AZ93" s="10" t="n">
         <v>25</v>
       </c>
     </row>
@@ -5744,7 +5783,7 @@
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="E94" s="8" t="n">
+      <c r="E94" s="9" t="n">
         <v>2099</v>
       </c>
       <c r="F94" s="8" t="inlineStr">
@@ -5758,7 +5797,7 @@
       <c r="H94" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AB94" s="9" t="n">
+      <c r="AB94" s="10" t="n">
         <v>24</v>
       </c>
     </row>
@@ -5781,7 +5820,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E95" s="8" t="n">
+      <c r="E95" s="9" t="n">
         <v>2095</v>
       </c>
       <c r="F95" s="8" t="inlineStr">
@@ -5795,31 +5834,31 @@
       <c r="H95" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="U95" s="9" t="n">
+      <c r="U95" s="10" t="n">
         <v>109</v>
       </c>
-      <c r="V95" s="10" t="n">
+      <c r="V95" s="11" t="n">
         <v>-17</v>
       </c>
-      <c r="X95" s="10" t="n">
+      <c r="X95" s="11" t="n">
         <v>-17</v>
       </c>
-      <c r="AF95" s="9" t="n">
+      <c r="AF95" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="AH95" s="10" t="n">
+      <c r="AH95" s="11" t="n">
         <v>-60</v>
       </c>
-      <c r="AJ95" s="10" t="n">
+      <c r="AJ95" s="11" t="n">
         <v>-67</v>
       </c>
-      <c r="AR95" s="9" t="n">
+      <c r="AR95" s="10" t="n">
         <v>55</v>
       </c>
-      <c r="AT95" s="9" t="n">
+      <c r="AT95" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="AV95" s="10" t="n">
+      <c r="AV95" s="11" t="n">
         <v>-70</v>
       </c>
     </row>
@@ -5842,7 +5881,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E96" s="8" t="n">
+      <c r="E96" s="9" t="n">
         <v>2095</v>
       </c>
       <c r="F96" s="8" t="inlineStr">
@@ -5856,34 +5895,34 @@
       <c r="H96" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="U96" s="9" t="n">
+      <c r="U96" s="10" t="n">
         <v>123</v>
       </c>
-      <c r="V96" s="9" t="n">
+      <c r="V96" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="X96" s="9" t="n">
+      <c r="X96" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="AC96" s="9" t="n">
+      <c r="AC96" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="AF96" s="9" t="n">
+      <c r="AF96" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="AH96" s="10" t="n">
+      <c r="AH96" s="11" t="n">
         <v>-4</v>
       </c>
-      <c r="AJ96" s="10" t="n">
+      <c r="AJ96" s="11" t="n">
         <v>-84</v>
       </c>
-      <c r="AR96" s="9" t="n">
+      <c r="AR96" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="AT96" s="10" t="n">
+      <c r="AT96" s="11" t="n">
         <v>-59</v>
       </c>
-      <c r="AV96" s="10" t="n">
+      <c r="AV96" s="11" t="n">
         <v>-20</v>
       </c>
     </row>
@@ -5906,7 +5945,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E97" s="8" t="n">
+      <c r="E97" s="9" t="n">
         <v>2093</v>
       </c>
       <c r="F97" s="8" t="inlineStr">
@@ -5920,25 +5959,25 @@
       <c r="H97" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="J97" s="10" t="n">
+      <c r="J97" s="11" t="n">
         <v>-28</v>
       </c>
-      <c r="L97" s="9" t="n">
+      <c r="L97" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="AF97" s="10" t="n">
+      <c r="AF97" s="11" t="n">
         <v>-4</v>
       </c>
-      <c r="AG97" s="10" t="n">
+      <c r="AG97" s="11" t="n">
         <v>-60</v>
       </c>
-      <c r="AI97" s="9" t="n">
+      <c r="AI97" s="10" t="n">
         <v>52</v>
       </c>
-      <c r="AS97" s="9" t="n">
+      <c r="AS97" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="AU97" s="9" t="n">
+      <c r="AU97" s="10" t="n">
         <v>35</v>
       </c>
     </row>
@@ -5961,7 +6000,7 @@
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="E98" s="8" t="n">
+      <c r="E98" s="9" t="n">
         <v>2089</v>
       </c>
       <c r="F98" s="8" t="inlineStr">
@@ -5975,7 +6014,7 @@
       <c r="H98" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AB98" s="9" t="n">
+      <c r="AB98" s="10" t="n">
         <v>14</v>
       </c>
     </row>
@@ -5998,7 +6037,7 @@
           <t>Estados Unidos</t>
         </is>
       </c>
-      <c r="E99" s="8" t="n">
+      <c r="E99" s="9" t="n">
         <v>2088</v>
       </c>
       <c r="F99" s="8" t="inlineStr">
@@ -6012,13 +6051,13 @@
       <c r="H99" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="S99" s="9" t="n">
+      <c r="S99" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="AP99" s="9" t="n">
+      <c r="AP99" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="AQ99" s="10" t="n">
+      <c r="AQ99" s="11" t="n">
         <v>-22</v>
       </c>
     </row>
@@ -6041,7 +6080,7 @@
           <t>España</t>
         </is>
       </c>
-      <c r="E100" s="8" t="n">
+      <c r="E100" s="9" t="n">
         <v>2088</v>
       </c>
       <c r="F100" s="8" t="inlineStr">
@@ -6055,7 +6094,7 @@
       <c r="H100" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N100" s="9" t="n">
+      <c r="N100" s="10" t="n">
         <v>13</v>
       </c>
     </row>
@@ -6078,7 +6117,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E101" s="8" t="n">
+      <c r="E101" s="9" t="n">
         <v>2086</v>
       </c>
       <c r="F101" s="8" t="inlineStr">
@@ -6092,7 +6131,7 @@
       <c r="H101" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="R101" s="9" t="n">
+      <c r="R101" s="10" t="n">
         <v>11</v>
       </c>
     </row>
@@ -6115,7 +6154,7 @@
           <t>Panamá</t>
         </is>
       </c>
-      <c r="E102" s="8" t="n">
+      <c r="E102" s="9" t="n">
         <v>2084</v>
       </c>
       <c r="F102" s="8" t="inlineStr">
@@ -6129,16 +6168,16 @@
       <c r="H102" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="O102" s="10" t="n">
+      <c r="O102" s="11" t="n">
         <v>-40</v>
       </c>
-      <c r="AF102" s="9" t="n">
+      <c r="AF102" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="AG102" s="9" t="n">
+      <c r="AG102" s="10" t="n">
         <v>63</v>
       </c>
-      <c r="AI102" s="10" t="n">
+      <c r="AI102" s="11" t="n">
         <v>-47</v>
       </c>
     </row>
@@ -6161,7 +6200,7 @@
           <t>Francia</t>
         </is>
       </c>
-      <c r="E103" s="8" t="n">
+      <c r="E103" s="9" t="n">
         <v>2083</v>
       </c>
       <c r="F103" s="8" t="inlineStr">
@@ -6175,49 +6214,49 @@
       <c r="H103" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="I103" s="9" t="n">
+      <c r="I103" s="10" t="n">
         <v>53</v>
       </c>
-      <c r="K103" s="9" t="n">
+      <c r="K103" s="10" t="n">
         <v>29</v>
       </c>
-      <c r="M103" s="9" t="n">
+      <c r="M103" s="10" t="n">
         <v>59</v>
       </c>
-      <c r="U103" s="9" t="n">
+      <c r="U103" s="10" t="n">
         <v>44</v>
       </c>
-      <c r="W103" s="10" t="n">
+      <c r="W103" s="11" t="n">
         <v>-34</v>
       </c>
-      <c r="Y103" s="10" t="n">
+      <c r="Y103" s="11" t="n">
         <v>-106</v>
       </c>
-      <c r="Z103" s="9" t="n">
+      <c r="Z103" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="AF103" s="9" t="n">
+      <c r="AF103" s="10" t="n">
         <v>48</v>
       </c>
-      <c r="AH103" s="10" t="n">
+      <c r="AH103" s="11" t="n">
         <v>-90</v>
       </c>
-      <c r="AJ103" s="9" t="n">
+      <c r="AJ103" s="10" t="n">
         <v>117</v>
       </c>
-      <c r="AK103" s="10" t="n">
+      <c r="AK103" s="11" t="n">
         <v>-43</v>
       </c>
-      <c r="AR103" s="9" t="n">
+      <c r="AR103" s="10" t="n">
         <v>55</v>
       </c>
-      <c r="AT103" s="10" t="n">
+      <c r="AT103" s="11" t="n">
         <v>-13</v>
       </c>
-      <c r="AV103" s="10" t="n">
+      <c r="AV103" s="11" t="n">
         <v>-64</v>
       </c>
-      <c r="AW103" s="10" t="n">
+      <c r="AW103" s="11" t="n">
         <v>-59</v>
       </c>
     </row>
@@ -6240,7 +6279,7 @@
           <t>España</t>
         </is>
       </c>
-      <c r="E104" s="8" t="n">
+      <c r="E104" s="9" t="n">
         <v>2081</v>
       </c>
       <c r="F104" s="8" t="inlineStr">
@@ -6254,7 +6293,7 @@
       <c r="H104" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AK104" s="9" t="n">
+      <c r="AK104" s="10" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6277,7 +6316,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E105" s="8" t="n">
+      <c r="E105" s="9" t="n">
         <v>2078</v>
       </c>
       <c r="F105" s="8" t="inlineStr">
@@ -6291,10 +6330,10 @@
       <c r="H105" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="J105" s="9" t="n">
+      <c r="J105" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="L105" s="10" t="n">
+      <c r="L105" s="11" t="n">
         <v>-34</v>
       </c>
     </row>
@@ -6317,7 +6356,7 @@
           <t>Estados Unidos</t>
         </is>
       </c>
-      <c r="E106" s="8" t="n">
+      <c r="E106" s="9" t="n">
         <v>2076</v>
       </c>
       <c r="F106" s="8" t="inlineStr">
@@ -6331,25 +6370,25 @@
       <c r="H106" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="AA106" s="9" t="n">
+      <c r="AA106" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="AF106" s="9" t="n">
+      <c r="AF106" s="10" t="n">
         <v>105</v>
       </c>
-      <c r="AH106" s="9" t="n">
+      <c r="AH106" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="AJ106" s="10" t="n">
+      <c r="AJ106" s="11" t="n">
         <v>-35</v>
       </c>
-      <c r="AR106" s="10" t="n">
+      <c r="AR106" s="11" t="n">
         <v>-40</v>
       </c>
-      <c r="AT106" s="10" t="n">
+      <c r="AT106" s="11" t="n">
         <v>-164</v>
       </c>
-      <c r="AV106" s="9" t="n">
+      <c r="AV106" s="10" t="n">
         <v>60</v>
       </c>
     </row>
@@ -6372,7 +6411,7 @@
           <t>Estados Unidos</t>
         </is>
       </c>
-      <c r="E107" s="8" t="n">
+      <c r="E107" s="9" t="n">
         <v>2075</v>
       </c>
       <c r="F107" s="8" t="inlineStr">
@@ -6406,7 +6445,7 @@
           <t>México</t>
         </is>
       </c>
-      <c r="E108" s="8" t="n">
+      <c r="E108" s="9" t="n">
         <v>2074</v>
       </c>
       <c r="F108" s="8" t="inlineStr">
@@ -6420,31 +6459,31 @@
       <c r="H108" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="J108" s="9" t="n">
+      <c r="J108" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="L108" s="9" t="n">
+      <c r="L108" s="10" t="n">
         <v>98</v>
       </c>
-      <c r="O108" s="9" t="n">
+      <c r="O108" s="10" t="n">
         <v>63</v>
       </c>
-      <c r="U108" s="10" t="n">
+      <c r="U108" s="11" t="n">
         <v>-98</v>
       </c>
-      <c r="W108" s="10" t="n">
+      <c r="W108" s="11" t="n">
         <v>-123</v>
       </c>
-      <c r="Y108" s="9" t="n">
+      <c r="Y108" s="10" t="n">
         <v>170</v>
       </c>
-      <c r="AF108" s="10" t="n">
+      <c r="AF108" s="11" t="n">
         <v>-49</v>
       </c>
-      <c r="AG108" s="10" t="n">
+      <c r="AG108" s="11" t="n">
         <v>-56</v>
       </c>
-      <c r="AI108" s="10" t="n">
+      <c r="AI108" s="11" t="n">
         <v>-7</v>
       </c>
     </row>
@@ -6467,7 +6506,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E109" s="8" t="n">
+      <c r="E109" s="9" t="n">
         <v>2071</v>
       </c>
       <c r="F109" s="8" t="inlineStr">
@@ -6481,28 +6520,28 @@
       <c r="H109" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="J109" s="10" t="n">
+      <c r="J109" s="11" t="n">
         <v>-47</v>
       </c>
-      <c r="L109" s="9" t="n">
+      <c r="L109" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="U109" s="10" t="n">
+      <c r="U109" s="11" t="n">
         <v>-168</v>
       </c>
-      <c r="V109" s="9" t="n">
+      <c r="V109" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="X109" s="9" t="n">
+      <c r="X109" s="10" t="n">
         <v>76</v>
       </c>
-      <c r="AN109" s="9" t="n">
+      <c r="AN109" s="10" t="n">
         <v>85</v>
       </c>
-      <c r="AS109" s="10" t="n">
+      <c r="AS109" s="11" t="n">
         <v>-10</v>
       </c>
-      <c r="AU109" s="10" t="n">
+      <c r="AU109" s="11" t="n">
         <v>-5</v>
       </c>
     </row>
@@ -6525,7 +6564,7 @@
           <t>Estados Unidos</t>
         </is>
       </c>
-      <c r="E110" s="8" t="n">
+      <c r="E110" s="9" t="n">
         <v>2071</v>
       </c>
       <c r="F110" s="8" t="inlineStr">
@@ -6539,40 +6578,40 @@
       <c r="H110" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="J110" s="10" t="n">
+      <c r="J110" s="11" t="n">
         <v>-35</v>
       </c>
-      <c r="L110" s="10" t="n">
+      <c r="L110" s="11" t="n">
         <v>-15</v>
       </c>
-      <c r="U110" s="10" t="n">
+      <c r="U110" s="11" t="n">
         <v>-100</v>
       </c>
-      <c r="V110" s="9" t="n">
+      <c r="V110" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="X110" s="9" t="n">
+      <c r="X110" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="AA110" s="9" t="n">
+      <c r="AA110" s="10" t="n">
         <v>62</v>
       </c>
-      <c r="AF110" s="10" t="n">
+      <c r="AF110" s="11" t="n">
         <v>-99</v>
       </c>
-      <c r="AH110" s="9" t="n">
+      <c r="AH110" s="10" t="n">
         <v>123</v>
       </c>
-      <c r="AJ110" s="10" t="n">
+      <c r="AJ110" s="11" t="n">
         <v>-11</v>
       </c>
-      <c r="AR110" s="10" t="n">
+      <c r="AR110" s="11" t="n">
         <v>-80</v>
       </c>
-      <c r="AT110" s="9" t="n">
+      <c r="AT110" s="10" t="n">
         <v>52</v>
       </c>
-      <c r="AV110" s="9" t="n">
+      <c r="AV110" s="10" t="n">
         <v>50</v>
       </c>
     </row>
@@ -6595,7 +6634,7 @@
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="E111" s="8" t="n">
+      <c r="E111" s="9" t="n">
         <v>2070</v>
       </c>
       <c r="F111" s="8" t="inlineStr">
@@ -6609,7 +6648,7 @@
       <c r="H111" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AZ111" s="10" t="n">
+      <c r="AZ111" s="11" t="n">
         <v>-5</v>
       </c>
     </row>
@@ -6632,7 +6671,7 @@
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="E112" s="8" t="n">
+      <c r="E112" s="9" t="n">
         <v>2069</v>
       </c>
       <c r="F112" s="8" t="inlineStr">
@@ -6646,7 +6685,7 @@
       <c r="H112" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AB112" s="10" t="n">
+      <c r="AB112" s="11" t="n">
         <v>-6</v>
       </c>
     </row>
@@ -6669,7 +6708,7 @@
           <t>Cuba</t>
         </is>
       </c>
-      <c r="E113" s="8" t="n">
+      <c r="E113" s="9" t="n">
         <v>2067</v>
       </c>
       <c r="F113" s="8" t="inlineStr">
@@ -6683,25 +6722,25 @@
       <c r="H113" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="S113" s="10" t="n">
+      <c r="S113" s="11" t="n">
         <v>-91</v>
       </c>
-      <c r="T113" s="9" t="n">
+      <c r="T113" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="AD113" s="9" t="n">
+      <c r="AD113" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="AE113" s="9" t="n">
+      <c r="AE113" s="10" t="n">
         <v>79</v>
       </c>
-      <c r="AP113" s="10" t="n">
+      <c r="AP113" s="11" t="n">
         <v>-85</v>
       </c>
-      <c r="BA113" s="9" t="n">
+      <c r="BA113" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="BB113" s="9" t="n">
+      <c r="BB113" s="10" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6724,7 +6763,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E114" s="8" t="n">
+      <c r="E114" s="9" t="n">
         <v>2065</v>
       </c>
       <c r="F114" s="8" t="inlineStr">
@@ -6738,7 +6777,7 @@
       <c r="H114" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AA114" s="10" t="n">
+      <c r="AA114" s="11" t="n">
         <v>-10</v>
       </c>
     </row>
@@ -6761,7 +6800,7 @@
           <t>México</t>
         </is>
       </c>
-      <c r="E115" s="8" t="n">
+      <c r="E115" s="9" t="n">
         <v>2065</v>
       </c>
       <c r="F115" s="8" t="inlineStr">
@@ -6775,7 +6814,7 @@
       <c r="H115" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="O115" s="10" t="n">
+      <c r="O115" s="11" t="n">
         <v>-10</v>
       </c>
     </row>
@@ -6798,7 +6837,7 @@
           <t>España</t>
         </is>
       </c>
-      <c r="E116" s="8" t="n">
+      <c r="E116" s="9" t="n">
         <v>2064</v>
       </c>
       <c r="F116" s="8" t="inlineStr">
@@ -6812,16 +6851,16 @@
       <c r="H116" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="U116" s="10" t="n">
+      <c r="U116" s="11" t="n">
         <v>-55</v>
       </c>
-      <c r="W116" s="9" t="n">
+      <c r="W116" s="10" t="n">
         <v>102</v>
       </c>
-      <c r="Y116" s="10" t="n">
+      <c r="Y116" s="11" t="n">
         <v>-94</v>
       </c>
-      <c r="AK116" s="9" t="n">
+      <c r="AK116" s="10" t="n">
         <v>36</v>
       </c>
     </row>
@@ -6844,7 +6883,7 @@
           <t>Uruguay</t>
         </is>
       </c>
-      <c r="E117" s="8" t="n">
+      <c r="E117" s="9" t="n">
         <v>2064</v>
       </c>
       <c r="F117" s="8" t="inlineStr">
@@ -6858,7 +6897,7 @@
       <c r="H117" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AO117" s="10" t="n">
+      <c r="AO117" s="11" t="n">
         <v>-11</v>
       </c>
     </row>
@@ -6881,7 +6920,7 @@
           <t>España</t>
         </is>
       </c>
-      <c r="E118" s="8" t="n">
+      <c r="E118" s="9" t="n">
         <v>2063</v>
       </c>
       <c r="F118" s="8" t="inlineStr">
@@ -6895,13 +6934,13 @@
       <c r="H118" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="U118" s="9" t="n">
+      <c r="U118" s="10" t="n">
         <v>188</v>
       </c>
-      <c r="W118" s="10" t="n">
+      <c r="W118" s="11" t="n">
         <v>-210</v>
       </c>
-      <c r="Y118" s="9" t="n">
+      <c r="Y118" s="10" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6924,7 +6963,7 @@
           <t>Grecia</t>
         </is>
       </c>
-      <c r="E119" s="8" t="n">
+      <c r="E119" s="9" t="n">
         <v>2062</v>
       </c>
       <c r="F119" s="8" t="inlineStr">
@@ -6938,25 +6977,25 @@
       <c r="H119" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="I119" s="10" t="n">
+      <c r="I119" s="11" t="n">
         <v>-88</v>
       </c>
-      <c r="K119" s="9" t="n">
+      <c r="K119" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="M119" s="10" t="n">
+      <c r="M119" s="11" t="n">
         <v>-52</v>
       </c>
-      <c r="U119" s="9" t="n">
+      <c r="U119" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="W119" s="9" t="n">
+      <c r="W119" s="10" t="n">
         <v>29</v>
       </c>
-      <c r="Y119" s="9" t="n">
+      <c r="Y119" s="10" t="n">
         <v>77</v>
       </c>
-      <c r="AW119" s="10" t="n">
+      <c r="AW119" s="11" t="n">
         <v>-29</v>
       </c>
     </row>
@@ -6979,7 +7018,7 @@
           <t>España</t>
         </is>
       </c>
-      <c r="E120" s="8" t="n">
+      <c r="E120" s="9" t="n">
         <v>2061</v>
       </c>
       <c r="F120" s="8" t="inlineStr">
@@ -6993,7 +7032,7 @@
       <c r="H120" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AK120" s="10" t="n">
+      <c r="AK120" s="11" t="n">
         <v>-14</v>
       </c>
     </row>
@@ -7016,7 +7055,7 @@
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="E121" s="8" t="n">
+      <c r="E121" s="9" t="n">
         <v>2060</v>
       </c>
       <c r="F121" s="8" t="inlineStr">
@@ -7030,7 +7069,7 @@
       <c r="H121" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AZ121" s="10" t="n">
+      <c r="AZ121" s="11" t="n">
         <v>-15</v>
       </c>
     </row>
@@ -7053,7 +7092,7 @@
           <t>Cuba</t>
         </is>
       </c>
-      <c r="E122" s="8" t="n">
+      <c r="E122" s="9" t="n">
         <v>2060</v>
       </c>
       <c r="F122" s="8" t="inlineStr">
@@ -7067,10 +7106,10 @@
       <c r="H122" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="AD122" s="9" t="n">
+      <c r="AD122" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="AE122" s="10" t="n">
+      <c r="AE122" s="11" t="n">
         <v>-19</v>
       </c>
     </row>
@@ -7093,7 +7132,7 @@
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="E123" s="8" t="n">
+      <c r="E123" s="9" t="n">
         <v>2059</v>
       </c>
       <c r="F123" s="8" t="inlineStr">
@@ -7107,7 +7146,7 @@
       <c r="H123" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AB123" s="10" t="n">
+      <c r="AB123" s="11" t="n">
         <v>-16</v>
       </c>
     </row>
@@ -7130,7 +7169,7 @@
           <t>España</t>
         </is>
       </c>
-      <c r="E124" s="8" t="n">
+      <c r="E124" s="9" t="n">
         <v>2055</v>
       </c>
       <c r="F124" s="8" t="inlineStr">
@@ -7144,13 +7183,13 @@
       <c r="H124" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="AF124" s="10" t="n">
+      <c r="AF124" s="11" t="n">
         <v>-15</v>
       </c>
-      <c r="AH124" s="10" t="n">
+      <c r="AH124" s="11" t="n">
         <v>-103</v>
       </c>
-      <c r="AJ124" s="9" t="n">
+      <c r="AJ124" s="10" t="n">
         <v>98</v>
       </c>
     </row>
@@ -7173,7 +7212,7 @@
           <t>Cuba</t>
         </is>
       </c>
-      <c r="E125" s="8" t="n">
+      <c r="E125" s="9" t="n">
         <v>2053</v>
       </c>
       <c r="F125" s="8" t="inlineStr">
@@ -7187,13 +7226,13 @@
       <c r="H125" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J125" s="9" t="n">
+      <c r="J125" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="L125" s="10" t="n">
+      <c r="L125" s="11" t="n">
         <v>-7</v>
       </c>
-      <c r="T125" s="10" t="n">
+      <c r="T125" s="11" t="n">
         <v>-34</v>
       </c>
     </row>
@@ -7216,7 +7255,7 @@
           <t>México</t>
         </is>
       </c>
-      <c r="E126" s="8" t="n">
+      <c r="E126" s="9" t="n">
         <v>2053</v>
       </c>
       <c r="F126" s="8" t="inlineStr">
@@ -7230,10 +7269,10 @@
       <c r="H126" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="AS126" s="9" t="n">
+      <c r="AS126" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="AU126" s="10" t="n">
+      <c r="AU126" s="11" t="n">
         <v>-25</v>
       </c>
     </row>
@@ -7256,7 +7295,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E127" s="8" t="n">
+      <c r="E127" s="9" t="n">
         <v>2052</v>
       </c>
       <c r="F127" s="8" t="inlineStr">
@@ -7270,7 +7309,7 @@
       <c r="H127" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AN127" s="10" t="n">
+      <c r="AN127" s="11" t="n">
         <v>-23</v>
       </c>
     </row>
@@ -7293,7 +7332,7 @@
           <t>Cuba</t>
         </is>
       </c>
-      <c r="E128" s="8" t="n">
+      <c r="E128" s="9" t="n">
         <v>2051</v>
       </c>
       <c r="F128" s="8" t="inlineStr">
@@ -7307,7 +7346,7 @@
       <c r="H128" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="T128" s="10" t="n">
+      <c r="T128" s="11" t="n">
         <v>-24</v>
       </c>
     </row>
@@ -7330,7 +7369,7 @@
           <t>Cuba</t>
         </is>
       </c>
-      <c r="E129" s="8" t="n">
+      <c r="E129" s="9" t="n">
         <v>2051</v>
       </c>
       <c r="F129" s="8" t="inlineStr">
@@ -7344,10 +7383,10 @@
       <c r="H129" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="BA129" s="9" t="n">
+      <c r="BA129" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="BB129" s="10" t="n">
+      <c r="BB129" s="11" t="n">
         <v>-25</v>
       </c>
     </row>
@@ -7370,7 +7409,7 @@
           <t>Uruguay</t>
         </is>
       </c>
-      <c r="E130" s="8" t="n">
+      <c r="E130" s="9" t="n">
         <v>2049</v>
       </c>
       <c r="F130" s="8" t="inlineStr">
@@ -7384,28 +7423,28 @@
       <c r="H130" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="I130" s="10" t="n">
+      <c r="I130" s="11" t="n">
         <v>-35</v>
       </c>
-      <c r="K130" s="9" t="n">
+      <c r="K130" s="10" t="n">
         <v>93</v>
       </c>
-      <c r="M130" s="9" t="n">
+      <c r="M130" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="AC130" s="9" t="n">
+      <c r="AC130" s="10" t="n">
         <v>59</v>
       </c>
-      <c r="AO130" s="9" t="n">
+      <c r="AO130" s="10" t="n">
         <v>78</v>
       </c>
-      <c r="AR130" s="10" t="n">
+      <c r="AR130" s="11" t="n">
         <v>-97</v>
       </c>
-      <c r="AT130" s="10" t="n">
+      <c r="AT130" s="11" t="n">
         <v>-40</v>
       </c>
-      <c r="AV130" s="10" t="n">
+      <c r="AV130" s="11" t="n">
         <v>-90</v>
       </c>
     </row>
@@ -7428,7 +7467,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E131" s="8" t="n">
+      <c r="E131" s="9" t="n">
         <v>2046</v>
       </c>
       <c r="F131" s="8" t="inlineStr">
@@ -7442,7 +7481,7 @@
       <c r="H131" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="R131" s="10" t="n">
+      <c r="R131" s="11" t="n">
         <v>-29</v>
       </c>
     </row>
@@ -7465,7 +7504,7 @@
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="E132" s="8" t="n">
+      <c r="E132" s="9" t="n">
         <v>2043</v>
       </c>
       <c r="F132" s="8" t="inlineStr">
@@ -7479,13 +7518,13 @@
       <c r="H132" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="R132" s="9" t="n">
+      <c r="R132" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="AO132" s="10" t="n">
+      <c r="AO132" s="11" t="n">
         <v>-55</v>
       </c>
-      <c r="AZ132" s="9" t="n">
+      <c r="AZ132" s="10" t="n">
         <v>15</v>
       </c>
     </row>
@@ -7508,7 +7547,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E133" s="8" t="n">
+      <c r="E133" s="9" t="n">
         <v>2042</v>
       </c>
       <c r="F133" s="8" t="inlineStr">
@@ -7522,7 +7561,7 @@
       <c r="H133" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AN133" s="10" t="n">
+      <c r="AN133" s="11" t="n">
         <v>-33</v>
       </c>
     </row>
@@ -7545,7 +7584,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E134" s="8" t="n">
+      <c r="E134" s="9" t="n">
         <v>2041</v>
       </c>
       <c r="F134" s="8" t="inlineStr">
@@ -7559,34 +7598,34 @@
       <c r="H134" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="I134" s="10" t="n">
+      <c r="I134" s="11" t="n">
         <v>-46</v>
       </c>
-      <c r="K134" s="10" t="n">
+      <c r="K134" s="11" t="n">
         <v>-16</v>
       </c>
-      <c r="M134" s="10" t="n">
+      <c r="M134" s="11" t="n">
         <v>-104</v>
       </c>
-      <c r="R134" s="9" t="n">
+      <c r="R134" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="U134" s="10" t="n">
+      <c r="U134" s="11" t="n">
         <v>-130</v>
       </c>
-      <c r="W134" s="9" t="n">
+      <c r="W134" s="10" t="n">
         <v>271</v>
       </c>
-      <c r="Y134" s="9" t="n">
+      <c r="Y134" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AO134" s="9" t="n">
+      <c r="AO134" s="10" t="n">
         <v>90</v>
       </c>
-      <c r="AR134" s="10" t="n">
+      <c r="AR134" s="11" t="n">
         <v>-94</v>
       </c>
-      <c r="AS134" s="10" t="n">
+      <c r="AS134" s="11" t="n">
         <v>-40</v>
       </c>
     </row>
@@ -7609,7 +7648,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E135" s="8" t="n">
+      <c r="E135" s="9" t="n">
         <v>2040</v>
       </c>
       <c r="F135" s="8" t="inlineStr">
@@ -7623,7 +7662,7 @@
       <c r="H135" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AZ135" s="10" t="n">
+      <c r="AZ135" s="11" t="n">
         <v>-35</v>
       </c>
     </row>
@@ -7646,7 +7685,7 @@
           <t>España</t>
         </is>
       </c>
-      <c r="E136" s="8" t="n">
+      <c r="E136" s="9" t="n">
         <v>2040</v>
       </c>
       <c r="F136" s="8" t="inlineStr">
@@ -7660,16 +7699,16 @@
       <c r="H136" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="U136" s="9" t="n">
+      <c r="U136" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="W136" s="9" t="n">
+      <c r="W136" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Y136" s="10" t="n">
+      <c r="Y136" s="11" t="n">
         <v>-66</v>
       </c>
-      <c r="AK136" s="10" t="n">
+      <c r="AK136" s="11" t="n">
         <v>-4</v>
       </c>
     </row>
@@ -7692,7 +7731,7 @@
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="E137" s="8" t="n">
+      <c r="E137" s="9" t="n">
         <v>2039</v>
       </c>
       <c r="F137" s="8" t="inlineStr">
@@ -7706,7 +7745,7 @@
       <c r="H137" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AB137" s="10" t="n">
+      <c r="AB137" s="11" t="n">
         <v>-36</v>
       </c>
     </row>
@@ -7729,7 +7768,7 @@
           <t>México</t>
         </is>
       </c>
-      <c r="E138" s="8" t="n">
+      <c r="E138" s="9" t="n">
         <v>2039</v>
       </c>
       <c r="F138" s="8" t="inlineStr">
@@ -7743,13 +7782,13 @@
       <c r="H138" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="AA138" s="10" t="n">
+      <c r="AA138" s="11" t="n">
         <v>-26</v>
       </c>
-      <c r="AL138" s="9" t="n">
+      <c r="AL138" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="AM138" s="10" t="n">
+      <c r="AM138" s="11" t="n">
         <v>-48</v>
       </c>
     </row>
@@ -7772,7 +7811,7 @@
           <t>Perú</t>
         </is>
       </c>
-      <c r="E139" s="8" t="n">
+      <c r="E139" s="9" t="n">
         <v>2038</v>
       </c>
       <c r="F139" s="8" t="inlineStr">
@@ -7786,10 +7825,10 @@
       <c r="H139" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="P139" s="10" t="n">
+      <c r="P139" s="11" t="n">
         <v>-17</v>
       </c>
-      <c r="Q139" s="10" t="n">
+      <c r="Q139" s="11" t="n">
         <v>-19</v>
       </c>
     </row>
@@ -7812,7 +7851,7 @@
           <t>España</t>
         </is>
       </c>
-      <c r="E140" s="8" t="n">
+      <c r="E140" s="9" t="n">
         <v>2038</v>
       </c>
       <c r="F140" s="8" t="inlineStr">
@@ -7826,7 +7865,7 @@
       <c r="H140" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N140" s="10" t="n">
+      <c r="N140" s="11" t="n">
         <v>-37</v>
       </c>
     </row>
@@ -7849,7 +7888,7 @@
           <t>Estados Unidos</t>
         </is>
       </c>
-      <c r="E141" s="8" t="n">
+      <c r="E141" s="9" t="n">
         <v>2036</v>
       </c>
       <c r="F141" s="8" t="inlineStr">
@@ -7863,7 +7902,7 @@
       <c r="H141" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AA141" s="10" t="n">
+      <c r="AA141" s="11" t="n">
         <v>-39</v>
       </c>
     </row>
@@ -7886,7 +7925,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E142" s="8" t="n">
+      <c r="E142" s="9" t="n">
         <v>2034</v>
       </c>
       <c r="F142" s="8" t="inlineStr">
@@ -7900,7 +7939,7 @@
       <c r="H142" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AO142" s="10" t="n">
+      <c r="AO142" s="11" t="n">
         <v>-41</v>
       </c>
     </row>
@@ -7923,7 +7962,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E143" s="8" t="n">
+      <c r="E143" s="9" t="n">
         <v>2032</v>
       </c>
       <c r="F143" s="8" t="inlineStr">
@@ -7937,7 +7976,7 @@
       <c r="H143" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AN143" s="10" t="n">
+      <c r="AN143" s="11" t="n">
         <v>-43</v>
       </c>
     </row>
@@ -7960,7 +7999,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E144" s="8" t="n">
+      <c r="E144" s="9" t="n">
         <v>2031</v>
       </c>
       <c r="F144" s="8" t="inlineStr">
@@ -7974,37 +8013,37 @@
       <c r="H144" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="L144" s="10" t="n">
+      <c r="L144" s="11" t="n">
         <v>-83</v>
       </c>
-      <c r="U144" s="10" t="n">
+      <c r="U144" s="11" t="n">
         <v>-138</v>
       </c>
-      <c r="V144" s="10" t="n">
+      <c r="V144" s="11" t="n">
         <v>-7</v>
       </c>
-      <c r="X144" s="9" t="n">
+      <c r="X144" s="10" t="n">
         <v>75</v>
       </c>
-      <c r="AF144" s="10" t="n">
+      <c r="AF144" s="11" t="n">
         <v>-62</v>
       </c>
-      <c r="AG144" s="9" t="n">
+      <c r="AG144" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="AI144" s="10" t="n">
+      <c r="AI144" s="11" t="n">
         <v>-3</v>
       </c>
-      <c r="AL144" s="9" t="n">
+      <c r="AL144" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="AM144" s="9" t="n">
+      <c r="AM144" s="10" t="n">
         <v>62</v>
       </c>
-      <c r="AS144" s="9" t="n">
+      <c r="AS144" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="AU144" s="9" t="n">
+      <c r="AU144" s="10" t="n">
         <v>25</v>
       </c>
     </row>
@@ -8027,7 +8066,7 @@
           <t>Chile</t>
         </is>
       </c>
-      <c r="E145" s="8" t="n">
+      <c r="E145" s="9" t="n">
         <v>2030</v>
       </c>
       <c r="F145" s="8" t="inlineStr">
@@ -8041,13 +8080,13 @@
       <c r="H145" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I145" s="9" t="n">
+      <c r="I145" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="K145" s="10" t="n">
+      <c r="K145" s="11" t="n">
         <v>-44</v>
       </c>
-      <c r="M145" s="10" t="n">
+      <c r="M145" s="11" t="n">
         <v>-5</v>
       </c>
     </row>
@@ -8070,7 +8109,7 @@
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="E146" s="8" t="n">
+      <c r="E146" s="9" t="n">
         <v>2030</v>
       </c>
       <c r="F146" s="8" t="inlineStr">
@@ -8084,7 +8123,7 @@
       <c r="H146" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AZ146" s="10" t="n">
+      <c r="AZ146" s="11" t="n">
         <v>-45</v>
       </c>
     </row>
@@ -8107,7 +8146,7 @@
           <t>Chile</t>
         </is>
       </c>
-      <c r="E147" s="8" t="n">
+      <c r="E147" s="9" t="n">
         <v>2029</v>
       </c>
       <c r="F147" s="8" t="inlineStr">
@@ -8121,7 +8160,7 @@
       <c r="H147" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AB147" s="10" t="n">
+      <c r="AB147" s="11" t="n">
         <v>-46</v>
       </c>
     </row>
@@ -8144,7 +8183,7 @@
           <t>México</t>
         </is>
       </c>
-      <c r="E148" s="8" t="n">
+      <c r="E148" s="9" t="n">
         <v>2028</v>
       </c>
       <c r="F148" s="8" t="inlineStr">
@@ -8158,7 +8197,7 @@
       <c r="H148" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N148" s="10" t="n">
+      <c r="N148" s="11" t="n">
         <v>-47</v>
       </c>
     </row>
@@ -8181,7 +8220,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="E149" s="8" t="n">
+      <c r="E149" s="9" t="n">
         <v>2027</v>
       </c>
       <c r="F149" s="8" t="inlineStr">
@@ -8195,13 +8234,13 @@
       <c r="H149" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I149" s="9" t="n">
+      <c r="I149" s="10" t="n">
         <v>63</v>
       </c>
-      <c r="K149" s="10" t="n">
+      <c r="K149" s="11" t="n">
         <v>-27</v>
       </c>
-      <c r="M149" s="10" t="n">
+      <c r="M149" s="11" t="n">
         <v>-85</v>
       </c>
     </row>
@@ -8224,7 +8263,7 @@
           <t>España</t>
         </is>
       </c>
-      <c r="E150" s="8" t="n">
+      <c r="E150" s="9" t="n">
         <v>2026</v>
       </c>
       <c r="F150" s="8" t="inlineStr">
@@ -8238,7 +8277,7 @@
       <c r="H150" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AW150" s="10" t="n">
+      <c r="AW150" s="11" t="n">
         <v>-49</v>
       </c>
     </row>
@@ -8261,7 +8300,7 @@
           <t>Estados Unidos</t>
         </is>
       </c>
-      <c r="E151" s="8" t="n">
+      <c r="E151" s="9" t="n">
         <v>2026</v>
       </c>
       <c r="F151" s="8" t="inlineStr">
@@ -8275,7 +8314,7 @@
       <c r="H151" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AA151" s="10" t="n">
+      <c r="AA151" s="11" t="n">
         <v>-49</v>
       </c>
     </row>
@@ -8298,7 +8337,7 @@
           <t>Panamá</t>
         </is>
       </c>
-      <c r="E152" s="8" t="n">
+      <c r="E152" s="9" t="n">
         <v>2024</v>
       </c>
       <c r="F152" s="8" t="inlineStr">
@@ -8312,40 +8351,40 @@
       <c r="H152" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="O152" s="9" t="n">
+      <c r="O152" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="U152" s="9" t="n">
+      <c r="U152" s="10" t="n">
         <v>69</v>
       </c>
-      <c r="V152" s="10" t="n">
+      <c r="V152" s="11" t="n">
         <v>-60</v>
       </c>
-      <c r="X152" s="10" t="n">
+      <c r="X152" s="11" t="n">
         <v>-77</v>
       </c>
-      <c r="AL152" s="10" t="n">
+      <c r="AL152" s="11" t="n">
         <v>-31</v>
       </c>
-      <c r="AM152" s="10" t="n">
+      <c r="AM152" s="11" t="n">
         <v>-61</v>
       </c>
-      <c r="AN152" s="9" t="n">
+      <c r="AN152" s="10" t="n">
         <v>61</v>
       </c>
-      <c r="AR152" s="9" t="n">
+      <c r="AR152" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="AT152" s="10" t="n">
+      <c r="AT152" s="11" t="n">
         <v>-58</v>
       </c>
-      <c r="AV152" s="10" t="n">
+      <c r="AV152" s="11" t="n">
         <v>-25</v>
       </c>
-      <c r="AX152" s="9" t="n">
+      <c r="AX152" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="AY152" s="9" t="n">
+      <c r="AY152" s="10" t="n">
         <v>15</v>
       </c>
     </row>
@@ -8368,7 +8407,7 @@
           <t>México</t>
         </is>
       </c>
-      <c r="E153" s="8" t="n">
+      <c r="E153" s="9" t="n">
         <v>2024</v>
       </c>
       <c r="F153" s="8" t="inlineStr">
@@ -8382,10 +8421,10 @@
       <c r="H153" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="AS153" s="10" t="n">
+      <c r="AS153" s="11" t="n">
         <v>-16</v>
       </c>
-      <c r="AU153" s="10" t="n">
+      <c r="AU153" s="11" t="n">
         <v>-35</v>
       </c>
     </row>
@@ -8408,7 +8447,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E154" s="8" t="n">
+      <c r="E154" s="9" t="n">
         <v>2022</v>
       </c>
       <c r="F154" s="8" t="inlineStr">
@@ -8422,7 +8461,7 @@
       <c r="H154" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AN154" s="10" t="n">
+      <c r="AN154" s="11" t="n">
         <v>-53</v>
       </c>
     </row>
@@ -8445,7 +8484,7 @@
           <t>Chile</t>
         </is>
       </c>
-      <c r="E155" s="8" t="n">
+      <c r="E155" s="9" t="n">
         <v>2021</v>
       </c>
       <c r="F155" s="8" t="inlineStr">
@@ -8459,7 +8498,7 @@
       <c r="H155" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="L155" s="10" t="n">
+      <c r="L155" s="11" t="n">
         <v>-54</v>
       </c>
     </row>
@@ -8482,7 +8521,7 @@
           <t>Panamá</t>
         </is>
       </c>
-      <c r="E156" s="8" t="n">
+      <c r="E156" s="9" t="n">
         <v>2020</v>
       </c>
       <c r="F156" s="8" t="inlineStr">
@@ -8496,49 +8535,49 @@
       <c r="H156" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="R156" s="10" t="n">
+      <c r="R156" s="11" t="n">
         <v>-11</v>
       </c>
-      <c r="U156" s="10" t="n">
+      <c r="U156" s="11" t="n">
         <v>-10</v>
       </c>
-      <c r="W156" s="9" t="n">
+      <c r="W156" s="10" t="n">
         <v>134</v>
       </c>
-      <c r="Y156" s="10" t="n">
+      <c r="Y156" s="11" t="n">
         <v>-77</v>
       </c>
-      <c r="AB156" s="9" t="n">
+      <c r="AB156" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="AF156" s="10" t="n">
+      <c r="AF156" s="11" t="n">
         <v>-58</v>
       </c>
-      <c r="AH156" s="10" t="n">
+      <c r="AH156" s="11" t="n">
         <v>-4</v>
       </c>
-      <c r="AJ156" s="10" t="n">
+      <c r="AJ156" s="11" t="n">
         <v>-91</v>
       </c>
-      <c r="AL156" s="9" t="n">
+      <c r="AL156" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="AM156" s="9" t="n">
+      <c r="AM156" s="10" t="n">
         <v>151</v>
       </c>
-      <c r="AR156" s="10" t="n">
+      <c r="AR156" s="11" t="n">
         <v>-59</v>
       </c>
-      <c r="AT156" s="9" t="n">
+      <c r="AT156" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="AV156" s="10" t="n">
+      <c r="AV156" s="11" t="n">
         <v>-129</v>
       </c>
-      <c r="AX156" s="10" t="n">
+      <c r="AX156" s="11" t="n">
         <v>-13</v>
       </c>
-      <c r="AY156" s="10" t="n">
+      <c r="AY156" s="11" t="n">
         <v>-5</v>
       </c>
     </row>
@@ -8561,7 +8600,7 @@
           <t>Cuba</t>
         </is>
       </c>
-      <c r="E157" s="8" t="n">
+      <c r="E157" s="9" t="n">
         <v>2017</v>
       </c>
       <c r="F157" s="8" t="inlineStr">
@@ -8575,13 +8614,13 @@
       <c r="H157" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="T157" s="9" t="n">
+      <c r="T157" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="BA157" s="10" t="n">
+      <c r="BA157" s="11" t="n">
         <v>-51</v>
       </c>
-      <c r="BB157" s="10" t="n">
+      <c r="BB157" s="11" t="n">
         <v>-15</v>
       </c>
     </row>
@@ -8604,7 +8643,7 @@
           <t>Estados Unidos</t>
         </is>
       </c>
-      <c r="E158" s="8" t="n">
+      <c r="E158" s="9" t="n">
         <v>2016</v>
       </c>
       <c r="F158" s="8" t="inlineStr">
@@ -8618,7 +8657,7 @@
       <c r="H158" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AA158" s="10" t="n">
+      <c r="AA158" s="11" t="n">
         <v>-59</v>
       </c>
     </row>
@@ -8641,7 +8680,7 @@
           <t>México</t>
         </is>
       </c>
-      <c r="E159" s="8" t="n">
+      <c r="E159" s="9" t="n">
         <v>2014</v>
       </c>
       <c r="F159" s="8" t="inlineStr">
@@ -8655,13 +8694,13 @@
       <c r="H159" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="O159" s="10" t="n">
+      <c r="O159" s="11" t="n">
         <v>-35</v>
       </c>
-      <c r="AS159" s="10" t="n">
+      <c r="AS159" s="11" t="n">
         <v>-31</v>
       </c>
-      <c r="AU159" s="9" t="n">
+      <c r="AU159" s="10" t="n">
         <v>5</v>
       </c>
     </row>
@@ -8684,7 +8723,7 @@
           <t>Panamá</t>
         </is>
       </c>
-      <c r="E160" s="8" t="n">
+      <c r="E160" s="9" t="n">
         <v>2012</v>
       </c>
       <c r="F160" s="8" t="inlineStr">
@@ -8698,10 +8737,10 @@
       <c r="H160" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="AL160" s="10" t="n">
+      <c r="AL160" s="11" t="n">
         <v>-85</v>
       </c>
-      <c r="AM160" s="9" t="n">
+      <c r="AM160" s="10" t="n">
         <v>22</v>
       </c>
     </row>
@@ -8724,7 +8763,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E161" s="8" t="n">
+      <c r="E161" s="9" t="n">
         <v>2012</v>
       </c>
       <c r="F161" s="8" t="inlineStr">
@@ -8738,7 +8777,7 @@
       <c r="H161" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AN161" s="10" t="n">
+      <c r="AN161" s="11" t="n">
         <v>-63</v>
       </c>
     </row>
@@ -8761,7 +8800,7 @@
           <t>Cuba</t>
         </is>
       </c>
-      <c r="E162" s="8" t="n">
+      <c r="E162" s="9" t="n">
         <v>2011</v>
       </c>
       <c r="F162" s="8" t="inlineStr">
@@ -8775,7 +8814,7 @@
       <c r="H162" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="T162" s="10" t="n">
+      <c r="T162" s="11" t="n">
         <v>-64</v>
       </c>
     </row>
@@ -8798,7 +8837,7 @@
           <t>España</t>
         </is>
       </c>
-      <c r="E163" s="8" t="n">
+      <c r="E163" s="9" t="n">
         <v>2009</v>
       </c>
       <c r="F163" s="8" t="inlineStr">
@@ -8812,10 +8851,10 @@
       <c r="H163" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="AK163" s="10" t="n">
+      <c r="AK163" s="11" t="n">
         <v>-77</v>
       </c>
-      <c r="AW163" s="9" t="n">
+      <c r="AW163" s="10" t="n">
         <v>11</v>
       </c>
     </row>
@@ -8838,7 +8877,7 @@
           <t>España</t>
         </is>
       </c>
-      <c r="E164" s="8" t="n">
+      <c r="E164" s="9" t="n">
         <v>2008</v>
       </c>
       <c r="F164" s="8" t="inlineStr">
@@ -8852,7 +8891,7 @@
       <c r="H164" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N164" s="10" t="n">
+      <c r="N164" s="11" t="n">
         <v>-67</v>
       </c>
     </row>
@@ -8875,7 +8914,7 @@
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="E165" s="8" t="n">
+      <c r="E165" s="9" t="n">
         <v>2007</v>
       </c>
       <c r="F165" s="8" t="inlineStr">
@@ -8889,13 +8928,13 @@
       <c r="H165" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="R165" s="10" t="n">
+      <c r="R165" s="11" t="n">
         <v>-45</v>
       </c>
-      <c r="AC165" s="10" t="n">
+      <c r="AC165" s="11" t="n">
         <v>-58</v>
       </c>
-      <c r="AZ165" s="9" t="n">
+      <c r="AZ165" s="10" t="n">
         <v>35</v>
       </c>
     </row>
@@ -8918,7 +8957,7 @@
           <t>Estados Unidos</t>
         </is>
       </c>
-      <c r="E166" s="8" t="n">
+      <c r="E166" s="9" t="n">
         <v>2006</v>
       </c>
       <c r="F166" s="8" t="inlineStr">
@@ -8932,7 +8971,7 @@
       <c r="H166" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AA166" s="10" t="n">
+      <c r="AA166" s="11" t="n">
         <v>-69</v>
       </c>
     </row>
@@ -8955,7 +8994,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="E167" s="8" t="n">
+      <c r="E167" s="9" t="n">
         <v>2006</v>
       </c>
       <c r="F167" s="8" t="inlineStr">
@@ -8969,10 +9008,10 @@
       <c r="H167" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="AL167" s="9" t="n">
+      <c r="AL167" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="AM167" s="10" t="n">
+      <c r="AM167" s="11" t="n">
         <v>-78</v>
       </c>
     </row>
@@ -8995,7 +9034,7 @@
           <t>México</t>
         </is>
       </c>
-      <c r="E168" s="8" t="n">
+      <c r="E168" s="9" t="n">
         <v>2005</v>
       </c>
       <c r="F168" s="8" t="inlineStr">
@@ -9009,7 +9048,7 @@
       <c r="H168" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="O168" s="10" t="n">
+      <c r="O168" s="11" t="n">
         <v>-70</v>
       </c>
     </row>
@@ -9032,7 +9071,7 @@
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="E169" s="8" t="n">
+      <c r="E169" s="9" t="n">
         <v>2004</v>
       </c>
       <c r="F169" s="8" t="inlineStr">
@@ -9046,7 +9085,7 @@
       <c r="H169" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AO169" s="10" t="n">
+      <c r="AO169" s="11" t="n">
         <v>-71</v>
       </c>
     </row>
@@ -9069,7 +9108,7 @@
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="E170" s="8" t="n">
+      <c r="E170" s="9" t="n">
         <v>2002</v>
       </c>
       <c r="F170" s="8" t="inlineStr">
@@ -9083,13 +9122,13 @@
       <c r="H170" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="R170" s="9" t="n">
+      <c r="R170" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="AO170" s="10" t="n">
+      <c r="AO170" s="11" t="n">
         <v>-82</v>
       </c>
-      <c r="AZ170" s="9" t="n">
+      <c r="AZ170" s="10" t="n">
         <v>5</v>
       </c>
     </row>
@@ -9112,7 +9151,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E171" s="8" t="n">
+      <c r="E171" s="9" t="n">
         <v>2002</v>
       </c>
       <c r="F171" s="8" t="inlineStr">
@@ -9126,7 +9165,7 @@
       <c r="H171" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AN171" s="10" t="n">
+      <c r="AN171" s="11" t="n">
         <v>-73</v>
       </c>
     </row>
@@ -9149,7 +9188,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="E172" s="8" t="n">
+      <c r="E172" s="9" t="n">
         <v>2001</v>
       </c>
       <c r="F172" s="8" t="inlineStr">
@@ -9163,10 +9202,10 @@
       <c r="H172" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="P172" s="10" t="n">
+      <c r="P172" s="11" t="n">
         <v>-35</v>
       </c>
-      <c r="Q172" s="10" t="n">
+      <c r="Q172" s="11" t="n">
         <v>-39</v>
       </c>
     </row>
@@ -9189,7 +9228,7 @@
           <t>Cuba</t>
         </is>
       </c>
-      <c r="E173" s="8" t="n">
+      <c r="E173" s="9" t="n">
         <v>1999</v>
       </c>
       <c r="F173" s="8" t="inlineStr">
@@ -9203,28 +9242,28 @@
       <c r="H173" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="S173" s="9" t="n">
+      <c r="S173" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="T173" s="10" t="n">
+      <c r="T173" s="11" t="n">
         <v>-33</v>
       </c>
-      <c r="AD173" s="10" t="n">
+      <c r="AD173" s="11" t="n">
         <v>-23</v>
       </c>
-      <c r="AE173" s="10" t="n">
+      <c r="AE173" s="11" t="n">
         <v>-3</v>
       </c>
-      <c r="AP173" s="9" t="n">
+      <c r="AP173" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="AQ173" s="9" t="n">
+      <c r="AQ173" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="BA173" s="10" t="n">
+      <c r="BA173" s="11" t="n">
         <v>-4</v>
       </c>
-      <c r="BB173" s="10" t="n">
+      <c r="BB173" s="11" t="n">
         <v>-45</v>
       </c>
     </row>
@@ -9247,7 +9286,7 @@
           <t>Chile</t>
         </is>
       </c>
-      <c r="E174" s="8" t="n">
+      <c r="E174" s="9" t="n">
         <v>1995</v>
       </c>
       <c r="F174" s="8" t="inlineStr">
@@ -9261,31 +9300,31 @@
       <c r="H174" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="U174" s="10" t="n">
+      <c r="U174" s="11" t="n">
         <v>-94</v>
       </c>
-      <c r="W174" s="9" t="n">
+      <c r="W174" s="10" t="n">
         <v>244</v>
       </c>
-      <c r="Y174" s="10" t="n">
+      <c r="Y174" s="11" t="n">
         <v>-72</v>
       </c>
-      <c r="AF174" s="9" t="n">
+      <c r="AF174" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="AG174" s="9" t="n">
+      <c r="AG174" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="AI174" s="9" t="n">
+      <c r="AI174" s="10" t="n">
         <v>78</v>
       </c>
-      <c r="AR174" s="10" t="n">
+      <c r="AR174" s="11" t="n">
         <v>-80</v>
       </c>
-      <c r="AT174" s="10" t="n">
+      <c r="AT174" s="11" t="n">
         <v>-85</v>
       </c>
-      <c r="AV174" s="10" t="n">
+      <c r="AV174" s="11" t="n">
         <v>-220</v>
       </c>
     </row>
@@ -9308,7 +9347,7 @@
           <t>Cuba</t>
         </is>
       </c>
-      <c r="E175" s="8" t="n">
+      <c r="E175" s="9" t="n">
         <v>1995</v>
       </c>
       <c r="F175" s="8" t="inlineStr">
@@ -9322,19 +9361,19 @@
       <c r="H175" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="S175" s="10" t="n">
+      <c r="S175" s="11" t="n">
         <v>-34</v>
       </c>
-      <c r="AP175" s="10" t="n">
+      <c r="AP175" s="11" t="n">
         <v>-47</v>
       </c>
-      <c r="AQ175" s="9" t="n">
+      <c r="AQ175" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="BA175" s="9" t="n">
+      <c r="BA175" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="BB175" s="10" t="n">
+      <c r="BB175" s="11" t="n">
         <v>-35</v>
       </c>
     </row>
@@ -9357,7 +9396,7 @@
           <t>México</t>
         </is>
       </c>
-      <c r="E176" s="8" t="n">
+      <c r="E176" s="9" t="n">
         <v>1995</v>
       </c>
       <c r="F176" s="8" t="inlineStr">
@@ -9371,7 +9410,7 @@
       <c r="H176" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="O176" s="10" t="n">
+      <c r="O176" s="11" t="n">
         <v>-80</v>
       </c>
     </row>
@@ -9394,7 +9433,7 @@
           <t>Costa Rica</t>
         </is>
       </c>
-      <c r="E177" s="8" t="n">
+      <c r="E177" s="9" t="n">
         <v>1994</v>
       </c>
       <c r="F177" s="8" t="inlineStr">
@@ -9408,13 +9447,13 @@
       <c r="H177" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I177" s="10" t="n">
+      <c r="I177" s="11" t="n">
         <v>-38</v>
       </c>
-      <c r="K177" s="10" t="n">
+      <c r="K177" s="11" t="n">
         <v>-78</v>
       </c>
-      <c r="M177" s="9" t="n">
+      <c r="M177" s="10" t="n">
         <v>35</v>
       </c>
     </row>
@@ -9437,7 +9476,7 @@
           <t>España</t>
         </is>
       </c>
-      <c r="E178" s="8" t="n">
+      <c r="E178" s="9" t="n">
         <v>1993</v>
       </c>
       <c r="F178" s="8" t="inlineStr">
@@ -9451,13 +9490,13 @@
       <c r="H178" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="U178" s="9" t="n">
+      <c r="U178" s="10" t="n">
         <v>189</v>
       </c>
-      <c r="W178" s="10" t="n">
+      <c r="W178" s="11" t="n">
         <v>-327</v>
       </c>
-      <c r="X178" s="9" t="n">
+      <c r="X178" s="10" t="n">
         <v>57</v>
       </c>
     </row>
@@ -9480,7 +9519,7 @@
           <t>Cuba</t>
         </is>
       </c>
-      <c r="E179" s="8" t="n">
+      <c r="E179" s="9" t="n">
         <v>1993</v>
       </c>
       <c r="F179" s="8" t="inlineStr">
@@ -9494,19 +9533,19 @@
       <c r="H179" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="S179" s="10" t="n">
+      <c r="S179" s="11" t="n">
         <v>-21</v>
       </c>
-      <c r="AP179" s="10" t="n">
+      <c r="AP179" s="11" t="n">
         <v>-30</v>
       </c>
-      <c r="AQ179" s="10" t="n">
+      <c r="AQ179" s="11" t="n">
         <v>-57</v>
       </c>
-      <c r="BA179" s="9" t="n">
+      <c r="BA179" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="BB179" s="9" t="n">
+      <c r="BB179" s="10" t="n">
         <v>15</v>
       </c>
     </row>
@@ -9529,7 +9568,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E180" s="8" t="n">
+      <c r="E180" s="9" t="n">
         <v>1992</v>
       </c>
       <c r="F180" s="8" t="inlineStr">
@@ -9543,7 +9582,7 @@
       <c r="H180" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AN180" s="10" t="n">
+      <c r="AN180" s="11" t="n">
         <v>-83</v>
       </c>
     </row>
@@ -9566,7 +9605,7 @@
           <t>Cuba</t>
         </is>
       </c>
-      <c r="E181" s="8" t="n">
+      <c r="E181" s="9" t="n">
         <v>1989</v>
       </c>
       <c r="F181" s="8" t="inlineStr">
@@ -9580,19 +9619,19 @@
       <c r="H181" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="S181" s="10" t="n">
+      <c r="S181" s="11" t="n">
         <v>-8</v>
       </c>
-      <c r="AD181" s="10" t="n">
+      <c r="AD181" s="11" t="n">
         <v>-7</v>
       </c>
-      <c r="AE181" s="10" t="n">
+      <c r="AE181" s="11" t="n">
         <v>-20</v>
       </c>
-      <c r="AP181" s="10" t="n">
+      <c r="AP181" s="11" t="n">
         <v>-20</v>
       </c>
-      <c r="AQ181" s="10" t="n">
+      <c r="AQ181" s="11" t="n">
         <v>-32</v>
       </c>
     </row>
@@ -9615,7 +9654,7 @@
           <t>Panamá</t>
         </is>
       </c>
-      <c r="E182" s="8" t="n">
+      <c r="E182" s="9" t="n">
         <v>1989</v>
       </c>
       <c r="F182" s="8" t="inlineStr">
@@ -9629,10 +9668,10 @@
       <c r="H182" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="AL182" s="10" t="n">
+      <c r="AL182" s="11" t="n">
         <v>-28</v>
       </c>
-      <c r="AM182" s="10" t="n">
+      <c r="AM182" s="11" t="n">
         <v>-58</v>
       </c>
     </row>
@@ -9655,7 +9694,7 @@
           <t>Panamá</t>
         </is>
       </c>
-      <c r="E183" s="8" t="n">
+      <c r="E183" s="9" t="n">
         <v>1989</v>
       </c>
       <c r="F183" s="8" t="inlineStr">
@@ -9669,10 +9708,10 @@
       <c r="H183" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="AX183" s="10" t="n">
+      <c r="AX183" s="11" t="n">
         <v>-41</v>
       </c>
-      <c r="AY183" s="10" t="n">
+      <c r="AY183" s="11" t="n">
         <v>-45</v>
       </c>
     </row>
@@ -9695,7 +9734,7 @@
           <t>Estados Unidos</t>
         </is>
       </c>
-      <c r="E184" s="8" t="n">
+      <c r="E184" s="9" t="n">
         <v>1986</v>
       </c>
       <c r="F184" s="8" t="inlineStr">
@@ -9709,7 +9748,7 @@
       <c r="H184" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AA184" s="10" t="n">
+      <c r="AA184" s="11" t="n">
         <v>-89</v>
       </c>
     </row>
@@ -9732,7 +9771,7 @@
           <t>Cuba</t>
         </is>
       </c>
-      <c r="E185" s="8" t="n">
+      <c r="E185" s="9" t="n">
         <v>1985</v>
       </c>
       <c r="F185" s="8" t="inlineStr">
@@ -9746,10 +9785,10 @@
       <c r="H185" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="AD185" s="10" t="n">
+      <c r="AD185" s="11" t="n">
         <v>-41</v>
       </c>
-      <c r="AE185" s="10" t="n">
+      <c r="AE185" s="11" t="n">
         <v>-49</v>
       </c>
     </row>
@@ -9772,7 +9811,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E186" s="8" t="n">
+      <c r="E186" s="9" t="n">
         <v>1982</v>
       </c>
       <c r="F186" s="8" t="inlineStr">
@@ -9786,7 +9825,7 @@
       <c r="H186" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AN186" s="10" t="n">
+      <c r="AN186" s="11" t="n">
         <v>-93</v>
       </c>
     </row>
@@ -9809,7 +9848,7 @@
           <t>España</t>
         </is>
       </c>
-      <c r="E187" s="8" t="n">
+      <c r="E187" s="9" t="n">
         <v>1979</v>
       </c>
       <c r="F187" s="8" t="inlineStr">
@@ -9823,37 +9862,37 @@
       <c r="H187" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="N187" s="9" t="n">
+      <c r="N187" s="10" t="n">
         <v>62</v>
       </c>
-      <c r="U187" s="9" t="n">
+      <c r="U187" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="W187" s="10" t="n">
+      <c r="W187" s="11" t="n">
         <v>-212</v>
       </c>
-      <c r="Y187" s="9" t="n">
+      <c r="Y187" s="10" t="n">
         <v>208</v>
       </c>
-      <c r="AF187" s="9" t="n">
+      <c r="AF187" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="AH187" s="10" t="n">
+      <c r="AH187" s="11" t="n">
         <v>-44</v>
       </c>
-      <c r="AJ187" s="9" t="n">
+      <c r="AJ187" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="AK187" s="9" t="n">
+      <c r="AK187" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="AR187" s="9" t="n">
+      <c r="AR187" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="AT187" s="10" t="n">
+      <c r="AT187" s="11" t="n">
         <v>-63</v>
       </c>
-      <c r="AV187" s="10" t="n">
+      <c r="AV187" s="11" t="n">
         <v>-180</v>
       </c>
     </row>
@@ -9876,7 +9915,7 @@
           <t>Estados Unidos</t>
         </is>
       </c>
-      <c r="E188" s="8" t="n">
+      <c r="E188" s="9" t="n">
         <v>1977</v>
       </c>
       <c r="F188" s="8" t="inlineStr">
@@ -9890,10 +9929,10 @@
       <c r="H188" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="AA188" s="10" t="n">
+      <c r="AA188" s="11" t="n">
         <v>-72</v>
       </c>
-      <c r="AB188" s="10" t="n">
+      <c r="AB188" s="11" t="n">
         <v>-26</v>
       </c>
     </row>
@@ -9916,7 +9955,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E189" s="8" t="n">
+      <c r="E189" s="9" t="n">
         <v>1972</v>
       </c>
       <c r="F189" s="8" t="inlineStr">
@@ -9930,7 +9969,7 @@
       <c r="H189" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AN189" s="10" t="n">
+      <c r="AN189" s="11" t="n">
         <v>-103</v>
       </c>
     </row>
@@ -9953,7 +9992,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="E190" s="8" t="n">
+      <c r="E190" s="9" t="n">
         <v>1972</v>
       </c>
       <c r="F190" s="8" t="inlineStr">
@@ -9967,10 +10006,10 @@
       <c r="H190" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="AX190" s="10" t="n">
+      <c r="AX190" s="11" t="n">
         <v>-48</v>
       </c>
-      <c r="AY190" s="10" t="n">
+      <c r="AY190" s="11" t="n">
         <v>-55</v>
       </c>
     </row>
@@ -9993,7 +10032,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="E191" s="8" t="n">
+      <c r="E191" s="9" t="n">
         <v>1970</v>
       </c>
       <c r="F191" s="8" t="inlineStr">
@@ -10007,10 +10046,10 @@
       <c r="H191" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="AX191" s="10" t="n">
+      <c r="AX191" s="11" t="n">
         <v>-20</v>
       </c>
-      <c r="AY191" s="10" t="n">
+      <c r="AY191" s="11" t="n">
         <v>-85</v>
       </c>
     </row>
@@ -10033,7 +10072,7 @@
           <t>Guatemala</t>
         </is>
       </c>
-      <c r="E192" s="8" t="n">
+      <c r="E192" s="9" t="n">
         <v>1969</v>
       </c>
       <c r="F192" s="8" t="inlineStr">
@@ -10047,10 +10086,10 @@
       <c r="H192" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="AL192" s="10" t="n">
+      <c r="AL192" s="11" t="n">
         <v>-78</v>
       </c>
-      <c r="AM192" s="10" t="n">
+      <c r="AM192" s="11" t="n">
         <v>-28</v>
       </c>
     </row>
@@ -10073,7 +10112,7 @@
           <t>Cuba</t>
         </is>
       </c>
-      <c r="E193" s="8" t="n">
+      <c r="E193" s="9" t="n">
         <v>1967</v>
       </c>
       <c r="F193" s="8" t="inlineStr">
@@ -10087,10 +10126,10 @@
       <c r="H193" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="AD193" s="10" t="n">
+      <c r="AD193" s="11" t="n">
         <v>-49</v>
       </c>
-      <c r="AE193" s="10" t="n">
+      <c r="AE193" s="11" t="n">
         <v>-59</v>
       </c>
     </row>
@@ -10113,7 +10152,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E194" s="8" t="n">
+      <c r="E194" s="9" t="n">
         <v>1967</v>
       </c>
       <c r="F194" s="8" t="inlineStr">
@@ -10127,13 +10166,13 @@
       <c r="H194" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="AR194" s="9" t="n">
+      <c r="AR194" s="10" t="n">
         <v>170</v>
       </c>
-      <c r="AT194" s="10" t="n">
+      <c r="AT194" s="11" t="n">
         <v>-88</v>
       </c>
-      <c r="AV194" s="10" t="n">
+      <c r="AV194" s="11" t="n">
         <v>-190</v>
       </c>
     </row>
@@ -10156,7 +10195,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E195" s="8" t="n">
+      <c r="E195" s="9" t="n">
         <v>1966</v>
       </c>
       <c r="F195" s="8" t="inlineStr">
@@ -10170,34 +10209,34 @@
       <c r="H195" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="P195" s="9" t="n">
+      <c r="P195" s="10" t="n">
         <v>47</v>
       </c>
-      <c r="Q195" s="9" t="n">
+      <c r="Q195" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="U195" s="9" t="n">
+      <c r="U195" s="10" t="n">
         <v>56</v>
       </c>
-      <c r="V195" s="10" t="n">
+      <c r="V195" s="11" t="n">
         <v>-64</v>
       </c>
-      <c r="X195" s="10" t="n">
+      <c r="X195" s="11" t="n">
         <v>-81</v>
       </c>
-      <c r="AF195" s="10" t="n">
+      <c r="AF195" s="11" t="n">
         <v>-48</v>
       </c>
-      <c r="AG195" s="10" t="n">
+      <c r="AG195" s="11" t="n">
         <v>-28</v>
       </c>
-      <c r="AI195" s="10" t="n">
+      <c r="AI195" s="11" t="n">
         <v>-73</v>
       </c>
-      <c r="AL195" s="9" t="n">
+      <c r="AL195" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="AM195" s="9" t="n">
+      <c r="AM195" s="10" t="n">
         <v>32</v>
       </c>
     </row>
@@ -10220,7 +10259,7 @@
           <t>Francia</t>
         </is>
       </c>
-      <c r="E196" s="8" t="n">
+      <c r="E196" s="9" t="n">
         <v>1963</v>
       </c>
       <c r="F196" s="8" t="inlineStr">
@@ -10234,25 +10273,25 @@
       <c r="H196" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="U196" s="10" t="n">
+      <c r="U196" s="11" t="n">
         <v>-54</v>
       </c>
-      <c r="W196" s="9" t="n">
+      <c r="W196" s="10" t="n">
         <v>121</v>
       </c>
-      <c r="Y196" s="10" t="n">
+      <c r="Y196" s="11" t="n">
         <v>-194</v>
       </c>
-      <c r="Z196" s="10" t="n">
+      <c r="Z196" s="11" t="n">
         <v>-3</v>
       </c>
-      <c r="AW196" s="10" t="n">
+      <c r="AW196" s="11" t="n">
         <v>-54</v>
       </c>
-      <c r="AX196" s="9" t="n">
+      <c r="AX196" s="10" t="n">
         <v>47</v>
       </c>
-      <c r="AY196" s="9" t="n">
+      <c r="AY196" s="10" t="n">
         <v>25</v>
       </c>
     </row>
@@ -10275,7 +10314,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E197" s="8" t="n">
+      <c r="E197" s="9" t="n">
         <v>1962</v>
       </c>
       <c r="F197" s="8" t="inlineStr">
@@ -10289,7 +10328,7 @@
       <c r="H197" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AN197" s="10" t="n">
+      <c r="AN197" s="11" t="n">
         <v>-113</v>
       </c>
     </row>
@@ -10312,7 +10351,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E198" s="8" t="n">
+      <c r="E198" s="9" t="n">
         <v>1961</v>
       </c>
       <c r="F198" s="8" t="inlineStr">
@@ -10326,10 +10365,10 @@
       <c r="H198" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="BA198" s="10" t="n">
+      <c r="BA198" s="11" t="n">
         <v>-49</v>
       </c>
-      <c r="BB198" s="10" t="n">
+      <c r="BB198" s="11" t="n">
         <v>-65</v>
       </c>
     </row>
@@ -10352,7 +10391,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E199" s="8" t="n">
+      <c r="E199" s="9" t="n">
         <v>1952</v>
       </c>
       <c r="F199" s="8" t="inlineStr">
@@ -10366,7 +10405,7 @@
       <c r="H199" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AN199" s="10" t="n">
+      <c r="AN199" s="11" t="n">
         <v>-123</v>
       </c>
     </row>
@@ -10389,7 +10428,7 @@
           <t>Panamá</t>
         </is>
       </c>
-      <c r="E200" s="8" t="n">
+      <c r="E200" s="9" t="n">
         <v>1950</v>
       </c>
       <c r="F200" s="8" t="inlineStr">
@@ -10403,58 +10442,58 @@
       <c r="H200" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="I200" s="9" t="n">
+      <c r="I200" s="10" t="n">
         <v>78</v>
       </c>
-      <c r="K200" s="10" t="n">
+      <c r="K200" s="11" t="n">
         <v>-30</v>
       </c>
-      <c r="M200" s="10" t="n">
+      <c r="M200" s="11" t="n">
         <v>-27</v>
       </c>
-      <c r="R200" s="10" t="n">
+      <c r="R200" s="11" t="n">
         <v>-40</v>
       </c>
-      <c r="U200" s="10" t="n">
+      <c r="U200" s="11" t="n">
         <v>-66</v>
       </c>
-      <c r="V200" s="9" t="n">
+      <c r="V200" s="10" t="n">
         <v>130</v>
       </c>
-      <c r="X200" s="9" t="n">
+      <c r="X200" s="10" t="n">
         <v>148</v>
       </c>
-      <c r="AB200" s="9" t="n">
+      <c r="AB200" s="10" t="n">
         <v>73</v>
       </c>
-      <c r="AF200" s="10" t="n">
+      <c r="AF200" s="11" t="n">
         <v>-7</v>
       </c>
-      <c r="AH200" s="10" t="n">
+      <c r="AH200" s="11" t="n">
         <v>-8</v>
       </c>
-      <c r="AJ200" s="10" t="n">
+      <c r="AJ200" s="11" t="n">
         <v>-30</v>
       </c>
-      <c r="AL200" s="10" t="n">
+      <c r="AL200" s="11" t="n">
         <v>-9</v>
       </c>
-      <c r="AM200" s="10" t="n">
+      <c r="AM200" s="11" t="n">
         <v>-11</v>
       </c>
-      <c r="AR200" s="10" t="n">
+      <c r="AR200" s="11" t="n">
         <v>-36</v>
       </c>
-      <c r="AT200" s="10" t="n">
+      <c r="AT200" s="11" t="n">
         <v>-118</v>
       </c>
-      <c r="AV200" s="10" t="n">
+      <c r="AV200" s="11" t="n">
         <v>-21</v>
       </c>
-      <c r="AX200" s="10" t="n">
+      <c r="AX200" s="11" t="n">
         <v>-44</v>
       </c>
-      <c r="AY200" s="10" t="n">
+      <c r="AY200" s="11" t="n">
         <v>-105</v>
       </c>
     </row>
@@ -10477,7 +10516,7 @@
           <t>Francia</t>
         </is>
       </c>
-      <c r="E201" s="8" t="n">
+      <c r="E201" s="9" t="n">
         <v>1943</v>
       </c>
       <c r="F201" s="8" t="inlineStr">
@@ -10491,25 +10530,25 @@
       <c r="H201" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="U201" s="10" t="n">
+      <c r="U201" s="11" t="n">
         <v>-40</v>
       </c>
-      <c r="V201" s="9" t="n">
+      <c r="V201" s="10" t="n">
         <v>54</v>
       </c>
-      <c r="X201" s="9" t="n">
+      <c r="X201" s="10" t="n">
         <v>52</v>
       </c>
-      <c r="Z201" s="10" t="n">
+      <c r="Z201" s="11" t="n">
         <v>-10</v>
       </c>
-      <c r="AW201" s="10" t="n">
+      <c r="AW201" s="11" t="n">
         <v>-40</v>
       </c>
-      <c r="AX201" s="10" t="n">
+      <c r="AX201" s="11" t="n">
         <v>-73</v>
       </c>
-      <c r="AY201" s="10" t="n">
+      <c r="AY201" s="11" t="n">
         <v>-75</v>
       </c>
     </row>
@@ -10532,7 +10571,7 @@
           <t>México</t>
         </is>
       </c>
-      <c r="E202" s="8" t="n">
+      <c r="E202" s="9" t="n">
         <v>1942</v>
       </c>
       <c r="F202" s="8" t="inlineStr">
@@ -10546,31 +10585,31 @@
       <c r="H202" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="J202" s="9" t="n">
+      <c r="J202" s="10" t="n">
         <v>53</v>
       </c>
-      <c r="L202" s="9" t="n">
+      <c r="L202" s="10" t="n">
         <v>76</v>
       </c>
-      <c r="O202" s="9" t="n">
+      <c r="O202" s="10" t="n">
         <v>59</v>
       </c>
-      <c r="U202" s="10" t="n">
+      <c r="U202" s="11" t="n">
         <v>-10</v>
       </c>
-      <c r="W202" s="10" t="n">
+      <c r="W202" s="11" t="n">
         <v>-43</v>
       </c>
-      <c r="Y202" s="10" t="n">
+      <c r="Y202" s="11" t="n">
         <v>-185</v>
       </c>
-      <c r="AF202" s="10" t="n">
+      <c r="AF202" s="11" t="n">
         <v>-71</v>
       </c>
-      <c r="AG202" s="9" t="n">
+      <c r="AG202" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="AI202" s="10" t="n">
+      <c r="AI202" s="11" t="n">
         <v>-17</v>
       </c>
     </row>
@@ -10593,7 +10632,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E203" s="8" t="n">
+      <c r="E203" s="9" t="n">
         <v>1942</v>
       </c>
       <c r="F203" s="8" t="inlineStr">
@@ -10607,7 +10646,7 @@
       <c r="H203" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AN203" s="10" t="n">
+      <c r="AN203" s="11" t="n">
         <v>-133</v>
       </c>
     </row>
@@ -10630,7 +10669,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E204" s="8" t="n">
+      <c r="E204" s="9" t="n">
         <v>1932</v>
       </c>
       <c r="F204" s="8" t="inlineStr">
@@ -10644,7 +10683,7 @@
       <c r="H204" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AN204" s="10" t="n">
+      <c r="AN204" s="11" t="n">
         <v>-143</v>
       </c>
     </row>
@@ -10667,7 +10706,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="E205" s="8" t="n">
+      <c r="E205" s="9" t="n">
         <v>1931</v>
       </c>
       <c r="F205" s="8" t="inlineStr">
@@ -10681,16 +10720,16 @@
       <c r="H205" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="AL205" s="9" t="n">
+      <c r="AL205" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="AM205" s="10" t="n">
+      <c r="AM205" s="11" t="n">
         <v>-67</v>
       </c>
-      <c r="AX205" s="9" t="n">
+      <c r="AX205" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="AY205" s="10" t="n">
+      <c r="AY205" s="11" t="n">
         <v>-95</v>
       </c>
     </row>
@@ -10713,7 +10752,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E206" s="8" t="n">
+      <c r="E206" s="9" t="n">
         <v>1926</v>
       </c>
       <c r="F206" s="8" t="inlineStr">
@@ -10727,43 +10766,43 @@
       <c r="H206" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="I206" s="10" t="n">
+      <c r="I206" s="11" t="n">
         <v>-51</v>
       </c>
-      <c r="K206" s="9" t="n">
+      <c r="K206" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="M206" s="10" t="n">
+      <c r="M206" s="11" t="n">
         <v>-42</v>
       </c>
-      <c r="O206" s="10" t="n">
+      <c r="O206" s="11" t="n">
         <v>-96</v>
       </c>
-      <c r="U206" s="9" t="n">
+      <c r="U206" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W206" s="9" t="n">
+      <c r="W206" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="Y206" s="9" t="n">
+      <c r="Y206" s="10" t="n">
         <v>94</v>
       </c>
-      <c r="AD206" s="9" t="n">
+      <c r="AD206" s="10" t="n">
         <v>70</v>
       </c>
-      <c r="AE206" s="9" t="n">
+      <c r="AE206" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="AK206" s="10" t="n">
+      <c r="AK206" s="11" t="n">
         <v>-3</v>
       </c>
-      <c r="AR206" s="10" t="n">
+      <c r="AR206" s="11" t="n">
         <v>-184</v>
       </c>
-      <c r="AT206" s="9" t="n">
+      <c r="AT206" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="AV206" s="10" t="n">
+      <c r="AV206" s="11" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -10786,7 +10825,7 @@
           <t>Chile</t>
         </is>
       </c>
-      <c r="E207" s="8" t="n">
+      <c r="E207" s="9" t="n">
         <v>1926</v>
       </c>
       <c r="F207" s="8" t="inlineStr">
@@ -10800,10 +10839,10 @@
       <c r="H207" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="BA207" s="10" t="n">
+      <c r="BA207" s="11" t="n">
         <v>-64</v>
       </c>
-      <c r="BB207" s="10" t="n">
+      <c r="BB207" s="11" t="n">
         <v>-85</v>
       </c>
     </row>
@@ -10826,7 +10865,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E208" s="8" t="n">
+      <c r="E208" s="9" t="n">
         <v>1924</v>
       </c>
       <c r="F208" s="8" t="inlineStr">
@@ -10840,16 +10879,16 @@
       <c r="H208" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="U208" s="9" t="n">
+      <c r="U208" s="10" t="n">
         <v>95</v>
       </c>
-      <c r="W208" s="10" t="n">
+      <c r="W208" s="11" t="n">
         <v>-145</v>
       </c>
-      <c r="Y208" s="9" t="n">
+      <c r="Y208" s="10" t="n">
         <v>62</v>
       </c>
-      <c r="AN208" s="10" t="n">
+      <c r="AN208" s="11" t="n">
         <v>-163</v>
       </c>
     </row>
@@ -10872,7 +10911,7 @@
           <t>España</t>
         </is>
       </c>
-      <c r="E209" s="8" t="n">
+      <c r="E209" s="9" t="n">
         <v>1922</v>
       </c>
       <c r="F209" s="8" t="inlineStr">
@@ -10886,16 +10925,16 @@
       <c r="H209" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="N209" s="9" t="n">
+      <c r="N209" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U209" s="10" t="n">
+      <c r="U209" s="11" t="n">
         <v>-29</v>
       </c>
-      <c r="W209" s="9" t="n">
+      <c r="W209" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="Y209" s="10" t="n">
+      <c r="Y209" s="11" t="n">
         <v>-170</v>
       </c>
     </row>
@@ -10918,7 +10957,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E210" s="8" t="n">
+      <c r="E210" s="9" t="n">
         <v>1915</v>
       </c>
       <c r="F210" s="8" t="inlineStr">
@@ -10932,16 +10971,16 @@
       <c r="H210" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="U210" s="10" t="n">
+      <c r="U210" s="11" t="n">
         <v>-86</v>
       </c>
-      <c r="V210" s="9" t="n">
+      <c r="V210" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="X210" s="9" t="n">
+      <c r="X210" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="AN210" s="10" t="n">
+      <c r="AN210" s="11" t="n">
         <v>-153</v>
       </c>
     </row>
@@ -10964,7 +11003,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E211" s="8" t="n">
+      <c r="E211" s="9" t="n">
         <v>1907</v>
       </c>
       <c r="F211" s="8" t="inlineStr">
@@ -10978,19 +11017,19 @@
       <c r="H211" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="J211" s="10" t="n">
+      <c r="J211" s="11" t="n">
         <v>-35</v>
       </c>
-      <c r="L211" s="10" t="n">
+      <c r="L211" s="11" t="n">
         <v>-20</v>
       </c>
-      <c r="U211" s="9" t="n">
+      <c r="U211" s="10" t="n">
         <v>51</v>
       </c>
-      <c r="V211" s="10" t="n">
+      <c r="V211" s="11" t="n">
         <v>-71</v>
       </c>
-      <c r="X211" s="10" t="n">
+      <c r="X211" s="11" t="n">
         <v>-93</v>
       </c>
     </row>
@@ -11013,7 +11052,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E212" s="8" t="n">
+      <c r="E212" s="9" t="n">
         <v>1904</v>
       </c>
       <c r="F212" s="8" t="inlineStr">
@@ -11027,34 +11066,34 @@
       <c r="H212" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="R212" s="10" t="n">
+      <c r="R212" s="11" t="n">
         <v>-12</v>
       </c>
-      <c r="T212" s="9" t="n">
+      <c r="T212" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="U212" s="9" t="n">
+      <c r="U212" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="V212" s="10" t="n">
+      <c r="V212" s="11" t="n">
         <v>-82</v>
       </c>
-      <c r="X212" s="10" t="n">
+      <c r="X212" s="11" t="n">
         <v>-108</v>
       </c>
-      <c r="AA212" s="9" t="n">
+      <c r="AA212" s="10" t="n">
         <v>61</v>
       </c>
-      <c r="AO212" s="10" t="n">
+      <c r="AO212" s="11" t="n">
         <v>-56</v>
       </c>
-      <c r="AS212" s="9" t="n">
+      <c r="AS212" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="AU212" s="10" t="n">
+      <c r="AU212" s="11" t="n">
         <v>-13</v>
       </c>
-      <c r="AZ212" s="10" t="n">
+      <c r="AZ212" s="11" t="n">
         <v>-25</v>
       </c>
     </row>
@@ -11077,7 +11116,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E213" s="8" t="n">
+      <c r="E213" s="9" t="n">
         <v>1902</v>
       </c>
       <c r="F213" s="8" t="inlineStr">
@@ -11091,7 +11130,7 @@
       <c r="H213" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AN213" s="10" t="n">
+      <c r="AN213" s="11" t="n">
         <v>-173</v>
       </c>
     </row>
@@ -11114,7 +11153,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E214" s="8" t="n">
+      <c r="E214" s="9" t="n">
         <v>1900</v>
       </c>
       <c r="F214" s="8" t="inlineStr">
@@ -11128,13 +11167,13 @@
       <c r="H214" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="AR214" s="10" t="n">
+      <c r="AR214" s="11" t="n">
         <v>-70</v>
       </c>
-      <c r="AT214" s="10" t="n">
+      <c r="AT214" s="11" t="n">
         <v>-185</v>
       </c>
-      <c r="AV214" s="9" t="n">
+      <c r="AV214" s="10" t="n">
         <v>80</v>
       </c>
     </row>
@@ -11157,7 +11196,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E215" s="8" t="n">
+      <c r="E215" s="9" t="n">
         <v>1892</v>
       </c>
       <c r="F215" s="8" t="inlineStr">
@@ -11171,7 +11210,7 @@
       <c r="H215" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AN215" s="10" t="n">
+      <c r="AN215" s="11" t="n">
         <v>-183</v>
       </c>
     </row>
@@ -11194,7 +11233,7 @@
           <t>Estados Unidos</t>
         </is>
       </c>
-      <c r="E216" s="8" t="n">
+      <c r="E216" s="9" t="n">
         <v>1881</v>
       </c>
       <c r="F216" s="8" t="inlineStr">
@@ -11208,16 +11247,16 @@
       <c r="H216" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="U216" s="9" t="n">
+      <c r="U216" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="V216" s="9" t="n">
+      <c r="V216" s="10" t="n">
         <v>102</v>
       </c>
-      <c r="Y216" s="10" t="n">
+      <c r="Y216" s="11" t="n">
         <v>-330</v>
       </c>
-      <c r="AA216" s="9" t="n">
+      <c r="AA216" s="10" t="n">
         <v>21</v>
       </c>
     </row>
@@ -11240,7 +11279,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E217" s="8" t="n">
+      <c r="E217" s="9" t="n">
         <v>1875</v>
       </c>
       <c r="F217" s="8" t="inlineStr">
@@ -11254,13 +11293,13 @@
       <c r="H217" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="AR217" s="9" t="n">
+      <c r="AR217" s="10" t="n">
         <v>64</v>
       </c>
-      <c r="AT217" s="10" t="n">
+      <c r="AT217" s="11" t="n">
         <v>-64</v>
       </c>
-      <c r="AV217" s="10" t="n">
+      <c r="AV217" s="11" t="n">
         <v>-200</v>
       </c>
     </row>
@@ -11283,7 +11322,7 @@
           <t>Panamá</t>
         </is>
       </c>
-      <c r="E218" s="8" t="n">
+      <c r="E218" s="9" t="n">
         <v>1872</v>
       </c>
       <c r="F218" s="8" t="inlineStr">
@@ -11297,10 +11336,10 @@
       <c r="H218" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="AL218" s="10" t="n">
+      <c r="AL218" s="11" t="n">
         <v>-75</v>
       </c>
-      <c r="AM218" s="10" t="n">
+      <c r="AM218" s="11" t="n">
         <v>-128</v>
       </c>
     </row>
@@ -11323,7 +11362,7 @@
           <t>Panamá</t>
         </is>
       </c>
-      <c r="E219" s="8" t="n">
+      <c r="E219" s="9" t="n">
         <v>1869</v>
       </c>
       <c r="F219" s="8" t="inlineStr">
@@ -11337,10 +11376,10 @@
       <c r="H219" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="AL219" s="10" t="n">
+      <c r="AL219" s="11" t="n">
         <v>-89</v>
       </c>
-      <c r="AM219" s="10" t="n">
+      <c r="AM219" s="11" t="n">
         <v>-118</v>
       </c>
     </row>
@@ -11363,7 +11402,7 @@
           <t>Cuba</t>
         </is>
       </c>
-      <c r="E220" s="8" t="n">
+      <c r="E220" s="9" t="n">
         <v>1868</v>
       </c>
       <c r="F220" s="8" t="inlineStr">
@@ -11377,19 +11416,19 @@
       <c r="H220" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="S220" s="10" t="n">
+      <c r="S220" s="11" t="n">
         <v>-18</v>
       </c>
-      <c r="AP220" s="10" t="n">
+      <c r="AP220" s="11" t="n">
         <v>-22</v>
       </c>
-      <c r="AQ220" s="10" t="n">
+      <c r="AQ220" s="11" t="n">
         <v>-36</v>
       </c>
-      <c r="BA220" s="10" t="n">
+      <c r="BA220" s="11" t="n">
         <v>-56</v>
       </c>
-      <c r="BB220" s="10" t="n">
+      <c r="BB220" s="11" t="n">
         <v>-75</v>
       </c>
     </row>
@@ -11412,7 +11451,7 @@
           <t>España</t>
         </is>
       </c>
-      <c r="E221" s="8" t="n">
+      <c r="E221" s="9" t="n">
         <v>1866</v>
       </c>
       <c r="F221" s="8" t="inlineStr">
@@ -11426,13 +11465,13 @@
       <c r="H221" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="U221" s="10" t="n">
+      <c r="U221" s="11" t="n">
         <v>-70</v>
       </c>
-      <c r="W221" s="10" t="n">
+      <c r="W221" s="11" t="n">
         <v>-109</v>
       </c>
-      <c r="Y221" s="10" t="n">
+      <c r="Y221" s="11" t="n">
         <v>-30</v>
       </c>
     </row>
@@ -11455,7 +11494,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E222" s="8" t="n">
+      <c r="E222" s="9" t="n">
         <v>1860</v>
       </c>
       <c r="F222" s="8" t="inlineStr">
@@ -11469,16 +11508,16 @@
       <c r="H222" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="U222" s="10" t="n">
+      <c r="U222" s="11" t="n">
         <v>-116</v>
       </c>
-      <c r="W222" s="10" t="n">
+      <c r="W222" s="11" t="n">
         <v>-160</v>
       </c>
-      <c r="Y222" s="9" t="n">
+      <c r="Y222" s="10" t="n">
         <v>54</v>
       </c>
-      <c r="AN222" s="9" t="n">
+      <c r="AN222" s="10" t="n">
         <v>7</v>
       </c>
     </row>
@@ -11501,7 +11540,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E223" s="8" t="n">
+      <c r="E223" s="9" t="n">
         <v>1856</v>
       </c>
       <c r="F223" s="8" t="inlineStr">
@@ -11515,16 +11554,16 @@
       <c r="H223" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="U223" s="9" t="n">
+      <c r="U223" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="W223" s="9" t="n">
+      <c r="W223" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="Y223" s="10" t="n">
+      <c r="Y223" s="11" t="n">
         <v>-267</v>
       </c>
-      <c r="AN223" s="10" t="n">
+      <c r="AN223" s="11" t="n">
         <v>-3</v>
       </c>
     </row>
@@ -11547,7 +11586,7 @@
           <t>México</t>
         </is>
       </c>
-      <c r="E224" s="8" t="n">
+      <c r="E224" s="9" t="n">
         <v>1855</v>
       </c>
       <c r="F224" s="8" t="inlineStr">
@@ -11561,31 +11600,31 @@
       <c r="H224" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="O224" s="9" t="n">
+      <c r="O224" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="T224" s="9" t="n">
+      <c r="T224" s="10" t="n">
         <v>63</v>
       </c>
-      <c r="U224" s="10" t="n">
+      <c r="U224" s="11" t="n">
         <v>-113</v>
       </c>
-      <c r="W224" s="10" t="n">
+      <c r="W224" s="11" t="n">
         <v>-20</v>
       </c>
-      <c r="Y224" s="9" t="n">
+      <c r="Y224" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="AA224" s="9" t="n">
+      <c r="AA224" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="AF224" s="10" t="n">
+      <c r="AF224" s="11" t="n">
         <v>-44</v>
       </c>
-      <c r="AH224" s="10" t="n">
+      <c r="AH224" s="11" t="n">
         <v>-100</v>
       </c>
-      <c r="AJ224" s="10" t="n">
+      <c r="AJ224" s="11" t="n">
         <v>-82</v>
       </c>
     </row>
@@ -11608,7 +11647,7 @@
           <t>Panamá</t>
         </is>
       </c>
-      <c r="E225" s="8" t="n">
+      <c r="E225" s="9" t="n">
         <v>1845</v>
       </c>
       <c r="F225" s="8" t="inlineStr">
@@ -11622,10 +11661,10 @@
       <c r="H225" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="AL225" s="10" t="n">
+      <c r="AL225" s="11" t="n">
         <v>-92</v>
       </c>
-      <c r="AM225" s="10" t="n">
+      <c r="AM225" s="11" t="n">
         <v>-138</v>
       </c>
     </row>
@@ -11648,7 +11687,7 @@
           <t>España</t>
         </is>
       </c>
-      <c r="E226" s="8" t="n">
+      <c r="E226" s="9" t="n">
         <v>1835</v>
       </c>
       <c r="F226" s="8" t="inlineStr">
@@ -11662,16 +11701,16 @@
       <c r="H226" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="U226" s="10" t="n">
+      <c r="U226" s="11" t="n">
         <v>-187</v>
       </c>
-      <c r="W226" s="10" t="n">
+      <c r="W226" s="11" t="n">
         <v>-145</v>
       </c>
-      <c r="Y226" s="9" t="n">
+      <c r="Y226" s="10" t="n">
         <v>65</v>
       </c>
-      <c r="AN226" s="9" t="n">
+      <c r="AN226" s="10" t="n">
         <v>27</v>
       </c>
     </row>
@@ -11694,7 +11733,7 @@
           <t>España</t>
         </is>
       </c>
-      <c r="E227" s="8" t="n">
+      <c r="E227" s="9" t="n">
         <v>1833</v>
       </c>
       <c r="F227" s="8" t="inlineStr">
@@ -11708,19 +11747,19 @@
       <c r="H227" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N227" s="9" t="n">
+      <c r="N227" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="U227" s="10" t="n">
+      <c r="U227" s="11" t="n">
         <v>-233</v>
       </c>
-      <c r="W227" s="10" t="n">
+      <c r="W227" s="11" t="n">
         <v>-248</v>
       </c>
-      <c r="Y227" s="9" t="n">
+      <c r="Y227" s="10" t="n">
         <v>212</v>
       </c>
-      <c r="AK227" s="10" t="n">
+      <c r="AK227" s="11" t="n">
         <v>-24</v>
       </c>
     </row>
@@ -11743,7 +11782,7 @@
           <t>Costa Rica</t>
         </is>
       </c>
-      <c r="E228" s="8" t="n">
+      <c r="E228" s="9" t="n">
         <v>1830</v>
       </c>
       <c r="F228" s="8" t="inlineStr">
@@ -11757,13 +11796,13 @@
       <c r="H228" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="AF228" s="10" t="n">
+      <c r="AF228" s="11" t="n">
         <v>-64</v>
       </c>
-      <c r="AH228" s="10" t="n">
+      <c r="AH228" s="11" t="n">
         <v>-69</v>
       </c>
-      <c r="AJ228" s="10" t="n">
+      <c r="AJ228" s="11" t="n">
         <v>-112</v>
       </c>
     </row>
@@ -11786,7 +11825,7 @@
           <t>Panamá</t>
         </is>
       </c>
-      <c r="E229" s="8" t="n">
+      <c r="E229" s="9" t="n">
         <v>1823</v>
       </c>
       <c r="F229" s="8" t="inlineStr">
@@ -11800,25 +11839,25 @@
       <c r="H229" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="AL229" s="9" t="n">
+      <c r="AL229" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="AM229" s="10" t="n">
+      <c r="AM229" s="11" t="n">
         <v>-6</v>
       </c>
-      <c r="AR229" s="10" t="n">
+      <c r="AR229" s="11" t="n">
         <v>-47</v>
       </c>
-      <c r="AT229" s="10" t="n">
+      <c r="AT229" s="11" t="n">
         <v>-73</v>
       </c>
-      <c r="AV229" s="9" t="n">
+      <c r="AV229" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="AX229" s="10" t="n">
+      <c r="AX229" s="11" t="n">
         <v>-85</v>
       </c>
-      <c r="AY229" s="10" t="n">
+      <c r="AY229" s="11" t="n">
         <v>-65</v>
       </c>
     </row>
@@ -11841,7 +11880,7 @@
           <t>Estados Unidos</t>
         </is>
       </c>
-      <c r="E230" s="8" t="n">
+      <c r="E230" s="9" t="n">
         <v>1822</v>
       </c>
       <c r="F230" s="8" t="inlineStr">
@@ -11855,19 +11894,19 @@
       <c r="H230" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="O230" s="10" t="n">
+      <c r="O230" s="11" t="n">
         <v>-14</v>
       </c>
-      <c r="U230" s="9" t="n">
+      <c r="U230" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="W230" s="10" t="n">
+      <c r="W230" s="11" t="n">
         <v>-22</v>
       </c>
-      <c r="Y230" s="10" t="n">
+      <c r="Y230" s="11" t="n">
         <v>-221</v>
       </c>
-      <c r="AA230" s="9" t="n">
+      <c r="AA230" s="10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11890,7 +11929,7 @@
           <t>Japón</t>
         </is>
       </c>
-      <c r="E231" s="8" t="n">
+      <c r="E231" s="9" t="n">
         <v>1807</v>
       </c>
       <c r="F231" s="8" t="inlineStr">
@@ -11904,25 +11943,25 @@
       <c r="H231" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="I231" s="10" t="n">
+      <c r="I231" s="11" t="n">
         <v>-22</v>
       </c>
-      <c r="K231" s="10" t="n">
+      <c r="K231" s="11" t="n">
         <v>-55</v>
       </c>
-      <c r="M231" s="10" t="n">
+      <c r="M231" s="11" t="n">
         <v>-91</v>
       </c>
-      <c r="U231" s="10" t="n">
+      <c r="U231" s="11" t="n">
         <v>-140</v>
       </c>
-      <c r="V231" s="9" t="n">
+      <c r="V231" s="10" t="n">
         <v>29</v>
       </c>
-      <c r="X231" s="9" t="n">
+      <c r="X231" s="10" t="n">
         <v>104</v>
       </c>
-      <c r="AK231" s="10" t="n">
+      <c r="AK231" s="11" t="n">
         <v>-94</v>
       </c>
     </row>
@@ -11945,7 +11984,7 @@
           <t>Costa Rica</t>
         </is>
       </c>
-      <c r="E232" s="8" t="n">
+      <c r="E232" s="9" t="n">
         <v>1803</v>
       </c>
       <c r="F232" s="8" t="inlineStr">
@@ -11959,16 +11998,16 @@
       <c r="H232" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="I232" s="10" t="n">
+      <c r="I232" s="11" t="n">
         <v>-60</v>
       </c>
-      <c r="K232" s="10" t="n">
+      <c r="K232" s="11" t="n">
         <v>-83</v>
       </c>
-      <c r="M232" s="10" t="n">
+      <c r="M232" s="11" t="n">
         <v>-76</v>
       </c>
-      <c r="T232" s="10" t="n">
+      <c r="T232" s="11" t="n">
         <v>-54</v>
       </c>
     </row>
@@ -11991,7 +12030,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E233" s="8" t="n">
+      <c r="E233" s="9" t="n">
         <v>1802</v>
       </c>
       <c r="F233" s="8" t="inlineStr">
@@ -12005,16 +12044,16 @@
       <c r="H233" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="U233" s="9" t="n">
+      <c r="U233" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="W233" s="10" t="n">
+      <c r="W233" s="11" t="n">
         <v>-143</v>
       </c>
-      <c r="Y233" s="10" t="n">
+      <c r="Y233" s="11" t="n">
         <v>-118</v>
       </c>
-      <c r="AN233" s="10" t="n">
+      <c r="AN233" s="11" t="n">
         <v>-13</v>
       </c>
     </row>
@@ -12037,7 +12076,7 @@
           <t>México</t>
         </is>
       </c>
-      <c r="E234" s="8" t="n">
+      <c r="E234" s="9" t="n">
         <v>1789</v>
       </c>
       <c r="F234" s="8" t="inlineStr">
@@ -12051,13 +12090,13 @@
       <c r="H234" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="AF234" s="10" t="n">
+      <c r="AF234" s="11" t="n">
         <v>-62</v>
       </c>
-      <c r="AH234" s="10" t="n">
+      <c r="AH234" s="11" t="n">
         <v>-92</v>
       </c>
-      <c r="AJ234" s="10" t="n">
+      <c r="AJ234" s="11" t="n">
         <v>-132</v>
       </c>
     </row>
@@ -12080,7 +12119,7 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="E235" s="8" t="n">
+      <c r="E235" s="9" t="n">
         <v>1773</v>
       </c>
       <c r="F235" s="8" t="inlineStr">
@@ -12094,13 +12133,13 @@
       <c r="H235" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="AR235" s="10" t="n">
+      <c r="AR235" s="11" t="n">
         <v>-68</v>
       </c>
-      <c r="AT235" s="10" t="n">
+      <c r="AT235" s="11" t="n">
         <v>-114</v>
       </c>
-      <c r="AV235" s="10" t="n">
+      <c r="AV235" s="11" t="n">
         <v>-120</v>
       </c>
     </row>
@@ -12123,7 +12162,7 @@
           <t>Estados Unidos</t>
         </is>
       </c>
-      <c r="E236" s="8" t="n">
+      <c r="E236" s="9" t="n">
         <v>1757</v>
       </c>
       <c r="F236" s="8" t="inlineStr">
@@ -12137,13 +12176,13 @@
       <c r="H236" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="AR236" s="10" t="n">
+      <c r="AR236" s="11" t="n">
         <v>-109</v>
       </c>
-      <c r="AT236" s="9" t="n">
+      <c r="AT236" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AV236" s="10" t="n">
+      <c r="AV236" s="11" t="n">
         <v>-210</v>
       </c>
     </row>
@@ -12166,7 +12205,7 @@
           <t>Chile</t>
         </is>
       </c>
-      <c r="E237" s="8" t="n">
+      <c r="E237" s="9" t="n">
         <v>1707</v>
       </c>
       <c r="F237" s="8" t="inlineStr">
@@ -12180,25 +12219,25 @@
       <c r="H237" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="I237" s="10" t="n">
+      <c r="I237" s="11" t="n">
         <v>-22</v>
       </c>
-      <c r="K237" s="10" t="n">
+      <c r="K237" s="11" t="n">
         <v>-2</v>
       </c>
-      <c r="M237" s="10" t="n">
+      <c r="M237" s="11" t="n">
         <v>-25</v>
       </c>
-      <c r="U237" s="10" t="n">
+      <c r="U237" s="11" t="n">
         <v>-33</v>
       </c>
-      <c r="W237" s="10" t="n">
+      <c r="W237" s="11" t="n">
         <v>-31</v>
       </c>
-      <c r="Y237" s="10" t="n">
+      <c r="Y237" s="11" t="n">
         <v>-194</v>
       </c>
-      <c r="AC237" s="10" t="n">
+      <c r="AC237" s="11" t="n">
         <v>-60</v>
       </c>
     </row>
@@ -12221,7 +12260,7 @@
           <t>México</t>
         </is>
       </c>
-      <c r="E238" s="8" t="n">
+      <c r="E238" s="9" t="n">
         <v>1691</v>
       </c>
       <c r="F238" s="8" t="inlineStr">
@@ -12235,25 +12274,25 @@
       <c r="H238" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="O238" s="9" t="n">
+      <c r="O238" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="U238" s="10" t="n">
+      <c r="U238" s="11" t="n">
         <v>-48</v>
       </c>
-      <c r="W238" s="10" t="n">
+      <c r="W238" s="11" t="n">
         <v>-124</v>
       </c>
-      <c r="Y238" s="10" t="n">
+      <c r="Y238" s="11" t="n">
         <v>-199</v>
       </c>
-      <c r="AF238" s="9" t="n">
+      <c r="AF238" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="AG238" s="10" t="n">
+      <c r="AG238" s="11" t="n">
         <v>-12</v>
       </c>
-      <c r="AI238" s="10" t="n">
+      <c r="AI238" s="11" t="n">
         <v>-27</v>
       </c>
     </row>
@@ -12276,7 +12315,7 @@
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="E239" s="8" t="n">
+      <c r="E239" s="9" t="n">
         <v>1678</v>
       </c>
       <c r="F239" s="8" t="inlineStr">
@@ -12290,28 +12329,28 @@
       <c r="H239" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="I239" s="10" t="n">
+      <c r="I239" s="11" t="n">
         <v>-5</v>
       </c>
-      <c r="K239" s="10" t="n">
+      <c r="K239" s="11" t="n">
         <v>-5</v>
       </c>
-      <c r="M239" s="10" t="n">
+      <c r="M239" s="11" t="n">
         <v>-4</v>
       </c>
-      <c r="P239" s="9" t="n">
+      <c r="P239" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q239" s="9" t="n">
+      <c r="Q239" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="U239" s="10" t="n">
+      <c r="U239" s="11" t="n">
         <v>-5</v>
       </c>
-      <c r="W239" s="10" t="n">
+      <c r="W239" s="11" t="n">
         <v>-106</v>
       </c>
-      <c r="Y239" s="10" t="n">
+      <c r="Y239" s="11" t="n">
         <v>-280</v>
       </c>
     </row>
@@ -12334,7 +12373,7 @@
           <t>Panamá</t>
         </is>
       </c>
-      <c r="E240" s="8" t="n">
+      <c r="E240" s="9" t="n">
         <v>1671</v>
       </c>
       <c r="F240" s="8" t="inlineStr">
@@ -12348,43 +12387,43 @@
       <c r="H240" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="S240" s="10" t="n">
+      <c r="S240" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="U240" s="10" t="n">
+      <c r="U240" s="11" t="n">
         <v>-130</v>
       </c>
-      <c r="W240" s="10" t="n">
+      <c r="W240" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="Y240" s="9" t="n">
+      <c r="Y240" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="AL240" s="10" t="n">
+      <c r="AL240" s="11" t="n">
         <v>-7</v>
       </c>
-      <c r="AM240" s="9" t="n">
+      <c r="AM240" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="AP240" s="10" t="n">
+      <c r="AP240" s="11" t="n">
         <v>-9</v>
       </c>
-      <c r="AQ240" s="9" t="n">
+      <c r="AQ240" s="10" t="n">
         <v>47</v>
       </c>
-      <c r="AR240" s="10" t="n">
+      <c r="AR240" s="11" t="n">
         <v>-57</v>
       </c>
-      <c r="AT240" s="10" t="n">
+      <c r="AT240" s="11" t="n">
         <v>-114</v>
       </c>
-      <c r="AV240" s="10" t="n">
+      <c r="AV240" s="11" t="n">
         <v>-123</v>
       </c>
-      <c r="BA240" s="10" t="n">
+      <c r="BA240" s="11" t="n">
         <v>-21</v>
       </c>
-      <c r="BB240" s="10" t="n">
+      <c r="BB240" s="11" t="n">
         <v>-55</v>
       </c>
     </row>
@@ -12407,7 +12446,7 @@
           <t>México</t>
         </is>
       </c>
-      <c r="E241" s="8" t="n">
+      <c r="E241" s="9" t="n">
         <v>1666</v>
       </c>
       <c r="F241" s="8" t="inlineStr">
@@ -12421,22 +12460,22 @@
       <c r="H241" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="U241" s="10" t="n">
+      <c r="U241" s="11" t="n">
         <v>-83</v>
       </c>
-      <c r="W241" s="10" t="n">
+      <c r="W241" s="11" t="n">
         <v>-123</v>
       </c>
-      <c r="Y241" s="10" t="n">
+      <c r="Y241" s="11" t="n">
         <v>-82</v>
       </c>
-      <c r="AF241" s="10" t="n">
+      <c r="AF241" s="11" t="n">
         <v>-21</v>
       </c>
-      <c r="AG241" s="10" t="n">
+      <c r="AG241" s="11" t="n">
         <v>-33</v>
       </c>
-      <c r="AI241" s="10" t="n">
+      <c r="AI241" s="11" t="n">
         <v>-67</v>
       </c>
     </row>
@@ -12459,7 +12498,7 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="E242" s="8" t="n">
+      <c r="E242" s="9" t="n">
         <v>1644</v>
       </c>
       <c r="F242" s="8" t="inlineStr">
@@ -12473,13 +12512,13 @@
       <c r="H242" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="U242" s="10" t="n">
+      <c r="U242" s="11" t="n">
         <v>-81</v>
       </c>
-      <c r="W242" s="10" t="n">
+      <c r="W242" s="11" t="n">
         <v>-61</v>
       </c>
-      <c r="Y242" s="10" t="n">
+      <c r="Y242" s="11" t="n">
         <v>-290</v>
       </c>
     </row>
@@ -12502,7 +12541,7 @@
           <t>México</t>
         </is>
       </c>
-      <c r="E243" s="8" t="n">
+      <c r="E243" s="9" t="n">
         <v>1643</v>
       </c>
       <c r="F243" s="8" t="inlineStr">
@@ -12516,22 +12555,22 @@
       <c r="H243" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="U243" s="10" t="n">
+      <c r="U243" s="11" t="n">
         <v>-12</v>
       </c>
-      <c r="W243" s="10" t="n">
+      <c r="W243" s="11" t="n">
         <v>-109</v>
       </c>
-      <c r="Y243" s="10" t="n">
+      <c r="Y243" s="11" t="n">
         <v>-202</v>
       </c>
-      <c r="AF243" s="10" t="n">
+      <c r="AF243" s="11" t="n">
         <v>-12</v>
       </c>
-      <c r="AG243" s="10" t="n">
+      <c r="AG243" s="11" t="n">
         <v>-59</v>
       </c>
-      <c r="AI243" s="10" t="n">
+      <c r="AI243" s="11" t="n">
         <v>-37</v>
       </c>
     </row>
@@ -12554,7 +12593,7 @@
           <t>España</t>
         </is>
       </c>
-      <c r="E244" s="8" t="n">
+      <c r="E244" s="9" t="n">
         <v>1584</v>
       </c>
       <c r="F244" s="8" t="inlineStr">
@@ -12568,16 +12607,16 @@
       <c r="H244" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="U244" s="10" t="n">
+      <c r="U244" s="11" t="n">
         <v>-72</v>
       </c>
-      <c r="W244" s="10" t="n">
+      <c r="W244" s="11" t="n">
         <v>-91</v>
       </c>
-      <c r="Y244" s="10" t="n">
+      <c r="Y244" s="11" t="n">
         <v>-243</v>
       </c>
-      <c r="AK244" s="10" t="n">
+      <c r="AK244" s="11" t="n">
         <v>-84</v>
       </c>
     </row>
@@ -12600,7 +12639,7 @@
           <t>México</t>
         </is>
       </c>
-      <c r="E245" s="8" t="n">
+      <c r="E245" s="9" t="n">
         <v>1557</v>
       </c>
       <c r="F245" s="8" t="inlineStr">
@@ -12614,22 +12653,22 @@
       <c r="H245" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="U245" s="10" t="n">
+      <c r="U245" s="11" t="n">
         <v>-72</v>
       </c>
-      <c r="W245" s="10" t="n">
+      <c r="W245" s="11" t="n">
         <v>-103</v>
       </c>
-      <c r="Y245" s="10" t="n">
+      <c r="Y245" s="11" t="n">
         <v>-222</v>
       </c>
-      <c r="AF245" s="9" t="n">
+      <c r="AF245" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="AG245" s="10" t="n">
+      <c r="AG245" s="11" t="n">
         <v>-61</v>
       </c>
-      <c r="AI245" s="10" t="n">
+      <c r="AI245" s="11" t="n">
         <v>-77</v>
       </c>
     </row>
@@ -12640,5 +12679,6 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/output/elod_progresivos.xlsx
+++ b/output/elod_progresivos.xlsx
@@ -580,14 +580,14 @@
     <col width="5" customWidth="1" min="54" max="54"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="35" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Federación Internacional de Léxico en Español (FILE)</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="25" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Elo Duplicada - Ranking Internacional</t>
@@ -599,6 +599,7 @@
         </is>
       </c>
     </row>
+    <row r="3" ht="25" customHeight="1"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>

--- a/output/elod_progresivos.xlsx
+++ b/output/elod_progresivos.xlsx
@@ -590,12 +590,7 @@
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Elo Duplicada - Ranking Internacional</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Actualizado al 8 de marzo de 2026</t>
+          <t>Elo Duplicada - Ranking Internacional  —  Actualizado al 8 de marzo de 2026</t>
         </is>
       </c>
     </row>
@@ -12674,10 +12669,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A1:BB1"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A2:BB2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/output/elod_progresivos.xlsx
+++ b/output/elod_progresivos.xlsx
@@ -12197,12 +12197,12 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>MARRERA, Deyanira</t>
+          <t>MARRERO, Deyanira</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="E237" s="9" t="n">

--- a/output/elod_progresivos.xlsx
+++ b/output/elod_progresivos.xlsx
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB245"/>
+  <dimension ref="A1:BB244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>2690</v>
+        <v>2689</v>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
     </row>
     <row r="19">
       <c r="A19" s="8" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>-25</v>
       </c>
       <c r="Y19" s="11" t="n">
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="AA19" s="10" t="n">
         <v>18</v>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         </is>
       </c>
       <c r="E47" s="9" t="n">
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         </is>
       </c>
       <c r="E93" s="9" t="n">
-        <v>2100</v>
+        <v>2099</v>
       </c>
       <c r="F93" s="8" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
     </row>
     <row r="106">
       <c r="A106" s="8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
@@ -6362,27 +6362,48 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MASDIAZ, Rafael</t>
+          <t>ALICHANIDIS, Sokratis</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>Grecia</t>
         </is>
       </c>
       <c r="E106" s="9" t="n">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="F106" s="8" t="inlineStr">
         <is>
-          <t>Norcenca Fort Lauderdale USA 2024</t>
+          <t>Mundial Santiago de Chile 2025</t>
         </is>
       </c>
       <c r="G106" s="8" t="n">
-        <v>2</v>
+        <v>335</v>
       </c>
       <c r="H106" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="I106" s="11" t="n">
+        <v>-85</v>
+      </c>
+      <c r="K106" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="M106" s="11" t="n">
+        <v>-45</v>
+      </c>
+      <c r="U106" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="W106" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y106" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AW106" s="11" t="n">
+        <v>-29</v>
       </c>
     </row>
     <row r="107">
@@ -6396,16 +6417,16 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ALICHANIDIS, Sokratis</t>
+          <t>LOZANO, Lucas Mateo</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Grecia</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E107" s="9" t="n">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="F107" s="8" t="inlineStr">
         <is>
@@ -6413,36 +6434,42 @@
         </is>
       </c>
       <c r="G107" s="8" t="n">
-        <v>335</v>
+        <v>381</v>
       </c>
       <c r="H107" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="I107" s="11" t="n">
-        <v>-85</v>
-      </c>
-      <c r="K107" s="10" t="n">
-        <v>31</v>
-      </c>
-      <c r="M107" s="11" t="n">
-        <v>-45</v>
-      </c>
-      <c r="U107" s="10" t="n">
-        <v>22</v>
-      </c>
-      <c r="W107" s="10" t="n">
-        <v>30</v>
+        <v>12</v>
+      </c>
+      <c r="J107" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L107" s="10" t="n">
+        <v>98</v>
+      </c>
+      <c r="O107" s="10" t="n">
+        <v>63</v>
+      </c>
+      <c r="U107" s="11" t="n">
+        <v>-98</v>
+      </c>
+      <c r="W107" s="11" t="n">
+        <v>-122</v>
       </c>
       <c r="Y107" s="10" t="n">
-        <v>76</v>
-      </c>
-      <c r="AW107" s="11" t="n">
-        <v>-29</v>
+        <v>169</v>
+      </c>
+      <c r="AF107" s="11" t="n">
+        <v>-49</v>
+      </c>
+      <c r="AG107" s="11" t="n">
+        <v>-56</v>
+      </c>
+      <c r="AI107" s="11" t="n">
+        <v>-7</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="8" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
@@ -6451,12 +6478,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>LOZANO, Lucas Mateo</t>
+          <t>MASDIAZ, Rafael</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos</t>
         </is>
       </c>
       <c r="E108" s="9" t="n">
@@ -6464,41 +6491,17 @@
       </c>
       <c r="F108" s="8" t="inlineStr">
         <is>
-          <t>Mundial Santiago de Chile 2025</t>
+          <t>Norcenca Fort Lauderdale USA 2024</t>
         </is>
       </c>
       <c r="G108" s="8" t="n">
-        <v>381</v>
+        <v>2</v>
       </c>
       <c r="H108" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="J108" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="L108" s="10" t="n">
-        <v>98</v>
-      </c>
-      <c r="O108" s="10" t="n">
-        <v>63</v>
-      </c>
-      <c r="U108" s="11" t="n">
-        <v>-98</v>
-      </c>
-      <c r="W108" s="11" t="n">
-        <v>-122</v>
-      </c>
-      <c r="Y108" s="10" t="n">
-        <v>169</v>
-      </c>
-      <c r="AF108" s="11" t="n">
-        <v>-49</v>
-      </c>
-      <c r="AG108" s="11" t="n">
-        <v>-56</v>
-      </c>
-      <c r="AI108" s="11" t="n">
-        <v>-7</v>
+        <v>1</v>
+      </c>
+      <c r="AA108" s="11" t="n">
+        <v>-2</v>
       </c>
     </row>
     <row r="109">
@@ -6769,12 +6772,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>VILLACÍS, Ricardo</t>
+          <t>GÁMEZ, Alejandro</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E114" s="9" t="n">
@@ -6782,16 +6785,16 @@
       </c>
       <c r="F114" s="8" t="inlineStr">
         <is>
-          <t>Norcenca Fort Lauderdale USA 2024</t>
+          <t>Norcenca Guanajuato 2025</t>
         </is>
       </c>
       <c r="G114" s="8" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H114" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AA114" s="11" t="n">
+      <c r="O114" s="11" t="n">
         <v>-10</v>
       </c>
     </row>
@@ -6806,35 +6809,56 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>GÁMEZ, Alejandro</t>
+          <t>DIANA, Eva</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="E115" s="9" t="n">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="F115" s="8" t="inlineStr">
         <is>
-          <t>Norcenca Guanajuato 2025</t>
+          <t>Mundial Santiago de Chile 2025</t>
         </is>
       </c>
       <c r="G115" s="8" t="n">
-        <v>16</v>
+        <v>275</v>
       </c>
       <c r="H115" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O115" s="11" t="n">
-        <v>-10</v>
+        <v>8</v>
+      </c>
+      <c r="I115" s="11" t="n">
+        <v>-33</v>
+      </c>
+      <c r="K115" s="10" t="n">
+        <v>98</v>
+      </c>
+      <c r="M115" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC115" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="AO115" s="10" t="n">
+        <v>78</v>
+      </c>
+      <c r="AR115" s="11" t="n">
+        <v>-97</v>
+      </c>
+      <c r="AT115" s="11" t="n">
+        <v>-40</v>
+      </c>
+      <c r="AV115" s="11" t="n">
+        <v>-90</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="8" t="n">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
@@ -6843,7 +6867,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>DIANA, Eva</t>
+          <t>ROUX, Mónica</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6856,43 +6880,22 @@
       </c>
       <c r="F116" s="8" t="inlineStr">
         <is>
-          <t>Mundial Santiago de Chile 2025</t>
+          <t>Austral Montevideo 2023</t>
         </is>
       </c>
       <c r="G116" s="8" t="n">
-        <v>275</v>
+        <v>19</v>
       </c>
       <c r="H116" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="I116" s="11" t="n">
-        <v>-33</v>
-      </c>
-      <c r="K116" s="10" t="n">
-        <v>98</v>
-      </c>
-      <c r="M116" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC116" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="AO116" s="10" t="n">
-        <v>78</v>
-      </c>
-      <c r="AR116" s="11" t="n">
-        <v>-97</v>
-      </c>
-      <c r="AT116" s="11" t="n">
-        <v>-40</v>
-      </c>
-      <c r="AV116" s="11" t="n">
-        <v>-90</v>
+        <v>1</v>
+      </c>
+      <c r="AO116" s="11" t="n">
+        <v>-11</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="8" t="n">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
@@ -6901,35 +6904,44 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ROUX, Mónica</t>
+          <t>TSALAPATI, Eva</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>España</t>
         </is>
       </c>
       <c r="E117" s="9" t="n">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="F117" s="8" t="inlineStr">
         <is>
-          <t>Austral Montevideo 2023</t>
+          <t>Mundial Granada 2024</t>
         </is>
       </c>
       <c r="G117" s="8" t="n">
-        <v>19</v>
+        <v>236</v>
       </c>
       <c r="H117" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO117" s="11" t="n">
-        <v>-11</v>
+        <v>4</v>
+      </c>
+      <c r="U117" s="11" t="n">
+        <v>-55</v>
+      </c>
+      <c r="W117" s="10" t="n">
+        <v>102</v>
+      </c>
+      <c r="Y117" s="11" t="n">
+        <v>-95</v>
+      </c>
+      <c r="AK117" s="10" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="8" t="n">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
@@ -6938,7 +6950,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>TSALAPATI, Eva</t>
+          <t>SÁNCHEZ, Joaquín</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6947,7 +6959,7 @@
         </is>
       </c>
       <c r="E118" s="9" t="n">
-        <v>2063</v>
+        <v>2062</v>
       </c>
       <c r="F118" s="8" t="inlineStr">
         <is>
@@ -6955,27 +6967,24 @@
         </is>
       </c>
       <c r="G118" s="8" t="n">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="H118" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="U118" s="11" t="n">
-        <v>-55</v>
-      </c>
-      <c r="W118" s="10" t="n">
-        <v>102</v>
-      </c>
-      <c r="Y118" s="11" t="n">
-        <v>-95</v>
-      </c>
-      <c r="AK118" s="10" t="n">
-        <v>36</v>
+        <v>3</v>
+      </c>
+      <c r="U118" s="10" t="n">
+        <v>188</v>
+      </c>
+      <c r="W118" s="11" t="n">
+        <v>-210</v>
+      </c>
+      <c r="Y118" s="10" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="8" t="n">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
@@ -6984,7 +6993,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SÁNCHEZ, Joaquín</t>
+          <t>MULA, Juan José</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6993,32 +7002,26 @@
         </is>
       </c>
       <c r="E119" s="9" t="n">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="F119" s="8" t="inlineStr">
         <is>
-          <t>Mundial Granada 2024</t>
+          <t>Europeo Castellón 2023</t>
         </is>
       </c>
       <c r="G119" s="8" t="n">
-        <v>217</v>
+        <v>19</v>
       </c>
       <c r="H119" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U119" s="10" t="n">
-        <v>188</v>
-      </c>
-      <c r="W119" s="11" t="n">
-        <v>-210</v>
-      </c>
-      <c r="Y119" s="10" t="n">
-        <v>9</v>
+        <v>1</v>
+      </c>
+      <c r="AK119" s="11" t="n">
+        <v>-14</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="8" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
@@ -7027,30 +7030,30 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MULA, Juan José</t>
+          <t>FALCÓN, Isaías</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="E120" s="9" t="n">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="F120" s="8" t="inlineStr">
         <is>
-          <t>Europeo Castellón 2023</t>
+          <t>Austral Asunción 2022</t>
         </is>
       </c>
       <c r="G120" s="8" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="H120" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AK120" s="11" t="n">
-        <v>-14</v>
+      <c r="AZ120" s="11" t="n">
+        <v>-15</v>
       </c>
     </row>
     <row r="121">
@@ -7064,12 +7067,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>FALCÓN, Isaías</t>
+          <t>ESTÉVEZ, Jackselyn</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Cuba</t>
         </is>
       </c>
       <c r="E121" s="9" t="n">
@@ -7077,22 +7080,25 @@
       </c>
       <c r="F121" s="8" t="inlineStr">
         <is>
-          <t>Austral Asunción 2022</t>
+          <t>Cuba Scrabble Matanzas 2024</t>
         </is>
       </c>
       <c r="G121" s="8" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="H121" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ121" s="11" t="n">
-        <v>-15</v>
+        <v>2</v>
+      </c>
+      <c r="AD121" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE121" s="11" t="n">
+        <v>-19</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="8" t="n">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
@@ -7101,38 +7107,35 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ESTÉVEZ, Jackselyn</t>
+          <t>SALVADOR, Augusta</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Cuba</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="E122" s="9" t="n">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="F122" s="8" t="inlineStr">
         <is>
-          <t>Cuba Scrabble Matanzas 2024</t>
+          <t>Andino Quito 2024</t>
         </is>
       </c>
       <c r="G122" s="8" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="H122" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD122" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE122" s="11" t="n">
-        <v>-19</v>
+        <v>1</v>
+      </c>
+      <c r="AB122" s="11" t="n">
+        <v>-16</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="8" t="n">
-        <v>-16</v>
+        <v>-20</v>
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
@@ -7141,35 +7144,41 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SALVADOR, Augusta</t>
+          <t>SÁNCHEZ, Montse</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>España</t>
         </is>
       </c>
       <c r="E123" s="9" t="n">
-        <v>2059</v>
+        <v>2055</v>
       </c>
       <c r="F123" s="8" t="inlineStr">
         <is>
-          <t>Andino Quito 2024</t>
+          <t>Mundial Costa Rica 2023</t>
         </is>
       </c>
       <c r="G123" s="8" t="n">
-        <v>8</v>
+        <v>101</v>
       </c>
       <c r="H123" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB123" s="11" t="n">
-        <v>-16</v>
+        <v>3</v>
+      </c>
+      <c r="AF123" s="11" t="n">
+        <v>-15</v>
+      </c>
+      <c r="AH123" s="11" t="n">
+        <v>-103</v>
+      </c>
+      <c r="AJ123" s="10" t="n">
+        <v>98</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="8" t="n">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
@@ -7178,41 +7187,62 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SÁNCHEZ, Montse</t>
+          <t>REY SARAVIA, Fernando</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E124" s="9" t="n">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="F124" s="8" t="inlineStr">
         <is>
-          <t>Mundial Costa Rica 2023</t>
+          <t>Mundial Santiago de Chile 2025</t>
         </is>
       </c>
       <c r="G124" s="8" t="n">
-        <v>101</v>
+        <v>406</v>
       </c>
       <c r="H124" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF124" s="11" t="n">
-        <v>-15</v>
-      </c>
-      <c r="AH124" s="11" t="n">
-        <v>-103</v>
-      </c>
-      <c r="AJ124" s="10" t="n">
-        <v>98</v>
+        <v>10</v>
+      </c>
+      <c r="I124" s="11" t="n">
+        <v>-43</v>
+      </c>
+      <c r="K124" s="11" t="n">
+        <v>-11</v>
+      </c>
+      <c r="M124" s="11" t="n">
+        <v>-99</v>
+      </c>
+      <c r="R124" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="U124" s="11" t="n">
+        <v>-129</v>
+      </c>
+      <c r="W124" s="10" t="n">
+        <v>271</v>
+      </c>
+      <c r="Y124" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO124" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="AR124" s="11" t="n">
+        <v>-94</v>
+      </c>
+      <c r="AS124" s="11" t="n">
+        <v>-40</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="8" t="n">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
@@ -7221,16 +7251,16 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>REY SARAVIA, Fernando</t>
+          <t>PANTOJA, Marcos</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Cuba</t>
         </is>
       </c>
       <c r="E125" s="9" t="n">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="F125" s="8" t="inlineStr">
         <is>
@@ -7238,40 +7268,19 @@
         </is>
       </c>
       <c r="G125" s="8" t="n">
-        <v>406</v>
+        <v>44</v>
       </c>
       <c r="H125" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="I125" s="11" t="n">
-        <v>-43</v>
-      </c>
-      <c r="K125" s="11" t="n">
-        <v>-11</v>
-      </c>
-      <c r="M125" s="11" t="n">
-        <v>-99</v>
-      </c>
-      <c r="R125" s="10" t="n">
-        <v>34</v>
-      </c>
-      <c r="U125" s="11" t="n">
-        <v>-129</v>
-      </c>
-      <c r="W125" s="10" t="n">
-        <v>271</v>
-      </c>
-      <c r="Y125" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO125" s="10" t="n">
-        <v>90</v>
-      </c>
-      <c r="AR125" s="11" t="n">
-        <v>-94</v>
-      </c>
-      <c r="AS125" s="11" t="n">
-        <v>-40</v>
+        <v>3</v>
+      </c>
+      <c r="J125" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="L125" s="11" t="n">
+        <v>-7</v>
+      </c>
+      <c r="T125" s="11" t="n">
+        <v>-34</v>
       </c>
     </row>
     <row r="126">
@@ -7285,12 +7294,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>PANTOJA, Marcos</t>
+          <t>RIVADENEYRA, Libertad</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Cuba</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E126" s="9" t="n">
@@ -7298,28 +7307,25 @@
       </c>
       <c r="F126" s="8" t="inlineStr">
         <is>
-          <t>Mundial Santiago de Chile 2025</t>
+          <t>Mundial Buenos Aires 2022</t>
         </is>
       </c>
       <c r="G126" s="8" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="H126" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS126" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="J126" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="L126" s="11" t="n">
-        <v>-7</v>
-      </c>
-      <c r="T126" s="11" t="n">
-        <v>-34</v>
+      <c r="AU126" s="11" t="n">
+        <v>-25</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="8" t="n">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
@@ -7328,38 +7334,35 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>RIVADENEYRA, Libertad</t>
+          <t>PARRA, José</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="E127" s="9" t="n">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="F127" s="8" t="inlineStr">
         <is>
-          <t>Mundial Buenos Aires 2022</t>
+          <t>Andino Caracas 2023</t>
         </is>
       </c>
       <c r="G127" s="8" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="H127" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS127" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU127" s="11" t="n">
-        <v>-25</v>
+        <v>1</v>
+      </c>
+      <c r="AN127" s="11" t="n">
+        <v>-23</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="8" t="n">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
@@ -7368,30 +7371,30 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>PARRA, José</t>
+          <t>DEL PINO, Amado</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Cuba</t>
         </is>
       </c>
       <c r="E128" s="9" t="n">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="F128" s="8" t="inlineStr">
         <is>
-          <t>Andino Caracas 2023</t>
+          <t>Cuba Scrabble Varadero 2025</t>
         </is>
       </c>
       <c r="G128" s="8" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="H128" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AN128" s="11" t="n">
-        <v>-23</v>
+      <c r="T128" s="11" t="n">
+        <v>-24</v>
       </c>
     </row>
     <row r="129">
@@ -7405,7 +7408,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>DEL PINO, Amado</t>
+          <t>CORTADA, José</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -7418,22 +7421,25 @@
       </c>
       <c r="F129" s="8" t="inlineStr">
         <is>
-          <t>Cuba Scrabble Varadero 2025</t>
+          <t>Norcenca/Cuba Scrabble La Habana 2022</t>
         </is>
       </c>
       <c r="G129" s="8" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="H129" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA129" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="T129" s="11" t="n">
-        <v>-24</v>
+      <c r="BB129" s="11" t="n">
+        <v>-25</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="8" t="n">
-        <v>-24</v>
+        <v>-29</v>
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
@@ -7442,38 +7448,35 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>CORTADA, José</t>
+          <t>LAZDÍN, Eduardo</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Cuba</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E130" s="9" t="n">
-        <v>2051</v>
+        <v>2046</v>
       </c>
       <c r="F130" s="8" t="inlineStr">
         <is>
-          <t>Norcenca/Cuba Scrabble La Habana 2022</t>
+          <t>Austral Asunción 2025</t>
         </is>
       </c>
       <c r="G130" s="8" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="H130" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA130" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="BB130" s="11" t="n">
-        <v>-25</v>
+      <c r="R130" s="11" t="n">
+        <v>-29</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="8" t="n">
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
@@ -7482,35 +7485,41 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>LAZDÍN, Eduardo</t>
+          <t>SANHUEZA, Víctor</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="E131" s="9" t="n">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="F131" s="8" t="inlineStr">
         <is>
-          <t>Austral Asunción 2025</t>
+          <t>Mundial Santiago de Chile 2025</t>
         </is>
       </c>
       <c r="G131" s="8" t="n">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="H131" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R131" s="11" t="n">
-        <v>-29</v>
+        <v>3</v>
+      </c>
+      <c r="I131" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K131" s="11" t="n">
+        <v>-40</v>
+      </c>
+      <c r="M131" s="10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="8" t="n">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
@@ -7519,16 +7528,16 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>SANHUEZA, Víctor</t>
+          <t>NOSSA, Johanna</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E132" s="9" t="n">
-        <v>2045</v>
+        <v>2043</v>
       </c>
       <c r="F132" s="8" t="inlineStr">
         <is>
@@ -7542,18 +7551,18 @@
         <v>3</v>
       </c>
       <c r="I132" s="10" t="n">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="K132" s="11" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M132" s="10" t="n">
-        <v>3</v>
+        <v>-21</v>
+      </c>
+      <c r="M132" s="11" t="n">
+        <v>-77</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="8" t="n">
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
@@ -7562,12 +7571,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>NOSSA, Johanna</t>
+          <t>MALDONADO, Roberto</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="E133" s="9" t="n">
@@ -7575,28 +7584,28 @@
       </c>
       <c r="F133" s="8" t="inlineStr">
         <is>
-          <t>Mundial Santiago de Chile 2025</t>
+          <t>Austral Asunción 2025</t>
         </is>
       </c>
       <c r="G133" s="8" t="n">
-        <v>104</v>
+        <v>41</v>
       </c>
       <c r="H133" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I133" s="10" t="n">
-        <v>67</v>
-      </c>
-      <c r="K133" s="11" t="n">
-        <v>-21</v>
-      </c>
-      <c r="M133" s="11" t="n">
-        <v>-77</v>
+      <c r="R133" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO133" s="11" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AZ133" s="10" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="8" t="n">
-        <v>-32</v>
+        <v>-33</v>
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
@@ -7605,41 +7614,35 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>MALDONADO, Roberto</t>
+          <t>HARRINGHTON, Susana</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="E134" s="9" t="n">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="F134" s="8" t="inlineStr">
         <is>
-          <t>Austral Asunción 2025</t>
+          <t>Andino Caracas 2023</t>
         </is>
       </c>
       <c r="G134" s="8" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H134" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R134" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO134" s="11" t="n">
-        <v>-55</v>
-      </c>
-      <c r="AZ134" s="10" t="n">
-        <v>15</v>
+        <v>1</v>
+      </c>
+      <c r="AN134" s="11" t="n">
+        <v>-33</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="8" t="n">
-        <v>-33</v>
+        <v>-35</v>
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
@@ -7648,35 +7651,35 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>HARRINGHTON, Susana</t>
+          <t>MARINANGELI, Mariela</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E135" s="9" t="n">
-        <v>2042</v>
+        <v>2040</v>
       </c>
       <c r="F135" s="8" t="inlineStr">
         <is>
-          <t>Andino Caracas 2023</t>
+          <t>Austral Asunción 2022</t>
         </is>
       </c>
       <c r="G135" s="8" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="H135" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AN135" s="11" t="n">
-        <v>-33</v>
+      <c r="AZ135" s="11" t="n">
+        <v>-35</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="8" t="n">
-        <v>-35</v>
+        <v>-36</v>
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
@@ -7685,30 +7688,30 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>MARINANGELI, Mariela</t>
+          <t>CASTILLO, Christian</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="E136" s="9" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="F136" s="8" t="inlineStr">
         <is>
-          <t>Austral Asunción 2022</t>
+          <t>Andino Quito 2024</t>
         </is>
       </c>
       <c r="G136" s="8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H136" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AZ136" s="11" t="n">
-        <v>-35</v>
+      <c r="AB136" s="11" t="n">
+        <v>-36</v>
       </c>
     </row>
     <row r="137">
@@ -7722,12 +7725,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>CASTILLO, Christian</t>
+          <t>GUERRERO, Francisco Javier</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E137" s="9" t="n">
@@ -7735,22 +7738,28 @@
       </c>
       <c r="F137" s="8" t="inlineStr">
         <is>
-          <t>Andino Quito 2024</t>
+          <t>Norcenca Fort Lauderdale USA 2024</t>
         </is>
       </c>
       <c r="G137" s="8" t="n">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="H137" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB137" s="11" t="n">
-        <v>-36</v>
+        <v>3</v>
+      </c>
+      <c r="AA137" s="11" t="n">
+        <v>-26</v>
+      </c>
+      <c r="AL137" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM137" s="11" t="n">
+        <v>-48</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="8" t="n">
-        <v>-36</v>
+        <v>-37</v>
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
@@ -7759,41 +7768,44 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>GUERRERO, Francisco Javier</t>
+          <t>RODRÍGUEZ, José Luis</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>España</t>
         </is>
       </c>
       <c r="E138" s="9" t="n">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="F138" s="8" t="inlineStr">
         <is>
-          <t>Norcenca Fort Lauderdale USA 2024</t>
+          <t>Mundial Granada 2024</t>
         </is>
       </c>
       <c r="G138" s="8" t="n">
-        <v>68</v>
+        <v>236</v>
       </c>
       <c r="H138" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA138" s="11" t="n">
-        <v>-26</v>
-      </c>
-      <c r="AL138" s="10" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM138" s="11" t="n">
-        <v>-48</v>
+        <v>4</v>
+      </c>
+      <c r="U138" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="W138" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y138" s="11" t="n">
+        <v>-68</v>
+      </c>
+      <c r="AK138" s="11" t="n">
+        <v>-4</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="8" t="n">
-        <v>-37</v>
+        <v>-36</v>
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
@@ -7802,44 +7814,38 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>RODRÍGUEZ, José Luis</t>
+          <t>GÓMEZ, Ana Lucía</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Perú</t>
         </is>
       </c>
       <c r="E139" s="9" t="n">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="F139" s="8" t="inlineStr">
         <is>
-          <t>Mundial Granada 2024</t>
+          <t>Andino Lima 2025</t>
         </is>
       </c>
       <c r="G139" s="8" t="n">
-        <v>236</v>
+        <v>18</v>
       </c>
       <c r="H139" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="U139" s="10" t="n">
-        <v>33</v>
-      </c>
-      <c r="W139" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Y139" s="11" t="n">
-        <v>-68</v>
-      </c>
-      <c r="AK139" s="11" t="n">
-        <v>-4</v>
+      <c r="P139" s="11" t="n">
+        <v>-17</v>
+      </c>
+      <c r="Q139" s="11" t="n">
+        <v>-19</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="8" t="n">
-        <v>-36</v>
+        <v>-37</v>
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
@@ -7848,12 +7854,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>GÓMEZ, Ana Lucía</t>
+          <t>ALONSO, Luis</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Perú</t>
+          <t>España</t>
         </is>
       </c>
       <c r="E140" s="9" t="n">
@@ -7861,25 +7867,22 @@
       </c>
       <c r="F140" s="8" t="inlineStr">
         <is>
-          <t>Andino Lima 2025</t>
+          <t>Europeo Murcia 2025</t>
         </is>
       </c>
       <c r="G140" s="8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H140" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="P140" s="11" t="n">
-        <v>-17</v>
-      </c>
-      <c r="Q140" s="11" t="n">
-        <v>-19</v>
+        <v>1</v>
+      </c>
+      <c r="N140" s="11" t="n">
+        <v>-37</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="8" t="n">
-        <v>-37</v>
+        <v>-39</v>
       </c>
       <c r="B141" s="8" t="inlineStr">
         <is>
@@ -7888,35 +7891,35 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>ALONSO, Luis</t>
+          <t>CHANG, Olivia</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Estados Unidos</t>
         </is>
       </c>
       <c r="E141" s="9" t="n">
-        <v>2038</v>
+        <v>2036</v>
       </c>
       <c r="F141" s="8" t="inlineStr">
         <is>
-          <t>Europeo Murcia 2025</t>
+          <t>Norcenca Fort Lauderdale USA 2024</t>
         </is>
       </c>
       <c r="G141" s="8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H141" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N141" s="11" t="n">
-        <v>-37</v>
+      <c r="AA141" s="11" t="n">
+        <v>-39</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="8" t="n">
-        <v>-39</v>
+        <v>-41</v>
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
@@ -7925,35 +7928,35 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>CHANG, Olivia</t>
+          <t>RAMÍREZ, Susana</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E142" s="9" t="n">
-        <v>2036</v>
+        <v>2034</v>
       </c>
       <c r="F142" s="8" t="inlineStr">
         <is>
-          <t>Norcenca Fort Lauderdale USA 2024</t>
+          <t>Austral Montevideo 2023</t>
         </is>
       </c>
       <c r="G142" s="8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H142" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AA142" s="11" t="n">
-        <v>-39</v>
+      <c r="AO142" s="11" t="n">
+        <v>-41</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="8" t="n">
-        <v>-41</v>
+        <v>-43</v>
       </c>
       <c r="B143" s="8" t="inlineStr">
         <is>
@@ -7962,35 +7965,35 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>RAMÍREZ, Susana</t>
+          <t>RESTREPO, Eliana</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="E143" s="9" t="n">
-        <v>2034</v>
+        <v>2032</v>
       </c>
       <c r="F143" s="8" t="inlineStr">
         <is>
-          <t>Austral Montevideo 2023</t>
+          <t>Andino Caracas 2023</t>
         </is>
       </c>
       <c r="G143" s="8" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="H143" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AO143" s="11" t="n">
-        <v>-41</v>
+      <c r="AN143" s="11" t="n">
+        <v>-43</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="8" t="n">
-        <v>-43</v>
+        <v>-44</v>
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
@@ -7999,7 +8002,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>ROMERO, Rosa</t>
+          <t>TERENZANI, Alejandro</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -8008,26 +8011,56 @@
         </is>
       </c>
       <c r="E144" s="9" t="n">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="F144" s="8" t="inlineStr">
         <is>
-          <t>Andino Caracas 2023</t>
+          <t>Mundial Santiago de Chile 2025</t>
         </is>
       </c>
       <c r="G144" s="8" t="n">
+        <v>199</v>
+      </c>
+      <c r="H144" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="L144" s="11" t="n">
+        <v>-83</v>
+      </c>
+      <c r="U144" s="11" t="n">
+        <v>-138</v>
+      </c>
+      <c r="V144" s="11" t="n">
+        <v>-7</v>
+      </c>
+      <c r="X144" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF144" s="11" t="n">
+        <v>-62</v>
+      </c>
+      <c r="AG144" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI144" s="11" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AL144" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="AM144" s="10" t="n">
+        <v>62</v>
+      </c>
+      <c r="AS144" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="H144" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN144" s="11" t="n">
-        <v>-43</v>
+      <c r="AU144" s="10" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="8" t="n">
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="B145" s="8" t="inlineStr">
         <is>
@@ -8036,65 +8069,35 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>TERENZANI, Alejandro</t>
+          <t>MALDONADO, Esther</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="E145" s="9" t="n">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="F145" s="8" t="inlineStr">
         <is>
-          <t>Mundial Santiago de Chile 2025</t>
+          <t>Austral Asunción 2022</t>
         </is>
       </c>
       <c r="G145" s="8" t="n">
-        <v>199</v>
+        <v>9</v>
       </c>
       <c r="H145" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="L145" s="11" t="n">
-        <v>-83</v>
-      </c>
-      <c r="U145" s="11" t="n">
-        <v>-138</v>
-      </c>
-      <c r="V145" s="11" t="n">
-        <v>-7</v>
-      </c>
-      <c r="X145" s="10" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF145" s="11" t="n">
-        <v>-62</v>
-      </c>
-      <c r="AG145" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI145" s="11" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AL145" s="10" t="n">
-        <v>43</v>
-      </c>
-      <c r="AM145" s="10" t="n">
-        <v>62</v>
-      </c>
-      <c r="AS145" s="10" t="n">
-        <v>37</v>
-      </c>
-      <c r="AU145" s="10" t="n">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="AZ145" s="11" t="n">
+        <v>-45</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="8" t="n">
-        <v>-45</v>
+        <v>-46</v>
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
@@ -8103,35 +8106,35 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>MALDONADO, Esther</t>
+          <t>MÁRQUEZ, Víctor</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="E146" s="9" t="n">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="F146" s="8" t="inlineStr">
         <is>
-          <t>Austral Asunción 2022</t>
+          <t>Andino Quito 2024</t>
         </is>
       </c>
       <c r="G146" s="8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H146" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AZ146" s="11" t="n">
-        <v>-45</v>
+      <c r="AB146" s="11" t="n">
+        <v>-46</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="8" t="n">
-        <v>-46</v>
+        <v>-47</v>
       </c>
       <c r="B147" s="8" t="inlineStr">
         <is>
@@ -8140,35 +8143,35 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>MÁRQUEZ, Víctor</t>
+          <t>STEPHENS, Suzanne</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E147" s="9" t="n">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="F147" s="8" t="inlineStr">
         <is>
-          <t>Andino Quito 2024</t>
+          <t>Europeo Murcia 2025</t>
         </is>
       </c>
       <c r="G147" s="8" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H147" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AB147" s="11" t="n">
-        <v>-46</v>
+      <c r="N147" s="11" t="n">
+        <v>-47</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="8" t="n">
-        <v>-47</v>
+        <v>-49</v>
       </c>
       <c r="B148" s="8" t="inlineStr">
         <is>
@@ -8177,30 +8180,30 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>STEPHENS, Suzanne</t>
+          <t>DALMAU, Marina</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>España</t>
         </is>
       </c>
       <c r="E148" s="9" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="F148" s="8" t="inlineStr">
         <is>
-          <t>Europeo Murcia 2025</t>
+          <t>Europeo Atenas 2022</t>
         </is>
       </c>
       <c r="G148" s="8" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H148" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N148" s="11" t="n">
-        <v>-47</v>
+      <c r="AW148" s="11" t="n">
+        <v>-49</v>
       </c>
     </row>
     <row r="149">
@@ -8214,12 +8217,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>DALMAU, Marina</t>
+          <t>FELA, Niria</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Estados Unidos</t>
         </is>
       </c>
       <c r="E149" s="9" t="n">
@@ -8227,22 +8230,22 @@
       </c>
       <c r="F149" s="8" t="inlineStr">
         <is>
-          <t>Europeo Atenas 2022</t>
+          <t>Norcenca Fort Lauderdale USA 2024</t>
         </is>
       </c>
       <c r="G149" s="8" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H149" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AW149" s="11" t="n">
+      <c r="AA149" s="11" t="n">
         <v>-49</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="8" t="n">
-        <v>-49</v>
+        <v>-50</v>
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
@@ -8251,35 +8254,68 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>FELA, Niria</t>
+          <t>FALCONETT, Rubén</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>Panamá</t>
         </is>
       </c>
       <c r="E150" s="9" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="F150" s="8" t="inlineStr">
         <is>
-          <t>Norcenca Fort Lauderdale USA 2024</t>
+          <t>Norcenca Guanajuato 2025</t>
         </is>
       </c>
       <c r="G150" s="8" t="n">
-        <v>18</v>
+        <v>346</v>
       </c>
       <c r="H150" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA150" s="11" t="n">
-        <v>-49</v>
+        <v>12</v>
+      </c>
+      <c r="O150" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="U150" s="10" t="n">
+        <v>69</v>
+      </c>
+      <c r="V150" s="11" t="n">
+        <v>-60</v>
+      </c>
+      <c r="X150" s="11" t="n">
+        <v>-77</v>
+      </c>
+      <c r="AL150" s="11" t="n">
+        <v>-31</v>
+      </c>
+      <c r="AM150" s="11" t="n">
+        <v>-61</v>
+      </c>
+      <c r="AN150" s="10" t="n">
+        <v>61</v>
+      </c>
+      <c r="AR150" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="AT150" s="11" t="n">
+        <v>-58</v>
+      </c>
+      <c r="AV150" s="11" t="n">
+        <v>-25</v>
+      </c>
+      <c r="AX150" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AY150" s="10" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="8" t="n">
-        <v>-50</v>
+        <v>-51</v>
       </c>
       <c r="B151" s="8" t="inlineStr">
         <is>
@@ -8288,12 +8324,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>FALCONETT, Rubén</t>
+          <t>PENALBA, Mónica</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Panamá</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E151" s="9" t="n">
@@ -8301,55 +8337,25 @@
       </c>
       <c r="F151" s="8" t="inlineStr">
         <is>
-          <t>Norcenca Guanajuato 2025</t>
+          <t>Mundial Buenos Aires 2022</t>
         </is>
       </c>
       <c r="G151" s="8" t="n">
-        <v>346</v>
+        <v>15</v>
       </c>
       <c r="H151" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="O151" s="10" t="n">
-        <v>38</v>
-      </c>
-      <c r="U151" s="10" t="n">
-        <v>69</v>
-      </c>
-      <c r="V151" s="11" t="n">
-        <v>-60</v>
-      </c>
-      <c r="X151" s="11" t="n">
-        <v>-77</v>
-      </c>
-      <c r="AL151" s="11" t="n">
-        <v>-31</v>
-      </c>
-      <c r="AM151" s="11" t="n">
-        <v>-61</v>
-      </c>
-      <c r="AN151" s="10" t="n">
-        <v>61</v>
-      </c>
-      <c r="AR151" s="10" t="n">
-        <v>39</v>
-      </c>
-      <c r="AT151" s="11" t="n">
-        <v>-58</v>
-      </c>
-      <c r="AV151" s="11" t="n">
-        <v>-25</v>
-      </c>
-      <c r="AX151" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AY151" s="10" t="n">
-        <v>15</v>
+        <v>2</v>
+      </c>
+      <c r="AS151" s="11" t="n">
+        <v>-16</v>
+      </c>
+      <c r="AU151" s="11" t="n">
+        <v>-35</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="8" t="n">
-        <v>-51</v>
+        <v>-53</v>
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
@@ -8358,38 +8364,35 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>PENALBA, Mónica</t>
+          <t>DELGADO, Naiken</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="E152" s="9" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="F152" s="8" t="inlineStr">
         <is>
-          <t>Mundial Buenos Aires 2022</t>
+          <t>Andino Caracas 2023</t>
         </is>
       </c>
       <c r="G152" s="8" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="H152" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS152" s="11" t="n">
-        <v>-16</v>
-      </c>
-      <c r="AU152" s="11" t="n">
-        <v>-35</v>
+        <v>1</v>
+      </c>
+      <c r="AN152" s="11" t="n">
+        <v>-53</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="8" t="n">
-        <v>-53</v>
+        <v>-54</v>
       </c>
       <c r="B153" s="8" t="inlineStr">
         <is>
@@ -8398,35 +8401,35 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>DELGADO, Naiken</t>
+          <t>LAZO, Elena</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="E153" s="9" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F153" s="8" t="inlineStr">
         <is>
-          <t>Andino Caracas 2023</t>
+          <t>Mundial Santiago de Chile 2025</t>
         </is>
       </c>
       <c r="G153" s="8" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="H153" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AN153" s="11" t="n">
-        <v>-53</v>
+      <c r="L153" s="11" t="n">
+        <v>-54</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="8" t="n">
-        <v>-54</v>
+        <v>-55</v>
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
@@ -8435,35 +8438,77 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>LAZO, Elena</t>
+          <t>ALMENGOR, César</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Panamá</t>
         </is>
       </c>
       <c r="E154" s="9" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="F154" s="8" t="inlineStr">
         <is>
-          <t>Mundial Santiago de Chile 2025</t>
+          <t>Austral Asunción 2025</t>
         </is>
       </c>
       <c r="G154" s="8" t="n">
+        <v>564</v>
+      </c>
+      <c r="H154" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="R154" s="11" t="n">
+        <v>-11</v>
+      </c>
+      <c r="U154" s="11" t="n">
+        <v>-10</v>
+      </c>
+      <c r="W154" s="10" t="n">
+        <v>134</v>
+      </c>
+      <c r="Y154" s="11" t="n">
+        <v>-78</v>
+      </c>
+      <c r="AB154" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="H154" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L154" s="11" t="n">
-        <v>-54</v>
+      <c r="AF154" s="11" t="n">
+        <v>-58</v>
+      </c>
+      <c r="AH154" s="11" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AJ154" s="11" t="n">
+        <v>-91</v>
+      </c>
+      <c r="AL154" s="10" t="n">
+        <v>41</v>
+      </c>
+      <c r="AM154" s="10" t="n">
+        <v>151</v>
+      </c>
+      <c r="AR154" s="11" t="n">
+        <v>-59</v>
+      </c>
+      <c r="AT154" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AV154" s="11" t="n">
+        <v>-129</v>
+      </c>
+      <c r="AX154" s="11" t="n">
+        <v>-13</v>
+      </c>
+      <c r="AY154" s="11" t="n">
+        <v>-5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="8" t="n">
-        <v>-55</v>
+        <v>-58</v>
       </c>
       <c r="B155" s="8" t="inlineStr">
         <is>
@@ -8472,77 +8517,41 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>ALMENGOR, César</t>
+          <t>CATALÁ, Antonio</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Panamá</t>
+          <t>Cuba</t>
         </is>
       </c>
       <c r="E155" s="9" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="F155" s="8" t="inlineStr">
         <is>
-          <t>Austral Asunción 2025</t>
+          <t>Cuba Scrabble Varadero 2025</t>
         </is>
       </c>
       <c r="G155" s="8" t="n">
-        <v>564</v>
+        <v>47</v>
       </c>
       <c r="H155" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="R155" s="11" t="n">
-        <v>-11</v>
-      </c>
-      <c r="U155" s="11" t="n">
-        <v>-10</v>
-      </c>
-      <c r="W155" s="10" t="n">
-        <v>134</v>
-      </c>
-      <c r="Y155" s="11" t="n">
-        <v>-78</v>
-      </c>
-      <c r="AB155" s="10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AF155" s="11" t="n">
-        <v>-58</v>
-      </c>
-      <c r="AH155" s="11" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AJ155" s="11" t="n">
-        <v>-91</v>
-      </c>
-      <c r="AL155" s="10" t="n">
-        <v>41</v>
-      </c>
-      <c r="AM155" s="10" t="n">
-        <v>151</v>
-      </c>
-      <c r="AR155" s="11" t="n">
-        <v>-59</v>
-      </c>
-      <c r="AT155" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AV155" s="11" t="n">
-        <v>-129</v>
-      </c>
-      <c r="AX155" s="11" t="n">
-        <v>-13</v>
-      </c>
-      <c r="AY155" s="11" t="n">
-        <v>-5</v>
+        <v>3</v>
+      </c>
+      <c r="T155" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA155" s="11" t="n">
+        <v>-51</v>
+      </c>
+      <c r="BB155" s="11" t="n">
+        <v>-15</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="8" t="n">
-        <v>-58</v>
+        <v>-59</v>
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
@@ -8551,41 +8560,35 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>CATALÁ, Antonio</t>
+          <t>SARMIENTO, Luz</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Cuba</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E156" s="9" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="F156" s="8" t="inlineStr">
         <is>
-          <t>Cuba Scrabble Varadero 2025</t>
+          <t>Norcenca Fort Lauderdale USA 2024</t>
         </is>
       </c>
       <c r="G156" s="8" t="n">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="H156" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T156" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA156" s="11" t="n">
-        <v>-51</v>
-      </c>
-      <c r="BB156" s="11" t="n">
-        <v>-15</v>
+        <v>1</v>
+      </c>
+      <c r="AA156" s="11" t="n">
+        <v>-59</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="8" t="n">
-        <v>-59</v>
+        <v>-61</v>
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
@@ -8594,35 +8597,41 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>SARMIENTO, Luz</t>
+          <t>DÍAZ, Óscar</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E157" s="9" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="F157" s="8" t="inlineStr">
         <is>
-          <t>Norcenca Fort Lauderdale USA 2024</t>
+          <t>Norcenca Guanajuato 2025</t>
         </is>
       </c>
       <c r="G157" s="8" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="H157" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA157" s="11" t="n">
-        <v>-59</v>
+        <v>3</v>
+      </c>
+      <c r="O157" s="11" t="n">
+        <v>-35</v>
+      </c>
+      <c r="AS157" s="11" t="n">
+        <v>-31</v>
+      </c>
+      <c r="AU157" s="10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="8" t="n">
-        <v>-61</v>
+        <v>-63</v>
       </c>
       <c r="B158" s="8" t="inlineStr">
         <is>
@@ -8631,36 +8640,33 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>DÍAZ, Óscar</t>
+          <t>ÁVILA, Celia</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Panamá</t>
         </is>
       </c>
       <c r="E158" s="9" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="F158" s="8" t="inlineStr">
         <is>
-          <t>Norcenca Guanajuato 2025</t>
+          <t>Norcenca Panamá 2023</t>
         </is>
       </c>
       <c r="G158" s="8" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="H158" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="O158" s="11" t="n">
-        <v>-35</v>
-      </c>
-      <c r="AS158" s="11" t="n">
-        <v>-31</v>
-      </c>
-      <c r="AU158" s="10" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="AL158" s="11" t="n">
+        <v>-85</v>
+      </c>
+      <c r="AM158" s="10" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="159">
@@ -8674,12 +8680,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>ÁVILA, Celia</t>
+          <t>MIRANDA, Carolina</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Panamá</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="E159" s="9" t="n">
@@ -8687,25 +8693,22 @@
       </c>
       <c r="F159" s="8" t="inlineStr">
         <is>
-          <t>Norcenca Panamá 2023</t>
+          <t>Andino Caracas 2023</t>
         </is>
       </c>
       <c r="G159" s="8" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="H159" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL159" s="11" t="n">
-        <v>-85</v>
-      </c>
-      <c r="AM159" s="10" t="n">
-        <v>22</v>
+        <v>1</v>
+      </c>
+      <c r="AN159" s="11" t="n">
+        <v>-63</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="8" t="n">
-        <v>-63</v>
+        <v>-64</v>
       </c>
       <c r="B160" s="8" t="inlineStr">
         <is>
@@ -8714,35 +8717,35 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>MIRANDA, Carolina</t>
+          <t>RODRÍGUEZ, Octavio</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Cuba</t>
         </is>
       </c>
       <c r="E160" s="9" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="F160" s="8" t="inlineStr">
         <is>
-          <t>Andino Caracas 2023</t>
+          <t>Cuba Scrabble Varadero 2025</t>
         </is>
       </c>
       <c r="G160" s="8" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="H160" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AN160" s="11" t="n">
-        <v>-63</v>
+      <c r="T160" s="11" t="n">
+        <v>-64</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="8" t="n">
-        <v>-64</v>
+        <v>-66</v>
       </c>
       <c r="B161" s="8" t="inlineStr">
         <is>
@@ -8751,30 +8754,33 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>RODRÍGUEZ, Octavio</t>
+          <t>GIL, Marivi</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Cuba</t>
+          <t>España</t>
         </is>
       </c>
       <c r="E161" s="9" t="n">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="F161" s="8" t="inlineStr">
         <is>
-          <t>Cuba Scrabble Varadero 2025</t>
+          <t>Europeo Castellón 2023</t>
         </is>
       </c>
       <c r="G161" s="8" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="H161" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="T161" s="11" t="n">
-        <v>-64</v>
+        <v>2</v>
+      </c>
+      <c r="AK161" s="11" t="n">
+        <v>-77</v>
+      </c>
+      <c r="AW161" s="10" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="162">
@@ -8788,12 +8794,12 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>GIL, Marivi</t>
+          <t>SANDI, Liliana</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="E162" s="9" t="n">
@@ -8801,25 +8807,28 @@
       </c>
       <c r="F162" s="8" t="inlineStr">
         <is>
-          <t>Europeo Castellón 2023</t>
+          <t>Mundial Santiago de Chile 2025</t>
         </is>
       </c>
       <c r="G162" s="8" t="n">
-        <v>33</v>
+        <v>104</v>
       </c>
       <c r="H162" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK162" s="11" t="n">
-        <v>-77</v>
-      </c>
-      <c r="AW162" s="10" t="n">
-        <v>11</v>
+        <v>3</v>
+      </c>
+      <c r="I162" s="11" t="n">
+        <v>-34</v>
+      </c>
+      <c r="K162" s="11" t="n">
+        <v>-75</v>
+      </c>
+      <c r="M162" s="10" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="8" t="n">
-        <v>-66</v>
+        <v>-67</v>
       </c>
       <c r="B163" s="8" t="inlineStr">
         <is>
@@ -8828,41 +8837,35 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>SANDI, Liliana</t>
+          <t>RODRÍGUEZ, Alberto</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Costa Rica</t>
+          <t>España</t>
         </is>
       </c>
       <c r="E163" s="9" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="F163" s="8" t="inlineStr">
         <is>
-          <t>Mundial Santiago de Chile 2025</t>
+          <t>Europeo Murcia 2025</t>
         </is>
       </c>
       <c r="G163" s="8" t="n">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="H163" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I163" s="11" t="n">
-        <v>-34</v>
-      </c>
-      <c r="K163" s="11" t="n">
-        <v>-75</v>
-      </c>
-      <c r="M163" s="10" t="n">
-        <v>43</v>
+        <v>1</v>
+      </c>
+      <c r="N163" s="11" t="n">
+        <v>-67</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="8" t="n">
-        <v>-67</v>
+        <v>-68</v>
       </c>
       <c r="B164" s="8" t="inlineStr">
         <is>
@@ -8871,12 +8874,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>RODRÍGUEZ, Alberto</t>
+          <t>RAMONES, Jhoanna</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="E164" s="9" t="n">
@@ -8884,22 +8887,28 @@
       </c>
       <c r="F164" s="8" t="inlineStr">
         <is>
-          <t>Europeo Murcia 2025</t>
+          <t>Austral Asunción 2025</t>
         </is>
       </c>
       <c r="G164" s="8" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="H164" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N164" s="11" t="n">
-        <v>-67</v>
+        <v>3</v>
+      </c>
+      <c r="R164" s="11" t="n">
+        <v>-45</v>
+      </c>
+      <c r="AC164" s="11" t="n">
+        <v>-58</v>
+      </c>
+      <c r="AZ164" s="10" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="8" t="n">
-        <v>-68</v>
+        <v>-69</v>
       </c>
       <c r="B165" s="8" t="inlineStr">
         <is>
@@ -8908,41 +8917,35 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>RAMONES, Jhoanna</t>
+          <t>BOBADILLA, Luz</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Estados Unidos</t>
         </is>
       </c>
       <c r="E165" s="9" t="n">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="F165" s="8" t="inlineStr">
         <is>
-          <t>Austral Asunción 2025</t>
+          <t>Norcenca Fort Lauderdale USA 2024</t>
         </is>
       </c>
       <c r="G165" s="8" t="n">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="H165" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R165" s="11" t="n">
-        <v>-45</v>
-      </c>
-      <c r="AC165" s="11" t="n">
-        <v>-58</v>
-      </c>
-      <c r="AZ165" s="10" t="n">
-        <v>35</v>
+        <v>1</v>
+      </c>
+      <c r="AA165" s="11" t="n">
+        <v>-69</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="8" t="n">
-        <v>-69</v>
+        <v>-70</v>
       </c>
       <c r="B166" s="8" t="inlineStr">
         <is>
@@ -8951,12 +8954,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>BOBADILLA, Luz</t>
+          <t>GARCÍA, María Alejandra</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E166" s="9" t="n">
@@ -8964,17 +8967,20 @@
       </c>
       <c r="F166" s="8" t="inlineStr">
         <is>
-          <t>Norcenca Fort Lauderdale USA 2024</t>
+          <t>Norcenca Panamá 2023</t>
         </is>
       </c>
       <c r="G166" s="8" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="H166" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA166" s="11" t="n">
-        <v>-69</v>
+        <v>2</v>
+      </c>
+      <c r="AL166" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM166" s="11" t="n">
+        <v>-78</v>
       </c>
     </row>
     <row r="167">
@@ -8988,38 +8994,35 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>GARCÍA, María Alejandra</t>
+          <t>GONZÁLEZ ROMERO, Alejandro</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E167" s="9" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="F167" s="8" t="inlineStr">
         <is>
-          <t>Norcenca Panamá 2023</t>
+          <t>Norcenca Guanajuato 2025</t>
         </is>
       </c>
       <c r="G167" s="8" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="H167" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL167" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AM167" s="11" t="n">
-        <v>-78</v>
+        <v>1</v>
+      </c>
+      <c r="O167" s="11" t="n">
+        <v>-70</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="8" t="n">
-        <v>-70</v>
+        <v>-71</v>
       </c>
       <c r="B168" s="8" t="inlineStr">
         <is>
@@ -9028,35 +9031,35 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>GONZÁLEZ ROMERO, Alejandro</t>
+          <t>FERNÁNDEZ, Víctor</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="E168" s="9" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="F168" s="8" t="inlineStr">
         <is>
-          <t>Norcenca Guanajuato 2025</t>
+          <t>Austral Montevideo 2023</t>
         </is>
       </c>
       <c r="G168" s="8" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H168" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="O168" s="11" t="n">
-        <v>-70</v>
+      <c r="AO168" s="11" t="n">
+        <v>-71</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="8" t="n">
-        <v>-71</v>
+        <v>-72</v>
       </c>
       <c r="B169" s="8" t="inlineStr">
         <is>
@@ -9065,7 +9068,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>FERNÁNDEZ, Víctor</t>
+          <t>GIL CORDERO, Laura</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -9074,26 +9077,32 @@
         </is>
       </c>
       <c r="E169" s="9" t="n">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="F169" s="8" t="inlineStr">
         <is>
-          <t>Austral Montevideo 2023</t>
+          <t>Austral Asunción 2025</t>
         </is>
       </c>
       <c r="G169" s="8" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="H169" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="R169" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="AO169" s="11" t="n">
-        <v>-71</v>
+        <v>-82</v>
+      </c>
+      <c r="AZ169" s="10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="8" t="n">
-        <v>-72</v>
+        <v>-73</v>
       </c>
       <c r="B170" s="8" t="inlineStr">
         <is>
@@ -9102,12 +9111,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>GIL CORDERO, Laura</t>
+          <t>OTERO, Isabel</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="E170" s="9" t="n">
@@ -9115,28 +9124,22 @@
       </c>
       <c r="F170" s="8" t="inlineStr">
         <is>
-          <t>Austral Asunción 2025</t>
+          <t>Andino Caracas 2023</t>
         </is>
       </c>
       <c r="G170" s="8" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H170" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R170" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO170" s="11" t="n">
-        <v>-82</v>
-      </c>
-      <c r="AZ170" s="10" t="n">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="AN170" s="11" t="n">
+        <v>-73</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="8" t="n">
-        <v>-73</v>
+        <v>-74</v>
       </c>
       <c r="B171" s="8" t="inlineStr">
         <is>
@@ -9145,35 +9148,38 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>OTERO, Isabel</t>
+          <t>MELO, Francisco</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E171" s="9" t="n">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="F171" s="8" t="inlineStr">
         <is>
-          <t>Andino Caracas 2023</t>
+          <t>Andino Lima 2025</t>
         </is>
       </c>
       <c r="G171" s="8" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="H171" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN171" s="11" t="n">
-        <v>-73</v>
+        <v>2</v>
+      </c>
+      <c r="P171" s="11" t="n">
+        <v>-35</v>
+      </c>
+      <c r="Q171" s="11" t="n">
+        <v>-39</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="8" t="n">
-        <v>-74</v>
+        <v>-76</v>
       </c>
       <c r="B172" s="8" t="inlineStr">
         <is>
@@ -9182,38 +9188,56 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>MELO, Francisco</t>
+          <t>MONTOUT, Yosvany</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Cuba</t>
         </is>
       </c>
       <c r="E172" s="9" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="F172" s="8" t="inlineStr">
         <is>
-          <t>Andino Lima 2025</t>
+          <t>Cuba Scrabble Varadero 2025</t>
         </is>
       </c>
       <c r="G172" s="8" t="n">
+        <v>120</v>
+      </c>
+      <c r="H172" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="S172" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T172" s="11" t="n">
+        <v>-34</v>
+      </c>
+      <c r="AD172" s="11" t="n">
+        <v>-23</v>
+      </c>
+      <c r="AE172" s="11" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AP172" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ172" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="H172" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="P172" s="11" t="n">
-        <v>-35</v>
-      </c>
-      <c r="Q172" s="11" t="n">
-        <v>-39</v>
+      <c r="BA172" s="11" t="n">
+        <v>-4</v>
+      </c>
+      <c r="BB172" s="11" t="n">
+        <v>-45</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="8" t="n">
-        <v>-76</v>
+        <v>-79</v>
       </c>
       <c r="B173" s="8" t="inlineStr">
         <is>
@@ -9222,7 +9246,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>MONTOUT, Yosvany</t>
+          <t>BÁEZ, Luar</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -9231,7 +9255,7 @@
         </is>
       </c>
       <c r="E173" s="9" t="n">
-        <v>1999</v>
+        <v>1995</v>
       </c>
       <c r="F173" s="8" t="inlineStr">
         <is>
@@ -9239,39 +9263,30 @@
         </is>
       </c>
       <c r="G173" s="8" t="n">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="H173" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="S173" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="T173" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="S173" s="11" t="n">
         <v>-34</v>
       </c>
-      <c r="AD173" s="11" t="n">
-        <v>-23</v>
-      </c>
-      <c r="AE173" s="11" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AP173" s="10" t="n">
-        <v>0</v>
+      <c r="AP173" s="11" t="n">
+        <v>-47</v>
       </c>
       <c r="AQ173" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA173" s="11" t="n">
-        <v>-4</v>
+        <v>23</v>
+      </c>
+      <c r="BA173" s="10" t="n">
+        <v>14</v>
       </c>
       <c r="BB173" s="11" t="n">
-        <v>-45</v>
+        <v>-35</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="8" t="n">
-        <v>-79</v>
+        <v>-80</v>
       </c>
       <c r="B174" s="8" t="inlineStr">
         <is>
@@ -9280,12 +9295,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>BÁEZ, Luar</t>
+          <t>FALCONER, Pablo</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Cuba</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E174" s="9" t="n">
@@ -9293,71 +9308,83 @@
       </c>
       <c r="F174" s="8" t="inlineStr">
         <is>
-          <t>Cuba Scrabble Varadero 2025</t>
+          <t>Norcenca Guanajuato 2025</t>
         </is>
       </c>
       <c r="G174" s="8" t="n">
-        <v>81</v>
+        <v>16</v>
       </c>
       <c r="H174" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="S174" s="11" t="n">
-        <v>-34</v>
-      </c>
-      <c r="AP174" s="11" t="n">
-        <v>-47</v>
-      </c>
-      <c r="AQ174" s="10" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA174" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="BB174" s="11" t="n">
-        <v>-35</v>
+        <v>1</v>
+      </c>
+      <c r="O174" s="11" t="n">
+        <v>-80</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="8" t="n">
+        <v>-81</v>
+      </c>
+      <c r="B175" s="8" t="inlineStr">
+        <is>
+          <t>170°</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>AYALA, Mariana</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="E175" s="9" t="n">
+        <v>1994</v>
+      </c>
+      <c r="F175" s="8" t="inlineStr">
+        <is>
+          <t>Mundial Granada 2024</t>
+        </is>
+      </c>
+      <c r="G175" s="8" t="n">
+        <v>399</v>
+      </c>
+      <c r="H175" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="U175" s="11" t="n">
+        <v>-94</v>
+      </c>
+      <c r="W175" s="10" t="n">
+        <v>244</v>
+      </c>
+      <c r="Y175" s="11" t="n">
+        <v>-73</v>
+      </c>
+      <c r="AF175" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="AG175" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI175" s="10" t="n">
+        <v>78</v>
+      </c>
+      <c r="AR175" s="11" t="n">
         <v>-80</v>
       </c>
-      <c r="B175" s="8" t="inlineStr">
-        <is>
-          <t>170°</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>FALCONER, Pablo</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>México</t>
-        </is>
-      </c>
-      <c r="E175" s="9" t="n">
-        <v>1995</v>
-      </c>
-      <c r="F175" s="8" t="inlineStr">
-        <is>
-          <t>Norcenca Guanajuato 2025</t>
-        </is>
-      </c>
-      <c r="G175" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="H175" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O175" s="11" t="n">
-        <v>-80</v>
+      <c r="AT175" s="11" t="n">
+        <v>-85</v>
+      </c>
+      <c r="AV175" s="11" t="n">
+        <v>-220</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="8" t="n">
-        <v>-81</v>
+        <v>-82</v>
       </c>
       <c r="B176" s="8" t="inlineStr">
         <is>
@@ -9366,54 +9393,42 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>AYALA, Mariana</t>
+          <t>LINARES, Rafael</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Cuba</t>
         </is>
       </c>
       <c r="E176" s="9" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="F176" s="8" t="inlineStr">
         <is>
-          <t>Mundial Granada 2024</t>
+          <t>Cuba Scrabble Varadero 2025</t>
         </is>
       </c>
       <c r="G176" s="8" t="n">
-        <v>399</v>
+        <v>81</v>
       </c>
       <c r="H176" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="U176" s="11" t="n">
-        <v>-94</v>
-      </c>
-      <c r="W176" s="10" t="n">
-        <v>244</v>
-      </c>
-      <c r="Y176" s="11" t="n">
-        <v>-73</v>
-      </c>
-      <c r="AF176" s="10" t="n">
-        <v>99</v>
-      </c>
-      <c r="AG176" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="AI176" s="10" t="n">
-        <v>78</v>
-      </c>
-      <c r="AR176" s="11" t="n">
-        <v>-80</v>
-      </c>
-      <c r="AT176" s="11" t="n">
-        <v>-85</v>
-      </c>
-      <c r="AV176" s="11" t="n">
-        <v>-220</v>
+        <v>5</v>
+      </c>
+      <c r="S176" s="11" t="n">
+        <v>-21</v>
+      </c>
+      <c r="AP176" s="11" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AQ176" s="11" t="n">
+        <v>-57</v>
+      </c>
+      <c r="BA176" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB176" s="10" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="177">
@@ -9427,47 +9442,41 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>LINARES, Rafael</t>
+          <t>BLANCO, Yvette</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Cuba</t>
+          <t>España</t>
         </is>
       </c>
       <c r="E177" s="9" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="F177" s="8" t="inlineStr">
         <is>
-          <t>Cuba Scrabble Varadero 2025</t>
+          <t>Mundial Granada 2024</t>
         </is>
       </c>
       <c r="G177" s="8" t="n">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="H177" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="S177" s="11" t="n">
-        <v>-21</v>
-      </c>
-      <c r="AP177" s="11" t="n">
-        <v>-30</v>
-      </c>
-      <c r="AQ177" s="11" t="n">
-        <v>-57</v>
-      </c>
-      <c r="BA177" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB177" s="10" t="n">
-        <v>15</v>
+        <v>3</v>
+      </c>
+      <c r="U177" s="10" t="n">
+        <v>189</v>
+      </c>
+      <c r="W177" s="11" t="n">
+        <v>-328</v>
+      </c>
+      <c r="X177" s="10" t="n">
+        <v>57</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="8" t="n">
-        <v>-82</v>
+        <v>-83</v>
       </c>
       <c r="B178" s="8" t="inlineStr">
         <is>
@@ -9476,12 +9485,12 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>BLANCO, Yvette</t>
+          <t>MALAVÉ, Gladys</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="E178" s="9" t="n">
@@ -9489,28 +9498,22 @@
       </c>
       <c r="F178" s="8" t="inlineStr">
         <is>
-          <t>Mundial Granada 2024</t>
+          <t>Andino Caracas 2023</t>
         </is>
       </c>
       <c r="G178" s="8" t="n">
-        <v>119</v>
+        <v>37</v>
       </c>
       <c r="H178" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U178" s="10" t="n">
-        <v>189</v>
-      </c>
-      <c r="W178" s="11" t="n">
-        <v>-328</v>
-      </c>
-      <c r="X178" s="10" t="n">
-        <v>57</v>
+        <v>1</v>
+      </c>
+      <c r="AN178" s="11" t="n">
+        <v>-83</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="8" t="n">
-        <v>-83</v>
+        <v>-87</v>
       </c>
       <c r="B179" s="8" t="inlineStr">
         <is>
@@ -9519,35 +9522,47 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>MALAVÉ, Gladys</t>
+          <t>TRELLES, Josefina</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Cuba</t>
         </is>
       </c>
       <c r="E179" s="9" t="n">
-        <v>1992</v>
+        <v>1989</v>
       </c>
       <c r="F179" s="8" t="inlineStr">
         <is>
-          <t>Andino Caracas 2023</t>
+          <t>Cuba Scrabble Varadero 2025</t>
         </is>
       </c>
       <c r="G179" s="8" t="n">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="H179" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN179" s="11" t="n">
-        <v>-83</v>
+        <v>5</v>
+      </c>
+      <c r="S179" s="11" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AD179" s="11" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AE179" s="11" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AP179" s="11" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AQ179" s="11" t="n">
+        <v>-32</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="8" t="n">
-        <v>-87</v>
+        <v>-86</v>
       </c>
       <c r="B180" s="8" t="inlineStr">
         <is>
@@ -9556,12 +9571,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>TRELLES, Josefina</t>
+          <t>RONDÓN, Yolys</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Cuba</t>
+          <t>Panamá</t>
         </is>
       </c>
       <c r="E180" s="9" t="n">
@@ -9569,29 +9584,20 @@
       </c>
       <c r="F180" s="8" t="inlineStr">
         <is>
-          <t>Cuba Scrabble Varadero 2025</t>
+          <t>Norcenca Panamá 2023</t>
         </is>
       </c>
       <c r="G180" s="8" t="n">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="H180" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="S180" s="11" t="n">
-        <v>-8</v>
-      </c>
-      <c r="AD180" s="11" t="n">
-        <v>-7</v>
-      </c>
-      <c r="AE180" s="11" t="n">
-        <v>-20</v>
-      </c>
-      <c r="AP180" s="11" t="n">
-        <v>-20</v>
-      </c>
-      <c r="AQ180" s="11" t="n">
-        <v>-32</v>
+        <v>2</v>
+      </c>
+      <c r="AL180" s="11" t="n">
+        <v>-28</v>
+      </c>
+      <c r="AM180" s="11" t="n">
+        <v>-58</v>
       </c>
     </row>
     <row r="181">
@@ -9605,7 +9611,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>RONDÓN, Yolys</t>
+          <t>REYES, Grace</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -9618,25 +9624,25 @@
       </c>
       <c r="F181" s="8" t="inlineStr">
         <is>
-          <t>Norcenca Panamá 2023</t>
+          <t>Andino Bogotá 2022</t>
         </is>
       </c>
       <c r="G181" s="8" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H181" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="AL181" s="11" t="n">
-        <v>-28</v>
-      </c>
-      <c r="AM181" s="11" t="n">
-        <v>-58</v>
+      <c r="AX181" s="11" t="n">
+        <v>-41</v>
+      </c>
+      <c r="AY181" s="11" t="n">
+        <v>-45</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="8" t="n">
-        <v>-86</v>
+        <v>-89</v>
       </c>
       <c r="B182" s="8" t="inlineStr">
         <is>
@@ -9645,38 +9651,35 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>REYES, Grace</t>
+          <t>GUTIÉRREZ, Beatriz</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Panamá</t>
+          <t>Estados Unidos</t>
         </is>
       </c>
       <c r="E182" s="9" t="n">
-        <v>1989</v>
+        <v>1986</v>
       </c>
       <c r="F182" s="8" t="inlineStr">
         <is>
-          <t>Andino Bogotá 2022</t>
+          <t>Norcenca Fort Lauderdale USA 2024</t>
         </is>
       </c>
       <c r="G182" s="8" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="H182" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX182" s="11" t="n">
-        <v>-41</v>
-      </c>
-      <c r="AY182" s="11" t="n">
-        <v>-45</v>
+        <v>1</v>
+      </c>
+      <c r="AA182" s="11" t="n">
+        <v>-89</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="8" t="n">
-        <v>-89</v>
+        <v>-90</v>
       </c>
       <c r="B183" s="8" t="inlineStr">
         <is>
@@ -9685,35 +9688,38 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>GUTIÉRREZ, Beatriz</t>
+          <t>ARIAS, Julky</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>Cuba</t>
         </is>
       </c>
       <c r="E183" s="9" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="F183" s="8" t="inlineStr">
         <is>
-          <t>Norcenca Fort Lauderdale USA 2024</t>
+          <t>Cuba Scrabble Matanzas 2024</t>
         </is>
       </c>
       <c r="G183" s="8" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H183" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA183" s="11" t="n">
-        <v>-89</v>
+        <v>2</v>
+      </c>
+      <c r="AD183" s="11" t="n">
+        <v>-41</v>
+      </c>
+      <c r="AE183" s="11" t="n">
+        <v>-49</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="8" t="n">
-        <v>-90</v>
+        <v>-93</v>
       </c>
       <c r="B184" s="8" t="inlineStr">
         <is>
@@ -9722,38 +9728,35 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>ARIAS, Julky</t>
+          <t>BRESSÁN, Isvelis</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Cuba</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="E184" s="9" t="n">
-        <v>1985</v>
+        <v>1982</v>
       </c>
       <c r="F184" s="8" t="inlineStr">
         <is>
-          <t>Cuba Scrabble Matanzas 2024</t>
+          <t>Andino Caracas 2023</t>
         </is>
       </c>
       <c r="G184" s="8" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H184" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD184" s="11" t="n">
-        <v>-41</v>
-      </c>
-      <c r="AE184" s="11" t="n">
-        <v>-49</v>
+        <v>1</v>
+      </c>
+      <c r="AN184" s="11" t="n">
+        <v>-93</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="8" t="n">
-        <v>-93</v>
+        <v>-95</v>
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
@@ -9762,35 +9765,65 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>BRESSÁN, Isvelis</t>
+          <t>PIQUÉ, Xavier</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>España</t>
         </is>
       </c>
       <c r="E185" s="9" t="n">
-        <v>1982</v>
+        <v>1978</v>
       </c>
       <c r="F185" s="8" t="inlineStr">
         <is>
-          <t>Andino Caracas 2023</t>
+          <t>Europeo Murcia 2025</t>
         </is>
       </c>
       <c r="G185" s="8" t="n">
-        <v>37</v>
+        <v>487</v>
       </c>
       <c r="H185" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN185" s="11" t="n">
-        <v>-93</v>
+        <v>11</v>
+      </c>
+      <c r="N185" s="10" t="n">
+        <v>62</v>
+      </c>
+      <c r="U185" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="W185" s="11" t="n">
+        <v>-212</v>
+      </c>
+      <c r="Y185" s="10" t="n">
+        <v>207</v>
+      </c>
+      <c r="AF185" s="10" t="n">
+        <v>41</v>
+      </c>
+      <c r="AH185" s="11" t="n">
+        <v>-44</v>
+      </c>
+      <c r="AJ185" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK185" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR185" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AT185" s="11" t="n">
+        <v>-63</v>
+      </c>
+      <c r="AV185" s="11" t="n">
+        <v>-180</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="8" t="n">
-        <v>-95</v>
+        <v>-98</v>
       </c>
       <c r="B186" s="8" t="inlineStr">
         <is>
@@ -9799,65 +9832,38 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>PIQUÉ, Xavier</t>
+          <t>RENDÓN, Xavier</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Estados Unidos</t>
         </is>
       </c>
       <c r="E186" s="9" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="F186" s="8" t="inlineStr">
         <is>
-          <t>Europeo Murcia 2025</t>
+          <t>Norcenca Fort Lauderdale USA 2024</t>
         </is>
       </c>
       <c r="G186" s="8" t="n">
-        <v>487</v>
+        <v>26</v>
       </c>
       <c r="H186" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="N186" s="10" t="n">
-        <v>62</v>
-      </c>
-      <c r="U186" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="W186" s="11" t="n">
-        <v>-212</v>
-      </c>
-      <c r="Y186" s="10" t="n">
-        <v>207</v>
-      </c>
-      <c r="AF186" s="10" t="n">
-        <v>41</v>
-      </c>
-      <c r="AH186" s="11" t="n">
-        <v>-44</v>
-      </c>
-      <c r="AJ186" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK186" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR186" s="10" t="n">
-        <v>46</v>
-      </c>
-      <c r="AT186" s="11" t="n">
-        <v>-63</v>
-      </c>
-      <c r="AV186" s="11" t="n">
-        <v>-180</v>
+        <v>2</v>
+      </c>
+      <c r="AA186" s="11" t="n">
+        <v>-72</v>
+      </c>
+      <c r="AB186" s="11" t="n">
+        <v>-26</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="8" t="n">
-        <v>-98</v>
+        <v>-103</v>
       </c>
       <c r="B187" s="8" t="inlineStr">
         <is>
@@ -9866,33 +9872,30 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>RENDÓN, Xavier</t>
+          <t>COLMENARES, Yugli</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="E187" s="9" t="n">
-        <v>1977</v>
+        <v>1972</v>
       </c>
       <c r="F187" s="8" t="inlineStr">
         <is>
-          <t>Norcenca Fort Lauderdale USA 2024</t>
+          <t>Andino Caracas 2023</t>
         </is>
       </c>
       <c r="G187" s="8" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H187" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA187" s="11" t="n">
-        <v>-72</v>
-      </c>
-      <c r="AB187" s="11" t="n">
-        <v>-26</v>
+        <v>1</v>
+      </c>
+      <c r="AN187" s="11" t="n">
+        <v>-103</v>
       </c>
     </row>
     <row r="188">
@@ -9906,12 +9909,12 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>COLMENARES, Yugli</t>
+          <t>LÓPEZ, LuzMaría</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E188" s="9" t="n">
@@ -9919,22 +9922,25 @@
       </c>
       <c r="F188" s="8" t="inlineStr">
         <is>
-          <t>Andino Caracas 2023</t>
+          <t>Andino Bogotá 2022</t>
         </is>
       </c>
       <c r="G188" s="8" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H188" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN188" s="11" t="n">
-        <v>-103</v>
+        <v>2</v>
+      </c>
+      <c r="AX188" s="11" t="n">
+        <v>-48</v>
+      </c>
+      <c r="AY188" s="11" t="n">
+        <v>-55</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="8" t="n">
-        <v>-103</v>
+        <v>-105</v>
       </c>
       <c r="B189" s="8" t="inlineStr">
         <is>
@@ -9943,7 +9949,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>LÓPEZ, LuzMaría</t>
+          <t>MONTAÑEZ, Carmen</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -9952,7 +9958,7 @@
         </is>
       </c>
       <c r="E189" s="9" t="n">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="F189" s="8" t="inlineStr">
         <is>
@@ -9966,55 +9972,103 @@
         <v>2</v>
       </c>
       <c r="AX189" s="11" t="n">
-        <v>-48</v>
+        <v>-20</v>
       </c>
       <c r="AY189" s="11" t="n">
-        <v>-55</v>
+        <v>-85</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="8" t="n">
+        <v>-104</v>
+      </c>
+      <c r="B190" s="8" t="inlineStr">
+        <is>
+          <t>185°</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>HACKSHAW, Yolanda</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Panamá</t>
+        </is>
+      </c>
+      <c r="E190" s="9" t="n">
+        <v>1969</v>
+      </c>
+      <c r="F190" s="8" t="inlineStr">
+        <is>
+          <t>Mundial Santiago de Chile 2025</t>
+        </is>
+      </c>
+      <c r="G190" s="8" t="n">
+        <v>519</v>
+      </c>
+      <c r="H190" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="I190" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="K190" s="11" t="n">
+        <v>-24</v>
+      </c>
+      <c r="M190" s="11" t="n">
+        <v>-18</v>
+      </c>
+      <c r="R190" s="11" t="n">
+        <v>-40</v>
+      </c>
+      <c r="U190" s="11" t="n">
+        <v>-66</v>
+      </c>
+      <c r="V190" s="10" t="n">
+        <v>130</v>
+      </c>
+      <c r="X190" s="10" t="n">
+        <v>148</v>
+      </c>
+      <c r="AB190" s="10" t="n">
+        <v>73</v>
+      </c>
+      <c r="AF190" s="11" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AH190" s="11" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AJ190" s="11" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AL190" s="11" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AM190" s="11" t="n">
+        <v>-11</v>
+      </c>
+      <c r="AR190" s="11" t="n">
+        <v>-36</v>
+      </c>
+      <c r="AT190" s="11" t="n">
+        <v>-118</v>
+      </c>
+      <c r="AV190" s="11" t="n">
+        <v>-21</v>
+      </c>
+      <c r="AX190" s="11" t="n">
+        <v>-44</v>
+      </c>
+      <c r="AY190" s="11" t="n">
         <v>-105</v>
-      </c>
-      <c r="B190" s="8" t="inlineStr">
-        <is>
-          <t>185°</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>MONTAÑEZ, Carmen</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="E190" s="9" t="n">
-        <v>1970</v>
-      </c>
-      <c r="F190" s="8" t="inlineStr">
-        <is>
-          <t>Andino Bogotá 2022</t>
-        </is>
-      </c>
-      <c r="G190" s="8" t="n">
-        <v>42</v>
-      </c>
-      <c r="H190" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX190" s="11" t="n">
-        <v>-20</v>
-      </c>
-      <c r="AY190" s="11" t="n">
-        <v>-85</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="8" t="n">
-        <v>-104</v>
+        <v>-106</v>
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
@@ -10023,12 +10077,12 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>HACKSHAW, Yolanda</t>
+          <t>GELY, Emmanuel</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Panamá</t>
+          <t>Guatemala</t>
         </is>
       </c>
       <c r="E191" s="9" t="n">
@@ -10036,73 +10090,25 @@
       </c>
       <c r="F191" s="8" t="inlineStr">
         <is>
-          <t>Mundial Santiago de Chile 2025</t>
+          <t>Norcenca Panamá 2023</t>
         </is>
       </c>
       <c r="G191" s="8" t="n">
-        <v>519</v>
+        <v>50</v>
       </c>
       <c r="H191" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="I191" s="10" t="n">
-        <v>82</v>
-      </c>
-      <c r="K191" s="11" t="n">
-        <v>-24</v>
-      </c>
-      <c r="M191" s="11" t="n">
-        <v>-18</v>
-      </c>
-      <c r="R191" s="11" t="n">
-        <v>-40</v>
-      </c>
-      <c r="U191" s="11" t="n">
-        <v>-66</v>
-      </c>
-      <c r="V191" s="10" t="n">
-        <v>130</v>
-      </c>
-      <c r="X191" s="10" t="n">
-        <v>148</v>
-      </c>
-      <c r="AB191" s="10" t="n">
-        <v>73</v>
-      </c>
-      <c r="AF191" s="11" t="n">
-        <v>-7</v>
-      </c>
-      <c r="AH191" s="11" t="n">
-        <v>-8</v>
-      </c>
-      <c r="AJ191" s="11" t="n">
-        <v>-30</v>
+        <v>2</v>
       </c>
       <c r="AL191" s="11" t="n">
-        <v>-9</v>
+        <v>-78</v>
       </c>
       <c r="AM191" s="11" t="n">
-        <v>-11</v>
-      </c>
-      <c r="AR191" s="11" t="n">
-        <v>-36</v>
-      </c>
-      <c r="AT191" s="11" t="n">
-        <v>-118</v>
-      </c>
-      <c r="AV191" s="11" t="n">
-        <v>-21</v>
-      </c>
-      <c r="AX191" s="11" t="n">
-        <v>-44</v>
-      </c>
-      <c r="AY191" s="11" t="n">
-        <v>-105</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="8" t="n">
-        <v>-106</v>
+        <v>-108</v>
       </c>
       <c r="B192" s="8" t="inlineStr">
         <is>
@@ -10111,33 +10117,33 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>GELY, Emmanuel</t>
+          <t>SAMUEL, Kevin</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Guatemala</t>
+          <t>Cuba</t>
         </is>
       </c>
       <c r="E192" s="9" t="n">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="F192" s="8" t="inlineStr">
         <is>
-          <t>Norcenca Panamá 2023</t>
+          <t>Cuba Scrabble Matanzas 2024</t>
         </is>
       </c>
       <c r="G192" s="8" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="H192" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="AL192" s="11" t="n">
-        <v>-78</v>
-      </c>
-      <c r="AM192" s="11" t="n">
-        <v>-28</v>
+      <c r="AD192" s="11" t="n">
+        <v>-49</v>
+      </c>
+      <c r="AE192" s="11" t="n">
+        <v>-59</v>
       </c>
     </row>
     <row r="193">
@@ -10151,12 +10157,12 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>SAMUEL, Kevin</t>
+          <t>DÍAZ, Solange</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Cuba</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="E193" s="9" t="n">
@@ -10164,25 +10170,28 @@
       </c>
       <c r="F193" s="8" t="inlineStr">
         <is>
-          <t>Cuba Scrabble Matanzas 2024</t>
+          <t>Mundial Buenos Aires 2022</t>
         </is>
       </c>
       <c r="G193" s="8" t="n">
-        <v>26</v>
+        <v>133</v>
       </c>
       <c r="H193" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD193" s="11" t="n">
-        <v>-49</v>
-      </c>
-      <c r="AE193" s="11" t="n">
-        <v>-59</v>
+        <v>3</v>
+      </c>
+      <c r="AR193" s="10" t="n">
+        <v>170</v>
+      </c>
+      <c r="AT193" s="11" t="n">
+        <v>-88</v>
+      </c>
+      <c r="AV193" s="11" t="n">
+        <v>-190</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="8" t="n">
-        <v>-108</v>
+        <v>-109</v>
       </c>
       <c r="B194" s="8" t="inlineStr">
         <is>
@@ -10191,41 +10200,62 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>DÍAZ, Solange</t>
+          <t>RODRIGO, Isabel</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E194" s="9" t="n">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="F194" s="8" t="inlineStr">
         <is>
-          <t>Mundial Buenos Aires 2022</t>
+          <t>Andino Lima 2025</t>
         </is>
       </c>
       <c r="G194" s="8" t="n">
-        <v>133</v>
+        <v>185</v>
       </c>
       <c r="H194" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR194" s="10" t="n">
-        <v>170</v>
-      </c>
-      <c r="AT194" s="11" t="n">
-        <v>-88</v>
-      </c>
-      <c r="AV194" s="11" t="n">
-        <v>-190</v>
+        <v>10</v>
+      </c>
+      <c r="P194" s="10" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q194" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="U194" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="V194" s="11" t="n">
+        <v>-64</v>
+      </c>
+      <c r="X194" s="11" t="n">
+        <v>-81</v>
+      </c>
+      <c r="AF194" s="11" t="n">
+        <v>-48</v>
+      </c>
+      <c r="AG194" s="11" t="n">
+        <v>-28</v>
+      </c>
+      <c r="AI194" s="11" t="n">
+        <v>-73</v>
+      </c>
+      <c r="AL194" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM194" s="10" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="8" t="n">
-        <v>-109</v>
+        <v>-113</v>
       </c>
       <c r="B195" s="8" t="inlineStr">
         <is>
@@ -10234,62 +10264,35 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>RODRIGO, Isabel</t>
+          <t>GUÍA, Luncy</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="E195" s="9" t="n">
-        <v>1966</v>
+        <v>1962</v>
       </c>
       <c r="F195" s="8" t="inlineStr">
         <is>
-          <t>Andino Lima 2025</t>
+          <t>Andino Caracas 2023</t>
         </is>
       </c>
       <c r="G195" s="8" t="n">
-        <v>185</v>
+        <v>37</v>
       </c>
       <c r="H195" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="P195" s="10" t="n">
-        <v>47</v>
-      </c>
-      <c r="Q195" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="U195" s="10" t="n">
-        <v>56</v>
-      </c>
-      <c r="V195" s="11" t="n">
-        <v>-64</v>
-      </c>
-      <c r="X195" s="11" t="n">
-        <v>-81</v>
-      </c>
-      <c r="AF195" s="11" t="n">
-        <v>-48</v>
-      </c>
-      <c r="AG195" s="11" t="n">
-        <v>-28</v>
-      </c>
-      <c r="AI195" s="11" t="n">
-        <v>-73</v>
-      </c>
-      <c r="AL195" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM195" s="10" t="n">
-        <v>32</v>
+        <v>1</v>
+      </c>
+      <c r="AN195" s="11" t="n">
+        <v>-113</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="8" t="n">
-        <v>-113</v>
+        <v>-114</v>
       </c>
       <c r="B196" s="8" t="inlineStr">
         <is>
@@ -10298,12 +10301,12 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>GUÍAS, Luncy</t>
+          <t>VERÁSTEGUI, Nelson</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="E196" s="9" t="n">
@@ -10311,17 +10314,35 @@
       </c>
       <c r="F196" s="8" t="inlineStr">
         <is>
-          <t>Andino Caracas 2023</t>
+          <t>Mundial Granada 2024</t>
         </is>
       </c>
       <c r="G196" s="8" t="n">
-        <v>37</v>
+        <v>277</v>
       </c>
       <c r="H196" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN196" s="11" t="n">
-        <v>-113</v>
+        <v>7</v>
+      </c>
+      <c r="U196" s="11" t="n">
+        <v>-54</v>
+      </c>
+      <c r="W196" s="10" t="n">
+        <v>121</v>
+      </c>
+      <c r="Y196" s="11" t="n">
+        <v>-196</v>
+      </c>
+      <c r="Z196" s="11" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AW196" s="11" t="n">
+        <v>-54</v>
+      </c>
+      <c r="AX196" s="10" t="n">
+        <v>47</v>
+      </c>
+      <c r="AY196" s="10" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="197">
@@ -10335,53 +10356,38 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>VERÁSTEGUI, Nelson</t>
+          <t>GRUNFELD, Sara</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Francia</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E197" s="9" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="F197" s="8" t="inlineStr">
         <is>
-          <t>Mundial Granada 2024</t>
+          <t>Norcenca/Cuba Scrabble La Habana 2022</t>
         </is>
       </c>
       <c r="G197" s="8" t="n">
-        <v>277</v>
+        <v>34</v>
       </c>
       <c r="H197" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="U197" s="11" t="n">
-        <v>-54</v>
-      </c>
-      <c r="W197" s="10" t="n">
-        <v>121</v>
-      </c>
-      <c r="Y197" s="11" t="n">
-        <v>-196</v>
-      </c>
-      <c r="Z197" s="11" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AW197" s="11" t="n">
-        <v>-54</v>
-      </c>
-      <c r="AX197" s="10" t="n">
-        <v>47</v>
-      </c>
-      <c r="AY197" s="10" t="n">
-        <v>25</v>
+        <v>2</v>
+      </c>
+      <c r="BA197" s="11" t="n">
+        <v>-49</v>
+      </c>
+      <c r="BB197" s="11" t="n">
+        <v>-65</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="8" t="n">
-        <v>-114</v>
+        <v>-123</v>
       </c>
       <c r="B198" s="8" t="inlineStr">
         <is>
@@ -10390,38 +10396,35 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>GRUNFELD, Sara</t>
+          <t>LUGO, Mery</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="E198" s="9" t="n">
-        <v>1961</v>
+        <v>1952</v>
       </c>
       <c r="F198" s="8" t="inlineStr">
         <is>
-          <t>Norcenca/Cuba Scrabble La Habana 2022</t>
+          <t>Andino Caracas 2023</t>
         </is>
       </c>
       <c r="G198" s="8" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H198" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA198" s="11" t="n">
-        <v>-49</v>
-      </c>
-      <c r="BB198" s="11" t="n">
-        <v>-65</v>
+        <v>1</v>
+      </c>
+      <c r="AN198" s="11" t="n">
+        <v>-123</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="8" t="n">
-        <v>-123</v>
+        <v>-132</v>
       </c>
       <c r="B199" s="8" t="inlineStr">
         <is>
@@ -10430,7 +10433,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>GARCÍA, Rebeca</t>
+          <t>TOPEL, Raquel</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -10439,26 +10442,62 @@
         </is>
       </c>
       <c r="E199" s="9" t="n">
-        <v>1952</v>
+        <v>1944</v>
       </c>
       <c r="F199" s="8" t="inlineStr">
         <is>
-          <t>Andino Caracas 2023</t>
+          <t>Mundial Santiago de Chile 2025</t>
         </is>
       </c>
       <c r="G199" s="8" t="n">
-        <v>37</v>
+        <v>468</v>
       </c>
       <c r="H199" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN199" s="11" t="n">
-        <v>-123</v>
+        <v>13</v>
+      </c>
+      <c r="I199" s="11" t="n">
+        <v>-47</v>
+      </c>
+      <c r="K199" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="M199" s="11" t="n">
+        <v>-33</v>
+      </c>
+      <c r="O199" s="11" t="n">
+        <v>-96</v>
+      </c>
+      <c r="U199" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W199" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y199" s="10" t="n">
+        <v>93</v>
+      </c>
+      <c r="AD199" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AE199" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="AK199" s="11" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AR199" s="11" t="n">
+        <v>-184</v>
+      </c>
+      <c r="AT199" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AV199" s="11" t="n">
+        <v>-50</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="8" t="n">
-        <v>-132</v>
+        <v>-133</v>
       </c>
       <c r="B200" s="8" t="inlineStr">
         <is>
@@ -10467,66 +10506,48 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>TOPEL, Raquel</t>
+          <t>VERÁSTEGUI, Coni</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="E200" s="9" t="n">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="F200" s="8" t="inlineStr">
         <is>
-          <t>Mundial Santiago de Chile 2025</t>
+          <t>Mundial Granada 2024</t>
         </is>
       </c>
       <c r="G200" s="8" t="n">
-        <v>468</v>
+        <v>128</v>
       </c>
       <c r="H200" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="I200" s="11" t="n">
-        <v>-47</v>
-      </c>
-      <c r="K200" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="M200" s="11" t="n">
-        <v>-33</v>
-      </c>
-      <c r="O200" s="11" t="n">
-        <v>-96</v>
-      </c>
-      <c r="U200" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W200" s="10" t="n">
-        <v>35</v>
-      </c>
-      <c r="Y200" s="10" t="n">
-        <v>93</v>
-      </c>
-      <c r="AD200" s="10" t="n">
-        <v>70</v>
-      </c>
-      <c r="AE200" s="10" t="n">
-        <v>35</v>
-      </c>
-      <c r="AK200" s="11" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AR200" s="11" t="n">
-        <v>-184</v>
-      </c>
-      <c r="AT200" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="AV200" s="11" t="n">
-        <v>-50</v>
+        <v>7</v>
+      </c>
+      <c r="U200" s="11" t="n">
+        <v>-41</v>
+      </c>
+      <c r="V200" s="10" t="n">
+        <v>54</v>
+      </c>
+      <c r="X200" s="10" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z200" s="11" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AW200" s="11" t="n">
+        <v>-40</v>
+      </c>
+      <c r="AX200" s="11" t="n">
+        <v>-73</v>
+      </c>
+      <c r="AY200" s="11" t="n">
+        <v>-75</v>
       </c>
     </row>
     <row r="201">
@@ -10540,53 +10561,59 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>VERÁSTEGUI, Coni</t>
+          <t>CHOWELL, Karlo</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Francia</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E201" s="9" t="n">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="F201" s="8" t="inlineStr">
         <is>
-          <t>Mundial Granada 2024</t>
+          <t>Mundial Santiago de Chile 2025</t>
         </is>
       </c>
       <c r="G201" s="8" t="n">
-        <v>128</v>
+        <v>313</v>
       </c>
       <c r="H201" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="J201" s="10" t="n">
+        <v>53</v>
+      </c>
+      <c r="L201" s="10" t="n">
+        <v>76</v>
+      </c>
+      <c r="O201" s="10" t="n">
+        <v>60</v>
       </c>
       <c r="U201" s="11" t="n">
-        <v>-41</v>
-      </c>
-      <c r="V201" s="10" t="n">
-        <v>54</v>
-      </c>
-      <c r="X201" s="10" t="n">
-        <v>52</v>
-      </c>
-      <c r="Z201" s="11" t="n">
         <v>-10</v>
       </c>
-      <c r="AW201" s="11" t="n">
-        <v>-40</v>
-      </c>
-      <c r="AX201" s="11" t="n">
-        <v>-73</v>
-      </c>
-      <c r="AY201" s="11" t="n">
-        <v>-75</v>
+      <c r="W201" s="11" t="n">
+        <v>-44</v>
+      </c>
+      <c r="Y201" s="11" t="n">
+        <v>-186</v>
+      </c>
+      <c r="AF201" s="11" t="n">
+        <v>-71</v>
+      </c>
+      <c r="AG201" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI201" s="11" t="n">
+        <v>-17</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="8" t="n">
-        <v>-133</v>
+        <v>-143</v>
       </c>
       <c r="B202" s="8" t="inlineStr">
         <is>
@@ -10595,59 +10622,35 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>CHOWELL, Karlo</t>
+          <t>SALAS, Carmen Elena</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="E202" s="9" t="n">
-        <v>1941</v>
+        <v>1932</v>
       </c>
       <c r="F202" s="8" t="inlineStr">
         <is>
-          <t>Mundial Santiago de Chile 2025</t>
+          <t>Andino Caracas 2023</t>
         </is>
       </c>
       <c r="G202" s="8" t="n">
-        <v>313</v>
+        <v>37</v>
       </c>
       <c r="H202" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="J202" s="10" t="n">
-        <v>53</v>
-      </c>
-      <c r="L202" s="10" t="n">
-        <v>76</v>
-      </c>
-      <c r="O202" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="U202" s="11" t="n">
-        <v>-10</v>
-      </c>
-      <c r="W202" s="11" t="n">
-        <v>-44</v>
-      </c>
-      <c r="Y202" s="11" t="n">
-        <v>-186</v>
-      </c>
-      <c r="AF202" s="11" t="n">
-        <v>-71</v>
-      </c>
-      <c r="AG202" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI202" s="11" t="n">
-        <v>-17</v>
+        <v>1</v>
+      </c>
+      <c r="AN202" s="11" t="n">
+        <v>-143</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="8" t="n">
-        <v>-143</v>
+        <v>-145</v>
       </c>
       <c r="B203" s="8" t="inlineStr">
         <is>
@@ -10656,35 +10659,44 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>SALAS, Carmen Elena</t>
+          <t>VELASCO, Liliana</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E203" s="9" t="n">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="F203" s="8" t="inlineStr">
         <is>
-          <t>Andino Caracas 2023</t>
+          <t>Norcenca Panamá 2023</t>
         </is>
       </c>
       <c r="G203" s="8" t="n">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="H203" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN203" s="11" t="n">
-        <v>-143</v>
+        <v>4</v>
+      </c>
+      <c r="AL203" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AM203" s="11" t="n">
+        <v>-67</v>
+      </c>
+      <c r="AX203" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY203" s="11" t="n">
+        <v>-95</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="8" t="n">
-        <v>-145</v>
+        <v>-149</v>
       </c>
       <c r="B204" s="8" t="inlineStr">
         <is>
@@ -10693,44 +10705,38 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>VELASCO, Liliana</t>
+          <t>HINOJOSA, Rodrigo</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="E204" s="9" t="n">
-        <v>1931</v>
+        <v>1926</v>
       </c>
       <c r="F204" s="8" t="inlineStr">
         <is>
-          <t>Norcenca Panamá 2023</t>
+          <t>Norcenca/Cuba Scrabble La Habana 2022</t>
         </is>
       </c>
       <c r="G204" s="8" t="n">
-        <v>92</v>
+        <v>34</v>
       </c>
       <c r="H204" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AL204" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AM204" s="11" t="n">
-        <v>-67</v>
-      </c>
-      <c r="AX204" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY204" s="11" t="n">
-        <v>-95</v>
+        <v>2</v>
+      </c>
+      <c r="BA204" s="11" t="n">
+        <v>-64</v>
+      </c>
+      <c r="BB204" s="11" t="n">
+        <v>-85</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="8" t="n">
-        <v>-149</v>
+        <v>-152</v>
       </c>
       <c r="B205" s="8" t="inlineStr">
         <is>
@@ -10739,38 +10745,44 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>HINOJOSA, Rodrigo</t>
+          <t>PULIDO, Wilma</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="E205" s="9" t="n">
-        <v>1926</v>
+        <v>1923</v>
       </c>
       <c r="F205" s="8" t="inlineStr">
         <is>
-          <t>Norcenca/Cuba Scrabble La Habana 2022</t>
+          <t>Mundial Granada 2024</t>
         </is>
       </c>
       <c r="G205" s="8" t="n">
-        <v>34</v>
+        <v>254</v>
       </c>
       <c r="H205" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA205" s="11" t="n">
-        <v>-64</v>
-      </c>
-      <c r="BB205" s="11" t="n">
-        <v>-85</v>
+        <v>4</v>
+      </c>
+      <c r="U205" s="10" t="n">
+        <v>95</v>
+      </c>
+      <c r="W205" s="11" t="n">
+        <v>-145</v>
+      </c>
+      <c r="Y205" s="10" t="n">
+        <v>61</v>
+      </c>
+      <c r="AN205" s="11" t="n">
+        <v>-163</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="8" t="n">
-        <v>-152</v>
+        <v>-154</v>
       </c>
       <c r="B206" s="8" t="inlineStr">
         <is>
@@ -10779,44 +10791,44 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>PULIDO, Wilma</t>
+          <t>RIERA, José María</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>España</t>
         </is>
       </c>
       <c r="E206" s="9" t="n">
-        <v>1923</v>
+        <v>1921</v>
       </c>
       <c r="F206" s="8" t="inlineStr">
         <is>
-          <t>Mundial Granada 2024</t>
+          <t>Europeo Murcia 2025</t>
         </is>
       </c>
       <c r="G206" s="8" t="n">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="H206" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="U206" s="10" t="n">
-        <v>95</v>
-      </c>
-      <c r="W206" s="11" t="n">
-        <v>-145</v>
-      </c>
-      <c r="Y206" s="10" t="n">
-        <v>61</v>
-      </c>
-      <c r="AN206" s="11" t="n">
-        <v>-163</v>
+      <c r="N206" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U206" s="11" t="n">
+        <v>-29</v>
+      </c>
+      <c r="W206" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y206" s="11" t="n">
+        <v>-171</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="8" t="n">
-        <v>-154</v>
+        <v>-160</v>
       </c>
       <c r="B207" s="8" t="inlineStr">
         <is>
@@ -10825,44 +10837,44 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>RIERA, José María</t>
+          <t>SAYEGH, Ricardo</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="E207" s="9" t="n">
-        <v>1921</v>
+        <v>1915</v>
       </c>
       <c r="F207" s="8" t="inlineStr">
         <is>
-          <t>Europeo Murcia 2025</t>
+          <t>Mundial Granada 2024</t>
         </is>
       </c>
       <c r="G207" s="8" t="n">
-        <v>234</v>
+        <v>105</v>
       </c>
       <c r="H207" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="N207" s="10" t="n">
-        <v>1</v>
-      </c>
       <c r="U207" s="11" t="n">
-        <v>-29</v>
-      </c>
-      <c r="W207" s="10" t="n">
-        <v>45</v>
-      </c>
-      <c r="Y207" s="11" t="n">
-        <v>-171</v>
+        <v>-86</v>
+      </c>
+      <c r="V207" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="X207" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN207" s="11" t="n">
+        <v>-153</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="8" t="n">
-        <v>-160</v>
+        <v>-168</v>
       </c>
       <c r="B208" s="8" t="inlineStr">
         <is>
@@ -10871,44 +10883,47 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>SAYEGH, Ricardo</t>
+          <t>LUCHINI, María de Jesús</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E208" s="9" t="n">
-        <v>1915</v>
+        <v>1906</v>
       </c>
       <c r="F208" s="8" t="inlineStr">
         <is>
-          <t>Mundial Granada 2024</t>
+          <t>Mundial Santiago de Chile 2025</t>
         </is>
       </c>
       <c r="G208" s="8" t="n">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="H208" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="U208" s="11" t="n">
-        <v>-86</v>
-      </c>
-      <c r="V208" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="X208" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN208" s="11" t="n">
-        <v>-153</v>
+        <v>5</v>
+      </c>
+      <c r="J208" s="11" t="n">
+        <v>-35</v>
+      </c>
+      <c r="L208" s="11" t="n">
+        <v>-20</v>
+      </c>
+      <c r="U208" s="10" t="n">
+        <v>51</v>
+      </c>
+      <c r="V208" s="11" t="n">
+        <v>-71</v>
+      </c>
+      <c r="X208" s="11" t="n">
+        <v>-93</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="8" t="n">
-        <v>-168</v>
+        <v>-172</v>
       </c>
       <c r="B209" s="8" t="inlineStr">
         <is>
@@ -10917,7 +10932,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>LUCHINI, María de Jesús</t>
+          <t>BALAJOVSKY, Adrián</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -10926,38 +10941,53 @@
         </is>
       </c>
       <c r="E209" s="9" t="n">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="F209" s="8" t="inlineStr">
         <is>
-          <t>Mundial Santiago de Chile 2025</t>
+          <t>Austral Asunción 2025</t>
         </is>
       </c>
       <c r="G209" s="8" t="n">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="H209" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="J209" s="11" t="n">
-        <v>-35</v>
-      </c>
-      <c r="L209" s="11" t="n">
-        <v>-20</v>
+        <v>10</v>
+      </c>
+      <c r="R209" s="11" t="n">
+        <v>-12</v>
+      </c>
+      <c r="T209" s="10" t="n">
+        <v>16</v>
       </c>
       <c r="U209" s="10" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="V209" s="11" t="n">
-        <v>-71</v>
+        <v>-82</v>
       </c>
       <c r="X209" s="11" t="n">
-        <v>-93</v>
+        <v>-108</v>
+      </c>
+      <c r="AA209" s="10" t="n">
+        <v>61</v>
+      </c>
+      <c r="AO209" s="11" t="n">
+        <v>-56</v>
+      </c>
+      <c r="AS209" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU209" s="11" t="n">
+        <v>-13</v>
+      </c>
+      <c r="AZ209" s="11" t="n">
+        <v>-25</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="8" t="n">
-        <v>-172</v>
+        <v>-173</v>
       </c>
       <c r="B210" s="8" t="inlineStr">
         <is>
@@ -10966,62 +10996,35 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>BALAJOVSKY, Adrián</t>
+          <t>CARRERAS, Juan</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="E210" s="9" t="n">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="F210" s="8" t="inlineStr">
         <is>
-          <t>Austral Asunción 2025</t>
+          <t>Andino Caracas 2023</t>
         </is>
       </c>
       <c r="G210" s="8" t="n">
-        <v>155</v>
+        <v>37</v>
       </c>
       <c r="H210" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="R210" s="11" t="n">
-        <v>-12</v>
-      </c>
-      <c r="T210" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="U210" s="10" t="n">
-        <v>33</v>
-      </c>
-      <c r="V210" s="11" t="n">
-        <v>-82</v>
-      </c>
-      <c r="X210" s="11" t="n">
-        <v>-108</v>
-      </c>
-      <c r="AA210" s="10" t="n">
-        <v>61</v>
-      </c>
-      <c r="AO210" s="11" t="n">
-        <v>-56</v>
-      </c>
-      <c r="AS210" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU210" s="11" t="n">
-        <v>-13</v>
-      </c>
-      <c r="AZ210" s="11" t="n">
-        <v>-25</v>
+        <v>1</v>
+      </c>
+      <c r="AN210" s="11" t="n">
+        <v>-173</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="8" t="n">
-        <v>-173</v>
+        <v>-175</v>
       </c>
       <c r="B211" s="8" t="inlineStr">
         <is>
@@ -11030,35 +11033,41 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>CARRERAS, Juan</t>
+          <t>PICO, Antonio</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E211" s="9" t="n">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="F211" s="8" t="inlineStr">
         <is>
-          <t>Andino Caracas 2023</t>
+          <t>Mundial Buenos Aires 2022</t>
         </is>
       </c>
       <c r="G211" s="8" t="n">
-        <v>37</v>
+        <v>133</v>
       </c>
       <c r="H211" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN211" s="11" t="n">
-        <v>-173</v>
+        <v>3</v>
+      </c>
+      <c r="AR211" s="11" t="n">
+        <v>-70</v>
+      </c>
+      <c r="AT211" s="11" t="n">
+        <v>-185</v>
+      </c>
+      <c r="AV211" s="10" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="8" t="n">
-        <v>-175</v>
+        <v>-188</v>
       </c>
       <c r="B212" s="8" t="inlineStr">
         <is>
@@ -11067,41 +11076,38 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>PICO, Antonio</t>
+          <t>VILLACÍS, Ricardo</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="E212" s="9" t="n">
-        <v>1900</v>
+        <v>1887</v>
       </c>
       <c r="F212" s="8" t="inlineStr">
         <is>
-          <t>Mundial Buenos Aires 2022</t>
+          <t>Norcenca Fort Lauderdale USA 2024</t>
         </is>
       </c>
       <c r="G212" s="8" t="n">
-        <v>133</v>
+        <v>39</v>
       </c>
       <c r="H212" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR212" s="11" t="n">
-        <v>-70</v>
-      </c>
-      <c r="AT212" s="11" t="n">
-        <v>-185</v>
-      </c>
-      <c r="AV212" s="10" t="n">
-        <v>80</v>
+        <v>2</v>
+      </c>
+      <c r="AA212" s="11" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN212" s="11" t="n">
+        <v>-183</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="8" t="n">
-        <v>-183</v>
+        <v>-194</v>
       </c>
       <c r="B213" s="8" t="inlineStr">
         <is>
@@ -11110,35 +11116,44 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>VILLEGAS, Evelyn</t>
+          <t>WHEATON, Merry</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Estados Unidos</t>
         </is>
       </c>
       <c r="E213" s="9" t="n">
-        <v>1892</v>
+        <v>1880</v>
       </c>
       <c r="F213" s="8" t="inlineStr">
         <is>
-          <t>Andino Caracas 2023</t>
+          <t>Mundial Granada 2024</t>
         </is>
       </c>
       <c r="G213" s="8" t="n">
-        <v>37</v>
+        <v>137</v>
       </c>
       <c r="H213" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN213" s="11" t="n">
-        <v>-183</v>
+        <v>4</v>
+      </c>
+      <c r="U213" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="V213" s="10" t="n">
+        <v>103</v>
+      </c>
+      <c r="Y213" s="11" t="n">
+        <v>-331</v>
+      </c>
+      <c r="AA213" s="10" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="8" t="n">
-        <v>-194</v>
+        <v>-200</v>
       </c>
       <c r="B214" s="8" t="inlineStr">
         <is>
@@ -11147,44 +11162,41 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>WHEATON, Merry</t>
+          <t>MARTÍNEZ GUALCO, Federico</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E214" s="9" t="n">
-        <v>1880</v>
+        <v>1875</v>
       </c>
       <c r="F214" s="8" t="inlineStr">
         <is>
-          <t>Mundial Granada 2024</t>
+          <t>Mundial Buenos Aires 2022</t>
         </is>
       </c>
       <c r="G214" s="8" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="H214" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="U214" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="V214" s="10" t="n">
-        <v>103</v>
-      </c>
-      <c r="Y214" s="11" t="n">
-        <v>-331</v>
-      </c>
-      <c r="AA214" s="10" t="n">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="AR214" s="10" t="n">
+        <v>64</v>
+      </c>
+      <c r="AT214" s="11" t="n">
+        <v>-64</v>
+      </c>
+      <c r="AV214" s="11" t="n">
+        <v>-200</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="8" t="n">
-        <v>-200</v>
+        <v>-203</v>
       </c>
       <c r="B215" s="8" t="inlineStr">
         <is>
@@ -11193,41 +11205,38 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>MARTÍNEZ GUALCO, Federico</t>
+          <t>FRAUCA, Diva</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Panamá</t>
         </is>
       </c>
       <c r="E215" s="9" t="n">
-        <v>1875</v>
+        <v>1872</v>
       </c>
       <c r="F215" s="8" t="inlineStr">
         <is>
-          <t>Mundial Buenos Aires 2022</t>
+          <t>Norcenca Panamá 2023</t>
         </is>
       </c>
       <c r="G215" s="8" t="n">
-        <v>133</v>
+        <v>50</v>
       </c>
       <c r="H215" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR215" s="10" t="n">
-        <v>64</v>
-      </c>
-      <c r="AT215" s="11" t="n">
-        <v>-64</v>
-      </c>
-      <c r="AV215" s="11" t="n">
-        <v>-200</v>
+        <v>2</v>
+      </c>
+      <c r="AL215" s="11" t="n">
+        <v>-75</v>
+      </c>
+      <c r="AM215" s="11" t="n">
+        <v>-128</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="8" t="n">
-        <v>-203</v>
+        <v>-207</v>
       </c>
       <c r="B216" s="8" t="inlineStr">
         <is>
@@ -11236,7 +11245,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>FRAUCA, Diva</t>
+          <t>ÁVILA, Janey</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -11245,7 +11254,7 @@
         </is>
       </c>
       <c r="E216" s="9" t="n">
-        <v>1872</v>
+        <v>1869</v>
       </c>
       <c r="F216" s="8" t="inlineStr">
         <is>
@@ -11259,10 +11268,10 @@
         <v>2</v>
       </c>
       <c r="AL216" s="11" t="n">
-        <v>-75</v>
+        <v>-89</v>
       </c>
       <c r="AM216" s="11" t="n">
-        <v>-128</v>
+        <v>-118</v>
       </c>
     </row>
     <row r="217">
@@ -11276,33 +11285,32 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>ÁVILA, Janey</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>Panamá</t>
-        </is>
-      </c>
+          <t>TARIPA, Rhy</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
       <c r="E217" s="9" t="n">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="F217" s="8" t="inlineStr">
         <is>
-          <t>Norcenca Panamá 2023</t>
+          <t>Mundial Santiago de Chile 2025</t>
         </is>
       </c>
       <c r="G217" s="8" t="n">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="H217" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL217" s="11" t="n">
-        <v>-89</v>
-      </c>
-      <c r="AM217" s="11" t="n">
-        <v>-118</v>
+        <v>3</v>
+      </c>
+      <c r="I217" s="11" t="n">
+        <v>-45</v>
+      </c>
+      <c r="K217" s="11" t="n">
+        <v>-65</v>
+      </c>
+      <c r="M217" s="11" t="n">
+        <v>-97</v>
       </c>
     </row>
     <row r="218">
@@ -11316,37 +11324,47 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>TARIPA, Rhy</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr"/>
+          <t>SARDUY, Diosbel</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Cuba</t>
+        </is>
+      </c>
       <c r="E218" s="9" t="n">
         <v>1868</v>
       </c>
       <c r="F218" s="8" t="inlineStr">
         <is>
-          <t>Mundial Santiago de Chile 2025</t>
+          <t>Cuba Scrabble Varadero 2025</t>
         </is>
       </c>
       <c r="G218" s="8" t="n">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="H218" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I218" s="11" t="n">
-        <v>-45</v>
-      </c>
-      <c r="K218" s="11" t="n">
-        <v>-65</v>
-      </c>
-      <c r="M218" s="11" t="n">
-        <v>-97</v>
+        <v>5</v>
+      </c>
+      <c r="S218" s="11" t="n">
+        <v>-18</v>
+      </c>
+      <c r="AP218" s="11" t="n">
+        <v>-22</v>
+      </c>
+      <c r="AQ218" s="11" t="n">
+        <v>-36</v>
+      </c>
+      <c r="BA218" s="11" t="n">
+        <v>-56</v>
+      </c>
+      <c r="BB218" s="11" t="n">
+        <v>-75</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="8" t="n">
-        <v>-207</v>
+        <v>-210</v>
       </c>
       <c r="B219" s="8" t="inlineStr">
         <is>
@@ -11355,47 +11373,41 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>SARDUY, Diosbel</t>
+          <t>HENARES, Miguel Ángel</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Cuba</t>
+          <t>España</t>
         </is>
       </c>
       <c r="E219" s="9" t="n">
-        <v>1868</v>
+        <v>1865</v>
       </c>
       <c r="F219" s="8" t="inlineStr">
         <is>
-          <t>Cuba Scrabble Varadero 2025</t>
+          <t>Mundial Granada 2024</t>
         </is>
       </c>
       <c r="G219" s="8" t="n">
-        <v>81</v>
+        <v>217</v>
       </c>
       <c r="H219" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="S219" s="11" t="n">
-        <v>-18</v>
-      </c>
-      <c r="AP219" s="11" t="n">
-        <v>-22</v>
-      </c>
-      <c r="AQ219" s="11" t="n">
-        <v>-36</v>
-      </c>
-      <c r="BA219" s="11" t="n">
-        <v>-56</v>
-      </c>
-      <c r="BB219" s="11" t="n">
-        <v>-75</v>
+        <v>3</v>
+      </c>
+      <c r="U219" s="11" t="n">
+        <v>-70</v>
+      </c>
+      <c r="W219" s="11" t="n">
+        <v>-109</v>
+      </c>
+      <c r="Y219" s="11" t="n">
+        <v>-31</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="8" t="n">
-        <v>-210</v>
+        <v>-213</v>
       </c>
       <c r="B220" s="8" t="inlineStr">
         <is>
@@ -11404,41 +11416,37 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>HENARES, Miguel Ángel</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
+          <t>MARRERO, Deyanura</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
       <c r="E220" s="9" t="n">
-        <v>1865</v>
+        <v>1861</v>
       </c>
       <c r="F220" s="8" t="inlineStr">
         <is>
-          <t>Mundial Granada 2024</t>
+          <t>Mundial Santiago de Chile 2025</t>
         </is>
       </c>
       <c r="G220" s="8" t="n">
-        <v>217</v>
+        <v>104</v>
       </c>
       <c r="H220" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="U220" s="11" t="n">
-        <v>-70</v>
-      </c>
-      <c r="W220" s="11" t="n">
-        <v>-109</v>
-      </c>
-      <c r="Y220" s="11" t="n">
-        <v>-31</v>
+      <c r="I220" s="11" t="n">
+        <v>-55</v>
+      </c>
+      <c r="K220" s="11" t="n">
+        <v>-51</v>
+      </c>
+      <c r="M220" s="11" t="n">
+        <v>-107</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="8" t="n">
-        <v>-213</v>
+        <v>-217</v>
       </c>
       <c r="B221" s="8" t="inlineStr">
         <is>
@@ -11447,37 +11455,44 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>MARRERO, Deyanura</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr"/>
+          <t>DECENA, Daniela</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
       <c r="E221" s="9" t="n">
-        <v>1861</v>
+        <v>1858</v>
       </c>
       <c r="F221" s="8" t="inlineStr">
         <is>
-          <t>Mundial Santiago de Chile 2025</t>
+          <t>Mundial Granada 2024</t>
         </is>
       </c>
       <c r="G221" s="8" t="n">
-        <v>104</v>
+        <v>254</v>
       </c>
       <c r="H221" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I221" s="11" t="n">
-        <v>-55</v>
-      </c>
-      <c r="K221" s="11" t="n">
-        <v>-51</v>
-      </c>
-      <c r="M221" s="11" t="n">
-        <v>-107</v>
+        <v>4</v>
+      </c>
+      <c r="U221" s="11" t="n">
+        <v>-116</v>
+      </c>
+      <c r="W221" s="11" t="n">
+        <v>-160</v>
+      </c>
+      <c r="Y221" s="10" t="n">
+        <v>52</v>
+      </c>
+      <c r="AN221" s="10" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="8" t="n">
-        <v>-217</v>
+        <v>-220</v>
       </c>
       <c r="B222" s="8" t="inlineStr">
         <is>
@@ -11486,7 +11501,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>DECENA, Daniela</t>
+          <t>PEROZO, Héctor</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -11495,7 +11510,7 @@
         </is>
       </c>
       <c r="E222" s="9" t="n">
-        <v>1858</v>
+        <v>1855</v>
       </c>
       <c r="F222" s="8" t="inlineStr">
         <is>
@@ -11508,22 +11523,22 @@
       <c r="H222" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="U222" s="11" t="n">
-        <v>-116</v>
-      </c>
-      <c r="W222" s="11" t="n">
-        <v>-160</v>
-      </c>
-      <c r="Y222" s="10" t="n">
-        <v>52</v>
-      </c>
-      <c r="AN222" s="10" t="n">
-        <v>7</v>
+      <c r="U222" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="W222" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y222" s="11" t="n">
+        <v>-268</v>
+      </c>
+      <c r="AN222" s="11" t="n">
+        <v>-3</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="8" t="n">
-        <v>-220</v>
+        <v>-222</v>
       </c>
       <c r="B223" s="8" t="inlineStr">
         <is>
@@ -11532,44 +11547,59 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>PEROZO, Héctor</t>
+          <t>FALCONER, Isaac</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E223" s="9" t="n">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="F223" s="8" t="inlineStr">
         <is>
-          <t>Mundial Granada 2024</t>
+          <t>Norcenca Guanajuato 2025</t>
         </is>
       </c>
       <c r="G223" s="8" t="n">
-        <v>254</v>
+        <v>365</v>
       </c>
       <c r="H223" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="U223" s="10" t="n">
-        <v>23</v>
-      </c>
-      <c r="W223" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="O223" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="Y223" s="11" t="n">
-        <v>-268</v>
-      </c>
-      <c r="AN223" s="11" t="n">
-        <v>-3</v>
+      <c r="T223" s="10" t="n">
+        <v>63</v>
+      </c>
+      <c r="U223" s="11" t="n">
+        <v>-113</v>
+      </c>
+      <c r="W223" s="11" t="n">
+        <v>-20</v>
+      </c>
+      <c r="Y223" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA223" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="AF223" s="11" t="n">
+        <v>-44</v>
+      </c>
+      <c r="AH223" s="11" t="n">
+        <v>-100</v>
+      </c>
+      <c r="AJ223" s="11" t="n">
+        <v>-82</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="8" t="n">
-        <v>-222</v>
+        <v>-230</v>
       </c>
       <c r="B224" s="8" t="inlineStr">
         <is>
@@ -11578,59 +11608,38 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>FALCONER, Isaac</t>
+          <t>ALVARADO, Katia</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Panamá</t>
         </is>
       </c>
       <c r="E224" s="9" t="n">
-        <v>1854</v>
+        <v>1845</v>
       </c>
       <c r="F224" s="8" t="inlineStr">
         <is>
-          <t>Norcenca Guanajuato 2025</t>
+          <t>Norcenca Panamá 2023</t>
         </is>
       </c>
       <c r="G224" s="8" t="n">
-        <v>365</v>
+        <v>50</v>
       </c>
       <c r="H224" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="O224" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="T224" s="10" t="n">
-        <v>63</v>
-      </c>
-      <c r="U224" s="11" t="n">
-        <v>-113</v>
-      </c>
-      <c r="W224" s="11" t="n">
-        <v>-20</v>
-      </c>
-      <c r="Y224" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA224" s="10" t="n">
-        <v>33</v>
-      </c>
-      <c r="AF224" s="11" t="n">
-        <v>-44</v>
-      </c>
-      <c r="AH224" s="11" t="n">
-        <v>-100</v>
-      </c>
-      <c r="AJ224" s="11" t="n">
-        <v>-82</v>
+        <v>2</v>
+      </c>
+      <c r="AL224" s="11" t="n">
+        <v>-92</v>
+      </c>
+      <c r="AM224" s="11" t="n">
+        <v>-138</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="8" t="n">
-        <v>-230</v>
+        <v>-241</v>
       </c>
       <c r="B225" s="8" t="inlineStr">
         <is>
@@ -11639,38 +11648,44 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>ALVARADO, Katia</t>
+          <t>MARTÍNEZ, Carlos</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Panamá</t>
+          <t>España</t>
         </is>
       </c>
       <c r="E225" s="9" t="n">
-        <v>1845</v>
+        <v>1833</v>
       </c>
       <c r="F225" s="8" t="inlineStr">
         <is>
-          <t>Norcenca Panamá 2023</t>
+          <t>Mundial Granada 2024</t>
         </is>
       </c>
       <c r="G225" s="8" t="n">
-        <v>50</v>
+        <v>254</v>
       </c>
       <c r="H225" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL225" s="11" t="n">
-        <v>-92</v>
-      </c>
-      <c r="AM225" s="11" t="n">
-        <v>-138</v>
+        <v>4</v>
+      </c>
+      <c r="U225" s="11" t="n">
+        <v>-187</v>
+      </c>
+      <c r="W225" s="11" t="n">
+        <v>-145</v>
+      </c>
+      <c r="Y225" s="10" t="n">
+        <v>64</v>
+      </c>
+      <c r="AN225" s="10" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="8" t="n">
-        <v>-241</v>
+        <v>-244</v>
       </c>
       <c r="B226" s="8" t="inlineStr">
         <is>
@@ -11679,7 +11694,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>MARTÍNEZ, Carlos</t>
+          <t>GONZÁLEZ, Inma</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -11688,35 +11703,38 @@
         </is>
       </c>
       <c r="E226" s="9" t="n">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="F226" s="8" t="inlineStr">
         <is>
-          <t>Mundial Granada 2024</t>
+          <t>Europeo Murcia 2025</t>
         </is>
       </c>
       <c r="G226" s="8" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H226" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="N226" s="10" t="n">
+        <v>50</v>
       </c>
       <c r="U226" s="11" t="n">
-        <v>-187</v>
+        <v>-233</v>
       </c>
       <c r="W226" s="11" t="n">
-        <v>-145</v>
+        <v>-248</v>
       </c>
       <c r="Y226" s="10" t="n">
-        <v>64</v>
-      </c>
-      <c r="AN226" s="10" t="n">
-        <v>27</v>
+        <v>211</v>
+      </c>
+      <c r="AK226" s="11" t="n">
+        <v>-24</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="8" t="n">
-        <v>-244</v>
+        <v>-245</v>
       </c>
       <c r="B227" s="8" t="inlineStr">
         <is>
@@ -11725,47 +11743,41 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>GONZÁLEZ, Inma</t>
+          <t>GONZÁLEZ, Christopher</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="E227" s="9" t="n">
-        <v>1832</v>
+        <v>1830</v>
       </c>
       <c r="F227" s="8" t="inlineStr">
         <is>
-          <t>Europeo Murcia 2025</t>
+          <t>Mundial Costa Rica 2023</t>
         </is>
       </c>
       <c r="G227" s="8" t="n">
-        <v>253</v>
+        <v>101</v>
       </c>
       <c r="H227" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N227" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="U227" s="11" t="n">
-        <v>-233</v>
-      </c>
-      <c r="W227" s="11" t="n">
-        <v>-248</v>
-      </c>
-      <c r="Y227" s="10" t="n">
-        <v>211</v>
-      </c>
-      <c r="AK227" s="11" t="n">
-        <v>-24</v>
+        <v>3</v>
+      </c>
+      <c r="AF227" s="11" t="n">
+        <v>-64</v>
+      </c>
+      <c r="AH227" s="11" t="n">
+        <v>-69</v>
+      </c>
+      <c r="AJ227" s="11" t="n">
+        <v>-112</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="8" t="n">
-        <v>-245</v>
+        <v>-249</v>
       </c>
       <c r="B228" s="8" t="inlineStr">
         <is>
@@ -11774,41 +11786,53 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>GONZÁLEZ, Christopher</t>
+          <t>KURODA, Kunihiko</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Costa Rica</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="E228" s="9" t="n">
-        <v>1830</v>
+        <v>1826</v>
       </c>
       <c r="F228" s="8" t="inlineStr">
         <is>
-          <t>Mundial Costa Rica 2023</t>
+          <t>Mundial Santiago de Chile 2025</t>
         </is>
       </c>
       <c r="G228" s="8" t="n">
-        <v>101</v>
+        <v>191</v>
       </c>
       <c r="H228" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF228" s="11" t="n">
-        <v>-64</v>
-      </c>
-      <c r="AH228" s="11" t="n">
-        <v>-69</v>
-      </c>
-      <c r="AJ228" s="11" t="n">
-        <v>-112</v>
+        <v>7</v>
+      </c>
+      <c r="I228" s="11" t="n">
+        <v>-17</v>
+      </c>
+      <c r="K228" s="11" t="n">
+        <v>-49</v>
+      </c>
+      <c r="M228" s="11" t="n">
+        <v>-82</v>
+      </c>
+      <c r="U228" s="11" t="n">
+        <v>-140</v>
+      </c>
+      <c r="V228" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="X228" s="10" t="n">
+        <v>104</v>
+      </c>
+      <c r="AK228" s="11" t="n">
+        <v>-94</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="8" t="n">
-        <v>-249</v>
+        <v>-251</v>
       </c>
       <c r="B229" s="8" t="inlineStr">
         <is>
@@ -11817,53 +11841,53 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>KURODA, Kunihiko</t>
+          <t>CRUZ, Elizabeth</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Panamá</t>
         </is>
       </c>
       <c r="E229" s="9" t="n">
-        <v>1826</v>
+        <v>1823</v>
       </c>
       <c r="F229" s="8" t="inlineStr">
         <is>
-          <t>Mundial Santiago de Chile 2025</t>
+          <t>Norcenca Panamá 2023</t>
         </is>
       </c>
       <c r="G229" s="8" t="n">
-        <v>191</v>
+        <v>225</v>
       </c>
       <c r="H229" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="I229" s="11" t="n">
-        <v>-17</v>
-      </c>
-      <c r="K229" s="11" t="n">
-        <v>-49</v>
-      </c>
-      <c r="M229" s="11" t="n">
-        <v>-82</v>
-      </c>
-      <c r="U229" s="11" t="n">
-        <v>-140</v>
-      </c>
-      <c r="V229" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="X229" s="10" t="n">
-        <v>104</v>
-      </c>
-      <c r="AK229" s="11" t="n">
-        <v>-94</v>
+      <c r="AL229" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM229" s="11" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AR229" s="11" t="n">
+        <v>-47</v>
+      </c>
+      <c r="AT229" s="11" t="n">
+        <v>-73</v>
+      </c>
+      <c r="AV229" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX229" s="11" t="n">
+        <v>-85</v>
+      </c>
+      <c r="AY229" s="11" t="n">
+        <v>-65</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="8" t="n">
-        <v>-251</v>
+        <v>-254</v>
       </c>
       <c r="B230" s="8" t="inlineStr">
         <is>
@@ -11872,53 +11896,44 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>CRUZ, Elizabeth</t>
+          <t>GUEVARA, Rolando</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Panamá</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="E230" s="9" t="n">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="F230" s="8" t="inlineStr">
         <is>
-          <t>Norcenca Panamá 2023</t>
+          <t>Mundial Santiago de Chile 2025</t>
         </is>
       </c>
       <c r="G230" s="8" t="n">
-        <v>225</v>
+        <v>117</v>
       </c>
       <c r="H230" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AL230" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM230" s="11" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AR230" s="11" t="n">
-        <v>-47</v>
-      </c>
-      <c r="AT230" s="11" t="n">
-        <v>-73</v>
-      </c>
-      <c r="AV230" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX230" s="11" t="n">
-        <v>-85</v>
-      </c>
-      <c r="AY230" s="11" t="n">
-        <v>-65</v>
+        <v>4</v>
+      </c>
+      <c r="I230" s="11" t="n">
+        <v>-55</v>
+      </c>
+      <c r="K230" s="11" t="n">
+        <v>-77</v>
+      </c>
+      <c r="M230" s="11" t="n">
+        <v>-68</v>
+      </c>
+      <c r="T230" s="11" t="n">
+        <v>-54</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="8" t="n">
-        <v>-254</v>
+        <v>-253</v>
       </c>
       <c r="B231" s="8" t="inlineStr">
         <is>
@@ -11927,12 +11942,12 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>GUEVARA, Rolando</t>
+          <t>SÁNCHEZ, Cristina</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Costa Rica</t>
+          <t>Estados Unidos</t>
         </is>
       </c>
       <c r="E231" s="9" t="n">
@@ -11940,31 +11955,34 @@
       </c>
       <c r="F231" s="8" t="inlineStr">
         <is>
-          <t>Mundial Santiago de Chile 2025</t>
+          <t>Norcenca Guanajuato 2025</t>
         </is>
       </c>
       <c r="G231" s="8" t="n">
-        <v>117</v>
+        <v>253</v>
       </c>
       <c r="H231" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="I231" s="11" t="n">
-        <v>-55</v>
-      </c>
-      <c r="K231" s="11" t="n">
-        <v>-77</v>
-      </c>
-      <c r="M231" s="11" t="n">
-        <v>-68</v>
-      </c>
-      <c r="T231" s="11" t="n">
-        <v>-54</v>
+        <v>6</v>
+      </c>
+      <c r="O231" s="11" t="n">
+        <v>-13</v>
+      </c>
+      <c r="U231" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="W231" s="11" t="n">
+        <v>-22</v>
+      </c>
+      <c r="Y231" s="11" t="n">
+        <v>-220</v>
+      </c>
+      <c r="AA231" s="11" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="8" t="n">
-        <v>-253</v>
+        <v>-275</v>
       </c>
       <c r="B232" s="8" t="inlineStr">
         <is>
@@ -11973,47 +11991,44 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>SÁNCHEZ, Cristina</t>
+          <t>PEROZO PULIDO, Héctor Andrés</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="E232" s="9" t="n">
-        <v>1821</v>
+        <v>1800</v>
       </c>
       <c r="F232" s="8" t="inlineStr">
         <is>
-          <t>Norcenca Guanajuato 2025</t>
+          <t>Mundial Granada 2024</t>
         </is>
       </c>
       <c r="G232" s="8" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H232" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="O232" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U232" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W232" s="11" t="n">
+        <v>-143</v>
+      </c>
+      <c r="Y232" s="11" t="n">
+        <v>-119</v>
+      </c>
+      <c r="AN232" s="11" t="n">
         <v>-13</v>
-      </c>
-      <c r="U232" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="W232" s="11" t="n">
-        <v>-22</v>
-      </c>
-      <c r="Y232" s="11" t="n">
-        <v>-222</v>
-      </c>
-      <c r="AA232" s="10" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="8" t="n">
-        <v>-275</v>
+        <v>-286</v>
       </c>
       <c r="B233" s="8" t="inlineStr">
         <is>
@@ -12022,44 +12037,41 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>PEROZO PULIDO, Héctor Andrés</t>
+          <t>LÓPEZ, Alexis</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E233" s="9" t="n">
-        <v>1800</v>
+        <v>1789</v>
       </c>
       <c r="F233" s="8" t="inlineStr">
         <is>
-          <t>Mundial Granada 2024</t>
+          <t>Mundial Costa Rica 2023</t>
         </is>
       </c>
       <c r="G233" s="8" t="n">
-        <v>254</v>
+        <v>101</v>
       </c>
       <c r="H233" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="U233" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W233" s="11" t="n">
-        <v>-143</v>
-      </c>
-      <c r="Y233" s="11" t="n">
-        <v>-119</v>
-      </c>
-      <c r="AN233" s="11" t="n">
-        <v>-13</v>
+        <v>3</v>
+      </c>
+      <c r="AF233" s="11" t="n">
+        <v>-62</v>
+      </c>
+      <c r="AH233" s="11" t="n">
+        <v>-92</v>
+      </c>
+      <c r="AJ233" s="11" t="n">
+        <v>-132</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="8" t="n">
-        <v>-286</v>
+        <v>-302</v>
       </c>
       <c r="B234" s="8" t="inlineStr">
         <is>
@@ -12068,41 +12080,41 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>LÓPEZ, Alexis</t>
+          <t>MORENO, Héctor Eduardo</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E234" s="9" t="n">
-        <v>1789</v>
+        <v>1773</v>
       </c>
       <c r="F234" s="8" t="inlineStr">
         <is>
-          <t>Mundial Costa Rica 2023</t>
+          <t>Mundial Buenos Aires 2022</t>
         </is>
       </c>
       <c r="G234" s="8" t="n">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="H234" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="AF234" s="11" t="n">
-        <v>-62</v>
-      </c>
-      <c r="AH234" s="11" t="n">
-        <v>-92</v>
-      </c>
-      <c r="AJ234" s="11" t="n">
-        <v>-132</v>
+      <c r="AR234" s="11" t="n">
+        <v>-68</v>
+      </c>
+      <c r="AT234" s="11" t="n">
+        <v>-114</v>
+      </c>
+      <c r="AV234" s="11" t="n">
+        <v>-120</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="8" t="n">
-        <v>-302</v>
+        <v>-318</v>
       </c>
       <c r="B235" s="8" t="inlineStr">
         <is>
@@ -12111,16 +12123,16 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>MORENO, Héctor Eduardo</t>
+          <t>TEJEIRA, Dulce</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Estados Unidos</t>
         </is>
       </c>
       <c r="E235" s="9" t="n">
-        <v>1773</v>
+        <v>1757</v>
       </c>
       <c r="F235" s="8" t="inlineStr">
         <is>
@@ -12134,18 +12146,18 @@
         <v>3</v>
       </c>
       <c r="AR235" s="11" t="n">
-        <v>-68</v>
-      </c>
-      <c r="AT235" s="11" t="n">
-        <v>-114</v>
+        <v>-109</v>
+      </c>
+      <c r="AT235" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AV235" s="11" t="n">
-        <v>-120</v>
+        <v>-210</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="8" t="n">
-        <v>-318</v>
+        <v>-319</v>
       </c>
       <c r="B236" s="8" t="inlineStr">
         <is>
@@ -12154,41 +12166,47 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>TEJEIRA, Dulce</t>
+          <t>MARRERO, Deyanira</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="E236" s="9" t="n">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="F236" s="8" t="inlineStr">
         <is>
-          <t>Mundial Buenos Aires 2022</t>
+          <t>Mundial Granada 2024</t>
         </is>
       </c>
       <c r="G236" s="8" t="n">
-        <v>133</v>
+        <v>273</v>
       </c>
       <c r="H236" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR236" s="11" t="n">
-        <v>-109</v>
-      </c>
-      <c r="AT236" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV236" s="11" t="n">
-        <v>-210</v>
+        <v>5</v>
+      </c>
+      <c r="U236" s="11" t="n">
+        <v>-34</v>
+      </c>
+      <c r="W236" s="11" t="n">
+        <v>-32</v>
+      </c>
+      <c r="Y236" s="11" t="n">
+        <v>-222</v>
+      </c>
+      <c r="AC236" s="11" t="n">
+        <v>-68</v>
+      </c>
+      <c r="AN236" s="10" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="8" t="n">
-        <v>-319</v>
+        <v>-386</v>
       </c>
       <c r="B237" s="8" t="inlineStr">
         <is>
@@ -12197,47 +12215,53 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>MARRERO, Deyanira</t>
+          <t>OLIVA, Brandon Uriel</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E237" s="9" t="n">
-        <v>1755</v>
+        <v>1689</v>
       </c>
       <c r="F237" s="8" t="inlineStr">
         <is>
-          <t>Mundial Granada 2024</t>
+          <t>Norcenca Guanajuato 2025</t>
         </is>
       </c>
       <c r="G237" s="8" t="n">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="H237" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="O237" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="U237" s="11" t="n">
+        <v>-48</v>
+      </c>
+      <c r="W237" s="11" t="n">
+        <v>-124</v>
+      </c>
+      <c r="Y237" s="11" t="n">
+        <v>-200</v>
+      </c>
+      <c r="AF237" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="U237" s="11" t="n">
-        <v>-34</v>
-      </c>
-      <c r="W237" s="11" t="n">
-        <v>-32</v>
-      </c>
-      <c r="Y237" s="11" t="n">
-        <v>-222</v>
-      </c>
-      <c r="AC237" s="11" t="n">
-        <v>-68</v>
-      </c>
-      <c r="AN237" s="10" t="n">
-        <v>37</v>
+      <c r="AG237" s="11" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AI237" s="11" t="n">
+        <v>-27</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="8" t="n">
-        <v>-386</v>
+        <v>-389</v>
       </c>
       <c r="B238" s="8" t="inlineStr">
         <is>
@@ -12246,53 +12270,50 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>OLIVA, Brandon Uriel</t>
+          <t>RIPA, Rhyta</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="E238" s="9" t="n">
-        <v>1689</v>
+        <v>1686</v>
       </c>
       <c r="F238" s="8" t="inlineStr">
         <is>
-          <t>Norcenca Guanajuato 2025</t>
+          <t>Andino Lima 2025</t>
         </is>
       </c>
       <c r="G238" s="8" t="n">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="H238" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="O238" s="10" t="n">
-        <v>20</v>
+        <v>6</v>
+      </c>
+      <c r="P238" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q238" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="U238" s="11" t="n">
-        <v>-48</v>
+        <v>-3</v>
       </c>
       <c r="W238" s="11" t="n">
-        <v>-124</v>
+        <v>-98</v>
       </c>
       <c r="Y238" s="11" t="n">
-        <v>-200</v>
-      </c>
-      <c r="AF238" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG238" s="11" t="n">
-        <v>-12</v>
-      </c>
-      <c r="AI238" s="11" t="n">
-        <v>-27</v>
+        <v>-163</v>
+      </c>
+      <c r="AN238" s="11" t="n">
+        <v>-133</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="8" t="n">
-        <v>-389</v>
+        <v>-406</v>
       </c>
       <c r="B239" s="8" t="inlineStr">
         <is>
@@ -12301,50 +12322,71 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>RIPA, Rhyta</t>
+          <t>ACUÑA, Beatriz</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Panamá</t>
         </is>
       </c>
       <c r="E239" s="9" t="n">
-        <v>1686</v>
+        <v>1670</v>
       </c>
       <c r="F239" s="8" t="inlineStr">
         <is>
-          <t>Andino Lima 2025</t>
+          <t>Cuba Scrabble Varadero 2025</t>
         </is>
       </c>
       <c r="G239" s="8" t="n">
-        <v>272</v>
+        <v>481</v>
       </c>
       <c r="H239" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="P239" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q239" s="10" t="n">
-        <v>4</v>
+        <v>13</v>
+      </c>
+      <c r="S239" s="11" t="n">
+        <v>-1</v>
       </c>
       <c r="U239" s="11" t="n">
-        <v>-3</v>
+        <v>-130</v>
       </c>
       <c r="W239" s="11" t="n">
-        <v>-98</v>
-      </c>
-      <c r="Y239" s="11" t="n">
-        <v>-163</v>
-      </c>
-      <c r="AN239" s="11" t="n">
-        <v>-133</v>
+        <v>-1</v>
+      </c>
+      <c r="Y239" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="AL239" s="11" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AM239" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP239" s="11" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AQ239" s="10" t="n">
+        <v>47</v>
+      </c>
+      <c r="AR239" s="11" t="n">
+        <v>-57</v>
+      </c>
+      <c r="AT239" s="11" t="n">
+        <v>-114</v>
+      </c>
+      <c r="AV239" s="11" t="n">
+        <v>-123</v>
+      </c>
+      <c r="BA239" s="11" t="n">
+        <v>-21</v>
+      </c>
+      <c r="BB239" s="11" t="n">
+        <v>-55</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="8" t="n">
-        <v>-406</v>
+        <v>-410</v>
       </c>
       <c r="B240" s="8" t="inlineStr">
         <is>
@@ -12353,71 +12395,50 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>ACUÑA, Beatriz</t>
+          <t>LÓPEZ, Adán</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Panamá</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E240" s="9" t="n">
-        <v>1670</v>
+        <v>1665</v>
       </c>
       <c r="F240" s="8" t="inlineStr">
         <is>
-          <t>Cuba Scrabble Varadero 2025</t>
+          <t>Mundial Granada 2024</t>
         </is>
       </c>
       <c r="G240" s="8" t="n">
-        <v>481</v>
+        <v>266</v>
       </c>
       <c r="H240" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="S240" s="11" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U240" s="11" t="n">
-        <v>-130</v>
+        <v>-83</v>
       </c>
       <c r="W240" s="11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Y240" s="10" t="n">
-        <v>35</v>
-      </c>
-      <c r="AL240" s="11" t="n">
-        <v>-7</v>
-      </c>
-      <c r="AM240" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP240" s="11" t="n">
-        <v>-9</v>
-      </c>
-      <c r="AQ240" s="10" t="n">
-        <v>47</v>
-      </c>
-      <c r="AR240" s="11" t="n">
-        <v>-57</v>
-      </c>
-      <c r="AT240" s="11" t="n">
-        <v>-114</v>
-      </c>
-      <c r="AV240" s="11" t="n">
         <v>-123</v>
       </c>
-      <c r="BA240" s="11" t="n">
+      <c r="Y240" s="11" t="n">
+        <v>-83</v>
+      </c>
+      <c r="AF240" s="11" t="n">
         <v>-21</v>
       </c>
-      <c r="BB240" s="11" t="n">
-        <v>-55</v>
+      <c r="AG240" s="11" t="n">
+        <v>-33</v>
+      </c>
+      <c r="AI240" s="11" t="n">
+        <v>-67</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="8" t="n">
-        <v>-410</v>
+        <v>-433</v>
       </c>
       <c r="B241" s="8" t="inlineStr">
         <is>
@@ -12426,16 +12447,16 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>LÓPEZ, Adán</t>
+          <t>GALINDO, Ligia</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E241" s="9" t="n">
-        <v>1665</v>
+        <v>1642</v>
       </c>
       <c r="F241" s="8" t="inlineStr">
         <is>
@@ -12443,33 +12464,24 @@
         </is>
       </c>
       <c r="G241" s="8" t="n">
-        <v>266</v>
+        <v>217</v>
       </c>
       <c r="H241" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U241" s="11" t="n">
-        <v>-83</v>
+        <v>-81</v>
       </c>
       <c r="W241" s="11" t="n">
-        <v>-123</v>
+        <v>-61</v>
       </c>
       <c r="Y241" s="11" t="n">
-        <v>-83</v>
-      </c>
-      <c r="AF241" s="11" t="n">
-        <v>-21</v>
-      </c>
-      <c r="AG241" s="11" t="n">
-        <v>-33</v>
-      </c>
-      <c r="AI241" s="11" t="n">
-        <v>-67</v>
+        <v>-291</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="8" t="n">
-        <v>-433</v>
+        <v>-434</v>
       </c>
       <c r="B242" s="8" t="inlineStr">
         <is>
@@ -12478,12 +12490,12 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>GALINDO, Ligia</t>
+          <t>REYNA, Uriel</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E242" s="9" t="n">
@@ -12495,24 +12507,33 @@
         </is>
       </c>
       <c r="G242" s="8" t="n">
-        <v>217</v>
+        <v>266</v>
       </c>
       <c r="H242" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U242" s="11" t="n">
-        <v>-81</v>
+        <v>-12</v>
       </c>
       <c r="W242" s="11" t="n">
-        <v>-61</v>
+        <v>-110</v>
       </c>
       <c r="Y242" s="11" t="n">
-        <v>-291</v>
+        <v>-204</v>
+      </c>
+      <c r="AF242" s="11" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AG242" s="11" t="n">
+        <v>-59</v>
+      </c>
+      <c r="AI242" s="11" t="n">
+        <v>-37</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="8" t="n">
-        <v>-434</v>
+        <v>-492</v>
       </c>
       <c r="B243" s="8" t="inlineStr">
         <is>
@@ -12521,16 +12542,16 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>REYNA, Uriel</t>
+          <t>GARCÍA, Maripili</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>España</t>
         </is>
       </c>
       <c r="E243" s="9" t="n">
-        <v>1642</v>
+        <v>1583</v>
       </c>
       <c r="F243" s="8" t="inlineStr">
         <is>
@@ -12538,33 +12559,27 @@
         </is>
       </c>
       <c r="G243" s="8" t="n">
-        <v>266</v>
+        <v>236</v>
       </c>
       <c r="H243" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U243" s="11" t="n">
-        <v>-12</v>
+        <v>-72</v>
       </c>
       <c r="W243" s="11" t="n">
-        <v>-110</v>
+        <v>-91</v>
       </c>
       <c r="Y243" s="11" t="n">
-        <v>-204</v>
-      </c>
-      <c r="AF243" s="11" t="n">
-        <v>-12</v>
-      </c>
-      <c r="AG243" s="11" t="n">
-        <v>-59</v>
-      </c>
-      <c r="AI243" s="11" t="n">
-        <v>-37</v>
+        <v>-245</v>
+      </c>
+      <c r="AK243" s="11" t="n">
+        <v>-84</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="8" t="n">
-        <v>-492</v>
+        <v>-520</v>
       </c>
       <c r="B244" s="8" t="inlineStr">
         <is>
@@ -12573,16 +12588,16 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>GARCÍA, Maripili</t>
+          <t>CHOWELL, Karla</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E244" s="9" t="n">
-        <v>1583</v>
+        <v>1555</v>
       </c>
       <c r="F244" s="8" t="inlineStr">
         <is>
@@ -12590,73 +12605,27 @@
         </is>
       </c>
       <c r="G244" s="8" t="n">
-        <v>236</v>
+        <v>266</v>
       </c>
       <c r="H244" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U244" s="11" t="n">
         <v>-72</v>
       </c>
       <c r="W244" s="11" t="n">
-        <v>-91</v>
+        <v>-104</v>
       </c>
       <c r="Y244" s="11" t="n">
-        <v>-245</v>
-      </c>
-      <c r="AK244" s="11" t="n">
-        <v>-84</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="8" t="n">
-        <v>-520</v>
-      </c>
-      <c r="B245" s="8" t="inlineStr">
-        <is>
-          <t>240°</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>CHOWELL, Karla</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>México</t>
-        </is>
-      </c>
-      <c r="E245" s="9" t="n">
-        <v>1556</v>
-      </c>
-      <c r="F245" s="8" t="inlineStr">
-        <is>
-          <t>Mundial Granada 2024</t>
-        </is>
-      </c>
-      <c r="G245" s="8" t="n">
-        <v>266</v>
-      </c>
-      <c r="H245" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="U245" s="11" t="n">
-        <v>-72</v>
-      </c>
-      <c r="W245" s="11" t="n">
-        <v>-104</v>
-      </c>
-      <c r="Y245" s="11" t="n">
         <v>-223</v>
       </c>
-      <c r="AF245" s="10" t="n">
+      <c r="AF244" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="AG245" s="11" t="n">
+      <c r="AG244" s="11" t="n">
         <v>-61</v>
       </c>
-      <c r="AI245" s="11" t="n">
+      <c r="AI244" s="11" t="n">
         <v>-77</v>
       </c>
     </row>
